--- a/gstdatabase/GSTR-3B-2023-2024.xlsx
+++ b/gstdatabase/GSTR-3B-2023-2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B53BD4-47F2-4DF7-84F6-98C4C0B7F3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F3E939-B3FB-4D22-BEB0-C6378C21B7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2023-2024</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -415,21 +415,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -441,6 +426,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -741,12 +741,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -758,10 +758,10 @@
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="21"/>
+      <c r="B3" s="28"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -807,100 +807,100 @@
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:62" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="25">
         <v>45017</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="23">
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="25">
         <v>45047</v>
       </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="23">
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="25">
         <v>45078</v>
       </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="23">
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="25">
         <v>45108</v>
       </c>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="23">
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="26"/>
+      <c r="V8" s="27"/>
+      <c r="W8" s="25">
         <v>45139</v>
       </c>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="23">
+      <c r="X8" s="26"/>
+      <c r="Y8" s="26"/>
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="27"/>
+      <c r="AB8" s="25">
         <v>45170</v>
       </c>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="25"/>
-      <c r="AG8" s="23">
+      <c r="AC8" s="26"/>
+      <c r="AD8" s="26"/>
+      <c r="AE8" s="26"/>
+      <c r="AF8" s="27"/>
+      <c r="AG8" s="25">
         <v>45200</v>
       </c>
-      <c r="AH8" s="24"/>
-      <c r="AI8" s="24"/>
-      <c r="AJ8" s="24"/>
-      <c r="AK8" s="25"/>
-      <c r="AL8" s="23">
+      <c r="AH8" s="26"/>
+      <c r="AI8" s="26"/>
+      <c r="AJ8" s="26"/>
+      <c r="AK8" s="27"/>
+      <c r="AL8" s="25">
         <v>45231</v>
       </c>
-      <c r="AM8" s="24"/>
-      <c r="AN8" s="24"/>
-      <c r="AO8" s="24"/>
-      <c r="AP8" s="25"/>
-      <c r="AQ8" s="23">
+      <c r="AM8" s="26"/>
+      <c r="AN8" s="26"/>
+      <c r="AO8" s="26"/>
+      <c r="AP8" s="27"/>
+      <c r="AQ8" s="25">
         <v>45261</v>
       </c>
-      <c r="AR8" s="24"/>
-      <c r="AS8" s="24"/>
-      <c r="AT8" s="24"/>
-      <c r="AU8" s="25"/>
-      <c r="AV8" s="23">
+      <c r="AR8" s="26"/>
+      <c r="AS8" s="26"/>
+      <c r="AT8" s="26"/>
+      <c r="AU8" s="27"/>
+      <c r="AV8" s="25">
         <v>45292</v>
       </c>
-      <c r="AW8" s="24"/>
-      <c r="AX8" s="24"/>
-      <c r="AY8" s="24"/>
-      <c r="AZ8" s="25"/>
-      <c r="BA8" s="23">
+      <c r="AW8" s="26"/>
+      <c r="AX8" s="26"/>
+      <c r="AY8" s="26"/>
+      <c r="AZ8" s="27"/>
+      <c r="BA8" s="25">
         <v>45323</v>
       </c>
-      <c r="BB8" s="24"/>
-      <c r="BC8" s="24"/>
-      <c r="BD8" s="24"/>
-      <c r="BE8" s="25"/>
-      <c r="BF8" s="23">
+      <c r="BB8" s="26"/>
+      <c r="BC8" s="26"/>
+      <c r="BD8" s="26"/>
+      <c r="BE8" s="27"/>
+      <c r="BF8" s="25">
         <v>45352</v>
       </c>
-      <c r="BG8" s="24"/>
-      <c r="BH8" s="24"/>
-      <c r="BI8" s="24"/>
-      <c r="BJ8" s="25"/>
+      <c r="BG8" s="26"/>
+      <c r="BH8" s="26"/>
+      <c r="BI8" s="26"/>
+      <c r="BJ8" s="27"/>
     </row>
     <row r="9" spans="1:62" s="16" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="17" t="s">
         <v>2</v>
       </c>
@@ -1097,14 +1097,14 @@
       </c>
       <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>15393</v>
+        <v>15396</v>
       </c>
       <c r="F10" s="14">
-        <v>70604</v>
+        <v>70607</v>
       </c>
       <c r="G10" s="5">
         <f>F10/C10</f>
-        <v>1.0050534527181882</v>
+        <v>1.0050961579524265</v>
       </c>
       <c r="H10" s="8">
         <v>72254</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="J10" s="4">
         <f>K10-I10</f>
-        <v>14611</v>
+        <v>14614</v>
       </c>
       <c r="K10" s="14">
-        <v>72211</v>
+        <v>72214</v>
       </c>
       <c r="L10" s="5">
         <f>K10/H10</f>
-        <v>0.99940487723863036</v>
+        <v>0.99944639743128405</v>
       </c>
       <c r="M10" s="8">
         <v>120466</v>
@@ -1131,14 +1131,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>23845</v>
+        <v>23852</v>
       </c>
       <c r="P10" s="14">
-        <v>120198</v>
+        <v>120205</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.99777530589543939</v>
+        <v>0.99783341357727495</v>
       </c>
       <c r="R10" s="8">
         <v>70979</v>
@@ -1148,14 +1148,14 @@
       </c>
       <c r="T10" s="4">
         <f>U10-S10</f>
-        <v>15286</v>
+        <v>15292</v>
       </c>
       <c r="U10" s="14">
-        <v>71273</v>
+        <v>71279</v>
       </c>
       <c r="V10" s="5">
         <f>U10/R10</f>
-        <v>1.0041420701897745</v>
+        <v>1.0042266022344637</v>
       </c>
       <c r="W10" s="8">
         <v>73348</v>
@@ -1165,14 +1165,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>14957</v>
+        <v>14963</v>
       </c>
       <c r="Z10" s="14">
-        <v>72985</v>
+        <v>72991</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>0.99505098980203954</v>
+        <v>0.99513279162349344</v>
       </c>
       <c r="AB10" s="8">
         <v>123554</v>
@@ -1182,14 +1182,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>25335</v>
+        <v>25350</v>
       </c>
       <c r="AE10" s="14">
-        <v>123339</v>
+        <v>123354</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.99825987017822171</v>
+        <v>0.9983812745843923</v>
       </c>
       <c r="AG10" s="8">
         <v>71950</v>
@@ -1199,14 +1199,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>15060</v>
+        <v>15069</v>
       </c>
       <c r="AJ10" s="14">
-        <v>72008</v>
+        <v>72017</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>1.0008061153578873</v>
+        <v>1.0009312022237664</v>
       </c>
       <c r="AL10" s="8">
         <v>73532</v>
@@ -1216,14 +1216,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>14445</v>
+        <v>14451</v>
       </c>
       <c r="AO10" s="14">
-        <v>72980</v>
+        <v>72986</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>0.99249306424413863</v>
+        <v>0.99257466137191974</v>
       </c>
       <c r="AQ10" s="8">
         <v>125499</v>
@@ -1233,14 +1233,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>22091</v>
+        <v>22106</v>
       </c>
       <c r="AT10" s="14">
-        <v>125730</v>
+        <v>125745</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>1.00184065211675</v>
+        <v>1.0019601749814739</v>
       </c>
       <c r="AV10" s="8">
         <v>72481</v>
@@ -1250,14 +1250,14 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>13998</v>
+        <v>14007</v>
       </c>
       <c r="AY10" s="14">
-        <v>72370</v>
+        <v>72379</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>0.99846856417543906</v>
+        <v>0.99859273464770082</v>
       </c>
       <c r="BA10" s="8">
         <v>73790</v>
@@ -1267,14 +1267,14 @@
       </c>
       <c r="BC10" s="4">
         <f>BD10-BB10</f>
-        <v>13136</v>
+        <v>13149</v>
       </c>
       <c r="BD10" s="14">
-        <v>73290</v>
+        <v>73303</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10/BA10</f>
-        <v>0.9932240140940507</v>
+        <v>0.99340018972760535</v>
       </c>
       <c r="BF10" s="8">
         <v>128129</v>
@@ -1284,14 +1284,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>30679</v>
+        <v>30702</v>
       </c>
       <c r="BI10" s="14">
-        <v>127879</v>
+        <v>127902</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.99804884140202454</v>
+        <v>0.99822834799303828</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1309,14 +1309,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E47" si="0">F11-D11</f>
-        <v>8351</v>
+        <v>8352</v>
       </c>
       <c r="F11" s="14">
-        <v>45069</v>
+        <v>45070</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>1.0124679875994069</v>
+        <v>1.0124904524419285</v>
       </c>
       <c r="H11" s="8">
         <v>46110</v>
@@ -1326,14 +1326,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>8437</v>
+        <v>8438</v>
       </c>
       <c r="K11" s="14">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>1.0001951854261548</v>
+        <v>1.0002168726957277</v>
       </c>
       <c r="M11" s="8">
         <v>102242</v>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>17893</v>
+        <v>17896</v>
       </c>
       <c r="P11" s="14">
-        <v>102359</v>
+        <v>102362</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>1.0011443438117407</v>
+        <v>1.0011736859607598</v>
       </c>
       <c r="R11" s="8">
         <v>44890</v>
@@ -1360,14 +1360,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>8654</v>
+        <v>8657</v>
       </c>
       <c r="U11" s="14">
-        <v>45091</v>
+        <v>45094</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>1.0044776119402985</v>
+        <v>1.0045444419692582</v>
       </c>
       <c r="W11" s="8">
         <v>46425</v>
@@ -1377,14 +1377,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8811</v>
+        <v>8815</v>
       </c>
       <c r="Z11" s="14">
-        <v>46015</v>
+        <v>46019</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.99116855142703286</v>
+        <v>0.99125471190091541</v>
       </c>
       <c r="AB11" s="8">
         <v>103964</v>
@@ -1394,14 +1394,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>17237</v>
+        <v>17247</v>
       </c>
       <c r="AE11" s="14">
-        <v>104122</v>
+        <v>104132</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>1.0015197568389058</v>
+        <v>1.0016159439806087</v>
       </c>
       <c r="AG11" s="8">
         <v>45569</v>
@@ -1411,14 +1411,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>8674</v>
+        <v>8682</v>
       </c>
       <c r="AJ11" s="14">
-        <v>45663</v>
+        <v>45671</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>1.0020628058548575</v>
+        <v>1.0022383637999517</v>
       </c>
       <c r="AL11" s="8">
         <v>46951</v>
@@ -1428,14 +1428,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>7773</v>
+        <v>7782</v>
       </c>
       <c r="AO11" s="14">
-        <v>46358</v>
+        <v>46367</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.98736981107963617</v>
+        <v>0.98756150028753387</v>
       </c>
       <c r="AQ11" s="8">
         <v>105644</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>15115</v>
+        <v>15131</v>
       </c>
       <c r="AT11" s="14">
-        <v>105829</v>
+        <v>105845</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>1.0017511642876074</v>
+        <v>1.0019026163341032</v>
       </c>
       <c r="AV11" s="8">
         <v>46072</v>
@@ -1462,14 +1462,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>7540</v>
+        <v>7550</v>
       </c>
       <c r="AY11" s="14">
-        <v>46190</v>
+        <v>46200</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>1.0025612085431499</v>
+        <v>1.0027782601146031</v>
       </c>
       <c r="BA11" s="8">
         <v>47252</v>
@@ -1479,14 +1479,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>7175</v>
+        <v>7186</v>
       </c>
       <c r="BD11" s="14">
-        <v>46990</v>
+        <v>47001</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.99445526115296712</v>
+        <v>0.99468805553204098</v>
       </c>
       <c r="BF11" s="8">
         <v>107665</v>
@@ -1496,14 +1496,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>19603</v>
+        <v>19639</v>
       </c>
       <c r="BI11" s="14">
-        <v>107493</v>
+        <v>107529</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.99840245205034128</v>
+        <v>0.9987368225514327</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>24305</v>
+        <v>24309</v>
       </c>
       <c r="F12" s="14">
-        <v>165516</v>
+        <v>165520</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.99726456588540102</v>
+        <v>0.99728866662649873</v>
       </c>
       <c r="H12" s="8">
         <v>170538</v>
@@ -1538,14 +1538,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>24742</v>
+        <v>24748</v>
       </c>
       <c r="K12" s="14">
-        <v>168567</v>
+        <v>168573</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.98844245857228297</v>
+        <v>0.98847764134679661</v>
       </c>
       <c r="M12" s="8">
         <v>344875</v>
@@ -1555,14 +1555,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>54189</v>
+        <v>54200</v>
       </c>
       <c r="P12" s="14">
-        <v>343191</v>
+        <v>343202</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.99511707140268213</v>
+        <v>0.99514896701703515</v>
       </c>
       <c r="R12" s="8">
         <v>167705</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>27001</v>
+        <v>27008</v>
       </c>
       <c r="U12" s="14">
-        <v>167143</v>
+        <v>167150</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.99664887749321729</v>
+        <v>0.99669061745326615</v>
       </c>
       <c r="W12" s="8">
         <v>171864</v>
@@ -1589,14 +1589,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>27600</v>
+        <v>27609</v>
       </c>
       <c r="Z12" s="14">
-        <v>170058</v>
+        <v>170067</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.98949169110459434</v>
+        <v>0.98954405809244517</v>
       </c>
       <c r="AB12" s="8">
         <v>349048</v>
@@ -1606,14 +1606,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>58533</v>
+        <v>58554</v>
       </c>
       <c r="AE12" s="14">
-        <v>348002</v>
+        <v>348023</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.997003277486191</v>
+        <v>0.99706344113130574</v>
       </c>
       <c r="AG12" s="8">
         <v>170526</v>
@@ -1623,14 +1623,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>27727</v>
+        <v>27740</v>
       </c>
       <c r="AJ12" s="14">
-        <v>170171</v>
+        <v>170184</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.99791820602136916</v>
+        <v>0.99799444073044574</v>
       </c>
       <c r="AL12" s="8">
         <v>174892</v>
@@ -1640,14 +1640,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>25062</v>
+        <v>25078</v>
       </c>
       <c r="AO12" s="14">
-        <v>172388</v>
+        <v>172404</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.98568259268577174</v>
+        <v>0.98577407771653358</v>
       </c>
       <c r="AQ12" s="8">
         <v>353589</v>
@@ -1657,14 +1657,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>50857</v>
+        <v>50886</v>
       </c>
       <c r="AT12" s="14">
-        <v>352767</v>
+        <v>352796</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.99767526704733467</v>
+        <v>0.99775728317340184</v>
       </c>
       <c r="AV12" s="8">
         <v>172980</v>
@@ -1674,14 +1674,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>24610</v>
+        <v>24625</v>
       </c>
       <c r="AY12" s="14">
-        <v>172327</v>
+        <v>172342</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.99622499710949242</v>
+        <v>0.99631171233668636</v>
       </c>
       <c r="BA12" s="8">
         <v>177212</v>
@@ -1691,14 +1691,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>24016</v>
+        <v>24036</v>
       </c>
       <c r="BD12" s="14">
-        <v>174767</v>
+        <v>174787</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.98620296593910117</v>
+        <v>0.98631582511342342</v>
       </c>
       <c r="BF12" s="8">
         <v>359260</v>
@@ -1708,14 +1708,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>65655</v>
+        <v>65701</v>
       </c>
       <c r="BI12" s="14">
-        <v>357361</v>
+        <v>357407</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.99471413461003177</v>
+        <v>0.99484217558314314</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1733,14 +1733,14 @@
       </c>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="F13" s="14">
-        <v>16598</v>
+        <v>16599</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>1.0054519021080688</v>
+        <v>1.0055124787981584</v>
       </c>
       <c r="H13" s="8">
         <v>16836</v>
@@ -1750,14 +1750,14 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" si="2"/>
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="K13" s="14">
-        <v>16793</v>
+        <v>16794</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="3"/>
-        <v>0.99744594915656926</v>
+        <v>0.9975053456878118</v>
       </c>
       <c r="M13" s="8">
         <v>27790</v>
@@ -1767,14 +1767,14 @@
       </c>
       <c r="O13" s="4">
         <f t="shared" si="4"/>
-        <v>4527</v>
+        <v>4529</v>
       </c>
       <c r="P13" s="14">
-        <v>27814</v>
+        <v>27816</v>
       </c>
       <c r="Q13" s="5">
         <f t="shared" si="5"/>
-        <v>1.0008636200071968</v>
+        <v>1.0009355883411299</v>
       </c>
       <c r="R13" s="8">
         <v>16731</v>
@@ -1920,14 +1920,14 @@
       </c>
       <c r="BH13" s="4">
         <f t="shared" si="22"/>
-        <v>4903</v>
+        <v>4904</v>
       </c>
       <c r="BI13" s="14">
-        <v>28646</v>
+        <v>28647</v>
       </c>
       <c r="BJ13" s="5">
         <f t="shared" si="23"/>
-        <v>1.0025197732204101</v>
+        <v>1.0025547700706936</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -1945,14 +1945,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>18146</v>
+        <v>18157</v>
       </c>
       <c r="F14" s="14">
-        <v>85305</v>
+        <v>85316</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.99908646920347144</v>
+        <v>0.99921530046964857</v>
       </c>
       <c r="H14" s="8">
         <v>88261</v>
@@ -1962,14 +1962,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18257</v>
+        <v>18270</v>
       </c>
       <c r="K14" s="14">
-        <v>87126</v>
+        <v>87139</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.98714041309298561</v>
+        <v>0.98728770351570905</v>
       </c>
       <c r="M14" s="8">
         <v>157146</v>
@@ -1979,14 +1979,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>32083</v>
+        <v>32103</v>
       </c>
       <c r="P14" s="14">
-        <v>155484</v>
+        <v>155504</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.98942384788667859</v>
+        <v>0.98955111806854767</v>
       </c>
       <c r="R14" s="8">
         <v>86469</v>
@@ -1996,14 +1996,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18327</v>
+        <v>18341</v>
       </c>
       <c r="U14" s="14">
-        <v>85392</v>
+        <v>85406</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.98754466918780137</v>
+        <v>0.98770657692352171</v>
       </c>
       <c r="W14" s="8">
         <v>88169</v>
@@ -2013,14 +2013,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>17838</v>
+        <v>17855</v>
       </c>
       <c r="Z14" s="14">
-        <v>86546</v>
+        <v>86563</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.98159216958341367</v>
+        <v>0.98178498111581169</v>
       </c>
       <c r="AB14" s="8">
         <v>157930</v>
@@ -2030,14 +2030,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>33720</v>
+        <v>33743</v>
       </c>
       <c r="AE14" s="14">
-        <v>157145</v>
+        <v>157168</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.99502944342430188</v>
+        <v>0.9951750775660102</v>
       </c>
       <c r="AG14" s="8">
         <v>87312</v>
@@ -2047,14 +2047,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>19573</v>
+        <v>19589</v>
       </c>
       <c r="AJ14" s="14">
-        <v>86905</v>
+        <v>86921</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.99533855598314092</v>
+        <v>0.9955218068535826</v>
       </c>
       <c r="AL14" s="8">
         <v>89337</v>
@@ -2064,14 +2064,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>16967</v>
+        <v>16985</v>
       </c>
       <c r="AO14" s="14">
-        <v>87907</v>
+        <v>87925</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.98399319430918886</v>
+        <v>0.98419467857662557</v>
       </c>
       <c r="AQ14" s="8">
         <v>160173</v>
@@ -2081,14 +2081,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>29813</v>
+        <v>29850</v>
       </c>
       <c r="AT14" s="14">
-        <v>160254</v>
+        <v>160291</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>1.0005057032084059</v>
+        <v>1.0007367034394061</v>
       </c>
       <c r="AV14" s="8">
         <v>88523</v>
@@ -2098,14 +2098,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>17201</v>
+        <v>17220</v>
       </c>
       <c r="AY14" s="14">
-        <v>88561</v>
+        <v>88580</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>1.000429266970166</v>
+        <v>1.000643900455249</v>
       </c>
       <c r="BA14" s="8">
         <v>90782</v>
@@ -2115,14 +2115,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>16163</v>
+        <v>16185</v>
       </c>
       <c r="BD14" s="14">
-        <v>89744</v>
+        <v>89766</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.9885660152893746</v>
+        <v>0.98880835407900247</v>
       </c>
       <c r="BF14" s="8">
         <v>163900</v>
@@ -2132,14 +2132,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>39428</v>
+        <v>39478</v>
       </c>
       <c r="BI14" s="14">
-        <v>162788</v>
+        <v>162838</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.9932153752287981</v>
+        <v>0.99352043929225142</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2157,14 +2157,14 @@
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
-        <v>48199</v>
+        <v>48200</v>
       </c>
       <c r="F15" s="14">
-        <v>282994</v>
+        <v>282995</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.99553932639607123</v>
+        <v>0.99554284427746231</v>
       </c>
       <c r="H15" s="8">
         <v>290906</v>
@@ -2174,14 +2174,14 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" si="2"/>
-        <v>47674</v>
+        <v>47676</v>
       </c>
       <c r="K15" s="14">
-        <v>287270</v>
+        <v>287272</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
-        <v>0.98750111719937028</v>
+        <v>0.98750799227241792</v>
       </c>
       <c r="M15" s="8">
         <v>490131</v>
@@ -2191,14 +2191,14 @@
       </c>
       <c r="O15" s="4">
         <f t="shared" si="4"/>
-        <v>81155</v>
+        <v>81158</v>
       </c>
       <c r="P15" s="14">
-        <v>485409</v>
+        <v>485412</v>
       </c>
       <c r="Q15" s="5">
         <f t="shared" si="5"/>
-        <v>0.99036584096904701</v>
+        <v>0.9903719617816461</v>
       </c>
       <c r="R15" s="8">
         <v>287010</v>
@@ -2208,14 +2208,14 @@
       </c>
       <c r="T15" s="4">
         <f t="shared" si="6"/>
-        <v>51979</v>
+        <v>51980</v>
       </c>
       <c r="U15" s="14">
-        <v>284136</v>
+        <v>284137</v>
       </c>
       <c r="V15" s="5">
         <f t="shared" si="7"/>
-        <v>0.98998641162328838</v>
+        <v>0.98998989582244523</v>
       </c>
       <c r="W15" s="8">
         <v>292338</v>
@@ -2225,14 +2225,14 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="8"/>
-        <v>49399</v>
+        <v>49401</v>
       </c>
       <c r="Z15" s="14">
-        <v>287669</v>
+        <v>287671</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="9"/>
-        <v>0.98402876122844107</v>
+        <v>0.98403560262435952</v>
       </c>
       <c r="AB15" s="8">
         <v>495688</v>
@@ -2242,14 +2242,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>86714</v>
+        <v>86719</v>
       </c>
       <c r="AE15" s="14">
-        <v>491006</v>
+        <v>491011</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.99055454237342844</v>
+        <v>0.99056462936363199</v>
       </c>
       <c r="AG15" s="8">
         <v>292071</v>
@@ -2259,14 +2259,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>54933</v>
+        <v>54939</v>
       </c>
       <c r="AJ15" s="14">
-        <v>289851</v>
+        <v>289857</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.99239910843596246</v>
+        <v>0.99241965138613553</v>
       </c>
       <c r="AL15" s="8">
         <v>298411</v>
@@ -2276,14 +2276,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>47355</v>
+        <v>47361</v>
       </c>
       <c r="AO15" s="14">
-        <v>293449</v>
+        <v>293455</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>0.98337192663809314</v>
+        <v>0.98339203313550771</v>
       </c>
       <c r="AQ15" s="8">
         <v>502913</v>
@@ -2293,14 +2293,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>75279</v>
+        <v>75295</v>
       </c>
       <c r="AT15" s="14">
-        <v>498838</v>
+        <v>498854</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.99189720687275929</v>
+        <v>0.9919290215206209</v>
       </c>
       <c r="AV15" s="8">
         <v>298012</v>
@@ -2310,14 +2310,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>47941</v>
+        <v>47948</v>
       </c>
       <c r="AY15" s="14">
-        <v>295208</v>
+        <v>295215</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>0.99059098291343972</v>
+        <v>0.99061447190046037</v>
       </c>
       <c r="BA15" s="8">
         <v>303376</v>
@@ -2327,14 +2327,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>45499</v>
+        <v>45511</v>
       </c>
       <c r="BD15" s="14">
-        <v>299077</v>
+        <v>299089</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.98582946574547758</v>
+        <v>0.98586902062127524</v>
       </c>
       <c r="BF15" s="8">
         <v>511329</v>
@@ -2344,14 +2344,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>92268</v>
+        <v>92291</v>
       </c>
       <c r="BI15" s="14">
-        <v>506534</v>
+        <v>506557</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.99062247594014807</v>
+        <v>0.99066745676462709</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2369,14 +2369,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>73082</v>
+        <v>73101</v>
       </c>
       <c r="F16" s="14">
-        <v>427849</v>
+        <v>427868</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.99353048405262001</v>
+        <v>0.99357460494386196</v>
       </c>
       <c r="H16" s="8">
         <v>441093</v>
@@ -2386,14 +2386,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>74271</v>
+        <v>74301</v>
       </c>
       <c r="K16" s="14">
-        <v>432656</v>
+        <v>432686</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.98087251441306034</v>
+        <v>0.98094052728109493</v>
       </c>
       <c r="M16" s="8">
         <v>754668</v>
@@ -2403,14 +2403,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>125309</v>
+        <v>125371</v>
       </c>
       <c r="P16" s="14">
-        <v>749279</v>
+        <v>749341</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.99285911155633999</v>
+        <v>0.99294126688822104</v>
       </c>
       <c r="R16" s="8">
         <v>429537</v>
@@ -2420,14 +2420,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>78623</v>
+        <v>78662</v>
       </c>
       <c r="U16" s="14">
-        <v>424873</v>
+        <v>424912</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.98914179686499648</v>
+        <v>0.98923259230287497</v>
       </c>
       <c r="W16" s="8">
         <v>433887</v>
@@ -2437,14 +2437,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>75965</v>
+        <v>76001</v>
       </c>
       <c r="Z16" s="14">
-        <v>427091</v>
+        <v>427127</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.98433693565375313</v>
+        <v>0.98441990656553435</v>
       </c>
       <c r="AB16" s="8">
         <v>753330</v>
@@ -2454,14 +2454,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>135792</v>
+        <v>135871</v>
       </c>
       <c r="AE16" s="14">
-        <v>749997</v>
+        <v>750076</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.99557564414001831</v>
+        <v>0.99568051186067197</v>
       </c>
       <c r="AG16" s="8">
         <v>431686</v>
@@ -2471,14 +2471,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>82714</v>
+        <v>82759</v>
       </c>
       <c r="AJ16" s="14">
-        <v>426892</v>
+        <v>426937</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.98889470587417705</v>
+        <v>0.98899894830965096</v>
       </c>
       <c r="AL16" s="8">
         <v>438911</v>
@@ -2488,14 +2488,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>73950</v>
+        <v>73998</v>
       </c>
       <c r="AO16" s="14">
-        <v>430531</v>
+        <v>430579</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.98090729099976992</v>
+        <v>0.9810166525787688</v>
       </c>
       <c r="AQ16" s="8">
         <v>759875</v>
@@ -2505,14 +2505,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>119845</v>
+        <v>119968</v>
       </c>
       <c r="AT16" s="14">
-        <v>756740</v>
+        <v>756863</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.99587432143444643</v>
+        <v>0.99603619016285572</v>
       </c>
       <c r="AV16" s="8">
         <v>437477</v>
@@ -2522,14 +2522,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>69787</v>
+        <v>69851</v>
       </c>
       <c r="AY16" s="14">
-        <v>432264</v>
+        <v>432328</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.98808394498453633</v>
+        <v>0.98823023838967539</v>
       </c>
       <c r="BA16" s="8">
         <v>445887</v>
@@ -2539,14 +2539,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>70416</v>
+        <v>70489</v>
       </c>
       <c r="BD16" s="14">
-        <v>437081</v>
+        <v>437154</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98025060160982491</v>
+        <v>0.98041432022014541</v>
       </c>
       <c r="BF16" s="8">
         <v>770088</v>
@@ -2556,14 +2556,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>139183</v>
+        <v>139349</v>
       </c>
       <c r="BI16" s="14">
-        <v>762738</v>
+        <v>762904</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.99045563623897526</v>
+        <v>0.99067119601915621</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2581,14 +2581,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>52674</v>
+        <v>52698</v>
       </c>
       <c r="F17" s="14">
-        <v>303692</v>
+        <v>303716</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>1.0036949638766053</v>
+        <v>1.003774283315817</v>
       </c>
       <c r="H17" s="8">
         <v>314962</v>
@@ -2598,14 +2598,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>52663</v>
+        <v>52682</v>
       </c>
       <c r="K17" s="14">
-        <v>311290</v>
+        <v>311309</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98834145071468937</v>
+        <v>0.98840177545227681</v>
       </c>
       <c r="M17" s="8">
         <v>695415</v>
@@ -2615,14 +2615,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>119246</v>
+        <v>119289</v>
       </c>
       <c r="P17" s="14">
-        <v>689907</v>
+        <v>689950</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.99207954962144906</v>
+        <v>0.99214138320283574</v>
       </c>
       <c r="R17" s="8">
         <v>305324</v>
@@ -2632,14 +2632,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>55791</v>
+        <v>55815</v>
       </c>
       <c r="U17" s="14">
-        <v>304459</v>
+        <v>304483</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>0.99716694396771954</v>
+        <v>0.99724554899058049</v>
       </c>
       <c r="W17" s="8">
         <v>316716</v>
@@ -2649,14 +2649,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>55774</v>
+        <v>55803</v>
       </c>
       <c r="Z17" s="14">
-        <v>310486</v>
+        <v>310515</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.9803293802649693</v>
+        <v>0.98042094494752396</v>
       </c>
       <c r="AB17" s="8">
         <v>703511</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>130700</v>
+        <v>130776</v>
       </c>
       <c r="AE17" s="14">
-        <v>697984</v>
+        <v>698060</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.99214369071698949</v>
+        <v>0.99225172030003794</v>
       </c>
       <c r="AG17" s="8">
         <v>311084</v>
@@ -2683,14 +2683,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>62993</v>
+        <v>63023</v>
       </c>
       <c r="AJ17" s="14">
-        <v>310672</v>
+        <v>310702</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.99867559887361612</v>
+        <v>0.99877203584883822</v>
       </c>
       <c r="AL17" s="8">
         <v>323550</v>
@@ -2700,14 +2700,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>52053</v>
+        <v>52091</v>
       </c>
       <c r="AO17" s="14">
-        <v>317124</v>
+        <v>317162</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.98013908205841449</v>
+        <v>0.98025652912996442</v>
       </c>
       <c r="AQ17" s="8">
         <v>714257</v>
@@ -2717,14 +2717,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>112751</v>
+        <v>112841</v>
       </c>
       <c r="AT17" s="14">
-        <v>712699</v>
+        <v>712789</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.99781871231223496</v>
+        <v>0.99794471737763857</v>
       </c>
       <c r="AV17" s="8">
         <v>316308</v>
@@ -2734,14 +2734,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>51051</v>
+        <v>51096</v>
       </c>
       <c r="AY17" s="14">
-        <v>316383</v>
+        <v>316428</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>1.0002371106642893</v>
+        <v>1.0003793770628628</v>
       </c>
       <c r="BA17" s="8">
         <v>328067</v>
@@ -2751,14 +2751,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>47093</v>
+        <v>47144</v>
       </c>
       <c r="BD17" s="14">
-        <v>322647</v>
+        <v>322698</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.98347898447573212</v>
+        <v>0.98363444052586824</v>
       </c>
       <c r="BF17" s="8">
         <v>726752</v>
@@ -2768,14 +2768,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>143693</v>
+        <v>143821</v>
       </c>
       <c r="BI17" s="14">
-        <v>723745</v>
+        <v>723873</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.99586241248734098</v>
+        <v>0.996038538593633</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2793,14 +2793,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>166603</v>
+        <v>166631</v>
       </c>
       <c r="F18" s="14">
-        <v>919234</v>
+        <v>919262</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99782683264657479</v>
+        <v>0.99785722659557374</v>
       </c>
       <c r="H18" s="8">
         <v>943261</v>
@@ -2810,14 +2810,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>163796</v>
+        <v>163833</v>
       </c>
       <c r="K18" s="14">
-        <v>933224</v>
+        <v>933261</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.98935925475557662</v>
+        <v>0.98939848037817746</v>
       </c>
       <c r="M18" s="8">
         <v>1440086</v>
@@ -2827,14 +2827,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>251661</v>
+        <v>251730</v>
       </c>
       <c r="P18" s="14">
-        <v>1426719</v>
+        <v>1426788</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.99071791545782684</v>
+        <v>0.99076582926297452</v>
       </c>
       <c r="R18" s="8">
         <v>938677</v>
@@ -2844,14 +2844,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>170610</v>
+        <v>170662</v>
       </c>
       <c r="U18" s="14">
-        <v>929278</v>
+        <v>929330</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.98998697102411159</v>
+        <v>0.99004236814154389</v>
       </c>
       <c r="W18" s="8">
         <v>958009</v>
@@ -2861,14 +2861,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>169000</v>
+        <v>169064</v>
       </c>
       <c r="Z18" s="14">
-        <v>943571</v>
+        <v>943635</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.98492916037323242</v>
+        <v>0.98499596559113745</v>
       </c>
       <c r="AB18" s="8">
         <v>1463397</v>
@@ -2878,14 +2878,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>274053</v>
+        <v>274167</v>
       </c>
       <c r="AE18" s="14">
-        <v>1451045</v>
+        <v>1451159</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.99155936495701436</v>
+        <v>0.99163726589572077</v>
       </c>
       <c r="AG18" s="8">
         <v>959088</v>
@@ -2895,14 +2895,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>195010</v>
+        <v>195097</v>
       </c>
       <c r="AJ18" s="14">
-        <v>951863</v>
+        <v>951950</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.99246680179503866</v>
+        <v>0.99255751297065542</v>
       </c>
       <c r="AL18" s="8">
         <v>980581</v>
@@ -2912,14 +2912,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>166693</v>
+        <v>166785</v>
       </c>
       <c r="AO18" s="14">
-        <v>964235</v>
+        <v>964327</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.98333029091936308</v>
+        <v>0.98342411284738329</v>
       </c>
       <c r="AQ18" s="8">
         <v>1490329</v>
@@ -2929,14 +2929,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>245896</v>
+        <v>246061</v>
       </c>
       <c r="AT18" s="14">
-        <v>1482372</v>
+        <v>1482537</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.99466091044326455</v>
+        <v>0.99477162425209464</v>
       </c>
       <c r="AV18" s="8">
         <v>983291</v>
@@ -2946,14 +2946,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>169992</v>
+        <v>170108</v>
       </c>
       <c r="AY18" s="14">
-        <v>975748</v>
+        <v>975864</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.99232882229167152</v>
+        <v>0.99244679347212572</v>
       </c>
       <c r="BA18" s="8">
         <v>1002255</v>
@@ -2963,14 +2963,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>160485</v>
+        <v>160619</v>
       </c>
       <c r="BD18" s="14">
-        <v>988086</v>
+        <v>988220</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.98586287920738735</v>
+        <v>0.98599657771724758</v>
       </c>
       <c r="BF18" s="8">
         <v>1522890</v>
@@ -2980,14 +2980,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>329000</v>
+        <v>329235</v>
       </c>
       <c r="BI18" s="14">
-        <v>1508741</v>
+        <v>1508976</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.99070911227994141</v>
+        <v>0.99086342414750905</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3005,14 +3005,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>63713</v>
+        <v>63737</v>
       </c>
       <c r="F19" s="14">
-        <v>271456</v>
+        <v>271480</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.98641327058994532</v>
+        <v>0.98650048147677105</v>
       </c>
       <c r="H19" s="8">
         <v>285702</v>
@@ -3022,14 +3022,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>60423</v>
+        <v>60450</v>
       </c>
       <c r="K19" s="14">
-        <v>277185</v>
+        <v>277212</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.97018921813637982</v>
+        <v>0.97028372220005465</v>
       </c>
       <c r="M19" s="8">
         <v>479092</v>
@@ -3039,14 +3039,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>93724</v>
+        <v>93773</v>
       </c>
       <c r="P19" s="14">
-        <v>468629</v>
+        <v>468678</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.97816077079141373</v>
+        <v>0.97826304759837357</v>
       </c>
       <c r="R19" s="8">
         <v>279649</v>
@@ -3056,14 +3056,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>57702</v>
+        <v>57739</v>
       </c>
       <c r="U19" s="14">
-        <v>272746</v>
+        <v>272783</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.97531548476840613</v>
+        <v>0.97544779348397459</v>
       </c>
       <c r="W19" s="8">
         <v>287758</v>
@@ -3073,14 +3073,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>59171</v>
+        <v>59210</v>
       </c>
       <c r="Z19" s="14">
-        <v>276591</v>
+        <v>276630</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.9611930858568658</v>
+        <v>0.96132861640684186</v>
       </c>
       <c r="AB19" s="8">
         <v>485015</v>
@@ -3090,14 +3090,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>101685</v>
+        <v>101764</v>
       </c>
       <c r="AE19" s="14">
-        <v>474871</v>
+        <v>474950</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.97908518293248659</v>
+        <v>0.97924806449285073</v>
       </c>
       <c r="AG19" s="8">
         <v>283525</v>
@@ -3107,14 +3107,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>74539</v>
+        <v>74591</v>
       </c>
       <c r="AJ19" s="14">
-        <v>276642</v>
+        <v>276694</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.97572348117449959</v>
+        <v>0.97590688651794377</v>
       </c>
       <c r="AL19" s="8">
         <v>295027</v>
@@ -3124,14 +3124,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>58000</v>
+        <v>58060</v>
       </c>
       <c r="AO19" s="14">
-        <v>282078</v>
+        <v>282138</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.95610910187881104</v>
+        <v>0.95631247309568279</v>
       </c>
       <c r="AQ19" s="8">
         <v>494059</v>
@@ -3141,14 +3141,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>91447</v>
+        <v>91547</v>
       </c>
       <c r="AT19" s="14">
-        <v>486235</v>
+        <v>486335</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.98416383468371182</v>
+        <v>0.98436623965963577</v>
       </c>
       <c r="AV19" s="8">
         <v>287237</v>
@@ -3158,14 +3158,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>56558</v>
+        <v>56617</v>
       </c>
       <c r="AY19" s="14">
-        <v>283308</v>
+        <v>283367</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.98632140009817681</v>
+        <v>0.98652680539067039</v>
       </c>
       <c r="BA19" s="8">
         <v>298081</v>
@@ -3175,14 +3175,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>54904</v>
+        <v>54972</v>
       </c>
       <c r="BD19" s="14">
-        <v>287415</v>
+        <v>287483</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.96421777973101275</v>
+        <v>0.96444590564309696</v>
       </c>
       <c r="BF19" s="8">
         <v>503654</v>
@@ -3192,14 +3192,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>132127</v>
+        <v>132271</v>
       </c>
       <c r="BI19" s="14">
-        <v>492523</v>
+        <v>492667</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.97789951037815648</v>
+        <v>0.97818542094374317</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3217,14 +3217,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="F20" s="14">
-        <v>5799</v>
+        <v>5803</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>1.0274627923458539</v>
+        <v>1.0281715095676824</v>
       </c>
       <c r="H20" s="8">
         <v>5914</v>
@@ -3234,14 +3234,14 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="K20" s="14">
-        <v>5957</v>
+        <v>5961</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>1.0072708826513359</v>
+        <v>1.0079472438282042</v>
       </c>
       <c r="M20" s="8">
         <v>9037</v>
@@ -3251,14 +3251,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>2199</v>
+        <v>2207</v>
       </c>
       <c r="P20" s="14">
-        <v>9269</v>
+        <v>9277</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>1.0256722363616244</v>
+        <v>1.0265574858913356</v>
       </c>
       <c r="R20" s="8">
         <v>5910</v>
@@ -3268,14 +3268,14 @@
       </c>
       <c r="T20" s="4">
         <f t="shared" si="6"/>
-        <v>1506</v>
+        <v>1512</v>
       </c>
       <c r="U20" s="14">
-        <v>6031</v>
+        <v>6037</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="7"/>
-        <v>1.0204737732656515</v>
+        <v>1.0214890016920475</v>
       </c>
       <c r="W20" s="8">
         <v>6115</v>
@@ -3285,14 +3285,14 @@
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="8"/>
-        <v>1487</v>
+        <v>1493</v>
       </c>
       <c r="Z20" s="14">
-        <v>6142</v>
+        <v>6148</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="9"/>
-        <v>1.0044153720359772</v>
+        <v>1.0053965658217499</v>
       </c>
       <c r="AB20" s="8">
         <v>9431</v>
@@ -3302,14 +3302,14 @@
       </c>
       <c r="AD20" s="4">
         <f t="shared" si="10"/>
-        <v>2317</v>
+        <v>2327</v>
       </c>
       <c r="AE20" s="14">
-        <v>9538</v>
+        <v>9548</v>
       </c>
       <c r="AF20" s="5">
         <f t="shared" si="11"/>
-        <v>1.011345562506627</v>
+        <v>1.0124058954511717</v>
       </c>
       <c r="AG20" s="8">
         <v>6099</v>
@@ -3319,14 +3319,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1753</v>
+        <v>1759</v>
       </c>
       <c r="AJ20" s="14">
-        <v>6150</v>
+        <v>6156</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>1.0083620265617315</v>
+        <v>1.0093457943925233</v>
       </c>
       <c r="AL20" s="8">
         <v>6250</v>
@@ -3336,14 +3336,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1502</v>
+        <v>1507</v>
       </c>
       <c r="AO20" s="14">
-        <v>6239</v>
+        <v>6244</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.99824000000000002</v>
+        <v>0.99904000000000004</v>
       </c>
       <c r="AQ20" s="8">
         <v>9632</v>
@@ -3353,14 +3353,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2349</v>
+        <v>2357</v>
       </c>
       <c r="AT20" s="14">
-        <v>9721</v>
+        <v>9729</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>1.0092400332225913</v>
+        <v>1.0100705980066444</v>
       </c>
       <c r="AV20" s="8">
         <v>6297</v>
@@ -3370,14 +3370,14 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>1658</v>
+        <v>1665</v>
       </c>
       <c r="AY20" s="14">
-        <v>6261</v>
+        <v>6268</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>0.99428299190090519</v>
+        <v>0.99539463236461811</v>
       </c>
       <c r="BA20" s="8">
         <v>6366</v>
@@ -3387,14 +3387,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1683</v>
+        <v>1690</v>
       </c>
       <c r="BD20" s="14">
-        <v>6291</v>
+        <v>6298</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>0.9882186616399623</v>
+        <v>0.98931825322023248</v>
       </c>
       <c r="BF20" s="8">
         <v>9853</v>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>3235</v>
+        <v>3245</v>
       </c>
       <c r="BI20" s="14">
-        <v>9870</v>
+        <v>9880</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>1.0017253628336547</v>
+        <v>1.0027402821475693</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3429,14 +3429,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>3690</v>
+        <v>3692</v>
       </c>
       <c r="F21" s="14">
-        <v>9824</v>
+        <v>9826</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>1.026434019433706</v>
+        <v>1.0266429840142095</v>
       </c>
       <c r="H21" s="8">
         <v>10057</v>
@@ -3446,14 +3446,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3488</v>
+        <v>3490</v>
       </c>
       <c r="K21" s="14">
-        <v>9967</v>
+        <v>9969</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.99105100924729039</v>
+        <v>0.99124987570846179</v>
       </c>
       <c r="M21" s="8">
         <v>12982</v>
@@ -3463,14 +3463,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>4284</v>
+        <v>4291</v>
       </c>
       <c r="P21" s="14">
-        <v>13225</v>
+        <v>13232</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>1.0187182252349407</v>
+        <v>1.0192574333692805</v>
       </c>
       <c r="R21" s="8">
         <v>9811</v>
@@ -3480,14 +3480,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3465</v>
+        <v>3468</v>
       </c>
       <c r="U21" s="14">
-        <v>10026</v>
+        <v>10029</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>1.0219141779635104</v>
+        <v>1.0222199571909081</v>
       </c>
       <c r="W21" s="8">
         <v>10152</v>
@@ -3497,14 +3497,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3282</v>
+        <v>3288</v>
       </c>
       <c r="Z21" s="14">
-        <v>10168</v>
+        <v>10174</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>1.0015760441292356</v>
+        <v>1.0021670606776989</v>
       </c>
       <c r="AB21" s="8">
         <v>13231</v>
@@ -3514,14 +3514,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4336</v>
+        <v>4348</v>
       </c>
       <c r="AE21" s="14">
-        <v>13546</v>
+        <v>13558</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>1.0238077242838788</v>
+        <v>1.024714685208979</v>
       </c>
       <c r="AG21" s="8">
         <v>10040</v>
@@ -3531,14 +3531,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3810</v>
+        <v>3816</v>
       </c>
       <c r="AJ21" s="14">
-        <v>10238</v>
+        <v>10244</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>1.0197211155378485</v>
+        <v>1.0203187250996015</v>
       </c>
       <c r="AL21" s="8">
         <v>10211</v>
@@ -3548,14 +3548,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3442</v>
+        <v>3448</v>
       </c>
       <c r="AO21" s="14">
-        <v>10389</v>
+        <v>10395</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>1.0174321809812947</v>
+        <v>1.0180197825874058</v>
       </c>
       <c r="AQ21" s="8">
         <v>13473</v>
@@ -3565,14 +3565,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4267</v>
+        <v>4281</v>
       </c>
       <c r="AT21" s="14">
-        <v>13870</v>
+        <v>13884</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>1.0294663400875825</v>
+        <v>1.0305054553551547</v>
       </c>
       <c r="AV21" s="8">
         <v>10213</v>
@@ -3582,14 +3582,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3510</v>
+        <v>3522</v>
       </c>
       <c r="AY21" s="14">
-        <v>10493</v>
+        <v>10505</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>1.0274160383824538</v>
+        <v>1.0285910114559875</v>
       </c>
       <c r="BA21" s="8">
         <v>10449</v>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="BD21" s="14">
-        <v>10615</v>
+        <v>10630</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>1.0158866877213131</v>
+        <v>1.0173222317925161</v>
       </c>
       <c r="BF21" s="8">
         <v>13925</v>
@@ -3616,14 +3616,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>6460</v>
+        <v>6485</v>
       </c>
       <c r="BI21" s="14">
-        <v>14287</v>
+        <v>14312</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>1.025996409335727</v>
+        <v>1.0277917414721724</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3641,14 +3641,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1826</v>
+        <v>1830</v>
       </c>
       <c r="F22" s="14">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>1.0100665692482547</v>
+        <v>1.0107160253287872</v>
       </c>
       <c r="H22" s="8">
         <v>6265</v>
@@ -3658,14 +3658,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1770</v>
+        <v>1775</v>
       </c>
       <c r="K22" s="14">
-        <v>6302</v>
+        <v>6307</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>1.005905826017558</v>
+        <v>1.0067039106145252</v>
       </c>
       <c r="M22" s="8">
         <v>7537</v>
@@ -3675,14 +3675,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>2035</v>
+        <v>2041</v>
       </c>
       <c r="P22" s="14">
-        <v>7589</v>
+        <v>7595</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>1.0068992968024413</v>
+        <v>1.0076953695104154</v>
       </c>
       <c r="R22" s="8">
         <v>6306</v>
@@ -3692,14 +3692,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1768</v>
+        <v>1775</v>
       </c>
       <c r="U22" s="14">
-        <v>6355</v>
+        <v>6362</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>1.0077703774183318</v>
+        <v>1.0088804313352362</v>
       </c>
       <c r="W22" s="8">
         <v>6435</v>
@@ -3709,14 +3709,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1757</v>
+        <v>1765</v>
       </c>
       <c r="Z22" s="14">
-        <v>6427</v>
+        <v>6435</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>0.99875679875679879</v>
+        <v>1</v>
       </c>
       <c r="AB22" s="8">
         <v>7668</v>
@@ -3726,14 +3726,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2036</v>
+        <v>2046</v>
       </c>
       <c r="AE22" s="14">
-        <v>7700</v>
+        <v>7710</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>1.0041731872717787</v>
+        <v>1.0054773082942097</v>
       </c>
       <c r="AG22" s="8">
         <v>6422</v>
@@ -3743,14 +3743,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1818</v>
+        <v>1828</v>
       </c>
       <c r="AJ22" s="14">
-        <v>6443</v>
+        <v>6453</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>1.0032700093428839</v>
+        <v>1.004827156649019</v>
       </c>
       <c r="AL22" s="8">
         <v>6508</v>
@@ -3760,14 +3760,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1622</v>
+        <v>1632</v>
       </c>
       <c r="AO22" s="14">
-        <v>6491</v>
+        <v>6501</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.99738783036263057</v>
+        <v>0.99892440073755373</v>
       </c>
       <c r="AQ22" s="8">
         <v>7781</v>
@@ -3777,14 +3777,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2083</v>
+        <v>2096</v>
       </c>
       <c r="AT22" s="14">
-        <v>7795</v>
+        <v>7808</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>1.0017992545945251</v>
+        <v>1.003469991003727</v>
       </c>
       <c r="AV22" s="8">
         <v>6603</v>
@@ -3794,14 +3794,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1635</v>
+        <v>1648</v>
       </c>
       <c r="AY22" s="14">
-        <v>6504</v>
+        <v>6517</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.98500681508405274</v>
+        <v>0.98697561714372251</v>
       </c>
       <c r="BA22" s="8">
         <v>6608</v>
@@ -3811,14 +3811,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1597</v>
+        <v>1609</v>
       </c>
       <c r="BD22" s="14">
-        <v>6545</v>
+        <v>6557</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>0.99046610169491522</v>
+        <v>0.99228208232445525</v>
       </c>
       <c r="BF22" s="8">
         <v>7906</v>
@@ -3828,14 +3828,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2436</v>
+        <v>2449</v>
       </c>
       <c r="BI22" s="14">
-        <v>7934</v>
+        <v>7947</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>1.0035416139640778</v>
+        <v>1.005185934733114</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3853,14 +3853,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>5976</v>
+        <v>5983</v>
       </c>
       <c r="F23" s="14">
-        <v>8463</v>
+        <v>8470</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.96170454545454542</v>
+        <v>0.96250000000000002</v>
       </c>
       <c r="H23" s="8">
         <v>8763</v>
@@ -3870,14 +3870,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>5139</v>
+        <v>5147</v>
       </c>
       <c r="K23" s="14">
-        <v>8491</v>
+        <v>8499</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.96896040168891928</v>
+        <v>0.96987333105100992</v>
       </c>
       <c r="M23" s="8">
         <v>10654</v>
@@ -3887,14 +3887,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>5534</v>
+        <v>5544</v>
       </c>
       <c r="P23" s="14">
-        <v>10466</v>
+        <v>10476</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.98235404542894689</v>
+        <v>0.98329266003379012</v>
       </c>
       <c r="R23" s="8">
         <v>8621</v>
@@ -3904,14 +3904,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>3741</v>
+        <v>3749</v>
       </c>
       <c r="U23" s="14">
-        <v>8385</v>
+        <v>8393</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.97262498550052201</v>
+        <v>0.97355295209372461</v>
       </c>
       <c r="W23" s="8">
         <v>8774</v>
@@ -3921,14 +3921,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>3688</v>
+        <v>3698</v>
       </c>
       <c r="Z23" s="14">
-        <v>8419</v>
+        <v>8429</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.9595395486665147</v>
+        <v>0.96067927968999312</v>
       </c>
       <c r="AB23" s="8">
         <v>10734</v>
@@ -3938,14 +3938,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3654</v>
+        <v>3663</v>
       </c>
       <c r="AE23" s="14">
-        <v>10542</v>
+        <v>10551</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.98211291224147568</v>
+        <v>0.98295136948015649</v>
       </c>
       <c r="AG23" s="8">
         <v>8589</v>
@@ -3955,14 +3955,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>3089</v>
+        <v>3098</v>
       </c>
       <c r="AJ23" s="14">
-        <v>8431</v>
+        <v>8440</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.98160437769239728</v>
+        <v>0.98265222959599485</v>
       </c>
       <c r="AL23" s="8">
         <v>8660</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2889</v>
+        <v>2899</v>
       </c>
       <c r="AO23" s="14">
-        <v>8491</v>
+        <v>8501</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.98048498845265586</v>
+        <v>0.98163972286374135</v>
       </c>
       <c r="AQ23" s="8">
         <v>10698</v>
@@ -3989,14 +3989,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3501</v>
+        <v>3514</v>
       </c>
       <c r="AT23" s="14">
-        <v>10720</v>
+        <v>10733</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>1.0020564591512433</v>
+        <v>1.0032716395587959</v>
       </c>
       <c r="AV23" s="8">
         <v>8445</v>
@@ -4006,14 +4006,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2784</v>
+        <v>2796</v>
       </c>
       <c r="AY23" s="14">
-        <v>8482</v>
+        <v>8494</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>1.0043812907045588</v>
+        <v>1.0058022498519834</v>
       </c>
       <c r="BA23" s="8">
         <v>8623</v>
@@ -4023,14 +4023,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2706</v>
+        <v>2718</v>
       </c>
       <c r="BD23" s="14">
-        <v>8529</v>
+        <v>8541</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.98909892148904088</v>
+        <v>0.99049054853299312</v>
       </c>
       <c r="BF23" s="8">
         <v>11023</v>
@@ -4040,14 +4040,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4216</v>
+        <v>4231</v>
       </c>
       <c r="BI23" s="14">
-        <v>10887</v>
+        <v>10902</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.98766216093622428</v>
+        <v>0.9890229520094348</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4082,14 +4082,14 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" si="2"/>
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="K24" s="14">
-        <v>5628</v>
+        <v>5629</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="3"/>
-        <v>0.96967608545830464</v>
+        <v>0.96984838042729149</v>
       </c>
       <c r="M24" s="8">
         <v>6771</v>
@@ -4133,14 +4133,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="Z24" s="14">
-        <v>5805</v>
+        <v>5807</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.97974683544303798</v>
+        <v>0.98008438818565402</v>
       </c>
       <c r="AB24" s="8">
         <v>6940</v>
@@ -4150,14 +4150,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="AE24" s="14">
-        <v>6799</v>
+        <v>6801</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.97968299711815565</v>
+        <v>0.979971181556196</v>
       </c>
       <c r="AG24" s="8">
         <v>6076</v>
@@ -4167,14 +4167,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="AJ24" s="14">
-        <v>5947</v>
+        <v>5950</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.97876892692560891</v>
+        <v>0.97926267281105994</v>
       </c>
       <c r="AL24" s="8">
         <v>6181</v>
@@ -4184,14 +4184,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="AO24" s="14">
-        <v>6007</v>
+        <v>6010</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.97184921533732405</v>
+        <v>0.97233457369357712</v>
       </c>
       <c r="AQ24" s="8">
         <v>6974</v>
@@ -4201,14 +4201,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="AT24" s="14">
-        <v>6895</v>
+        <v>6898</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.98867221106968739</v>
+        <v>0.98910238026957265</v>
       </c>
       <c r="AV24" s="8">
         <v>6124</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="AX24" s="4">
         <f t="shared" si="18"/>
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="AY24" s="14">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="AZ24" s="5">
         <f t="shared" si="19"/>
-        <v>0.98612018288700198</v>
+        <v>0.98677335075114303</v>
       </c>
       <c r="BA24" s="8">
         <v>6202</v>
@@ -4235,14 +4235,14 @@
       </c>
       <c r="BC24" s="4">
         <f t="shared" si="20"/>
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="BD24" s="14">
-        <v>6129</v>
+        <v>6134</v>
       </c>
       <c r="BE24" s="5">
         <f t="shared" si="21"/>
-        <v>0.98822960335375687</v>
+        <v>0.98903579490486937</v>
       </c>
       <c r="BF24" s="8">
         <v>7084</v>
@@ -4252,14 +4252,14 @@
       </c>
       <c r="BH24" s="4">
         <f t="shared" si="22"/>
-        <v>1744</v>
+        <v>1751</v>
       </c>
       <c r="BI24" s="14">
-        <v>7020</v>
+        <v>7027</v>
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="23"/>
-        <v>0.99096555618294746</v>
+        <v>0.99195369847543757</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4277,14 +4277,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>3661</v>
+        <v>3666</v>
       </c>
       <c r="F25" s="14">
-        <v>18483</v>
+        <v>18488</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>1.0108838328593306</v>
+        <v>1.0111572959964996</v>
       </c>
       <c r="H25" s="8">
         <v>18682</v>
@@ -4294,14 +4294,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>3634</v>
+        <v>3639</v>
       </c>
       <c r="K25" s="14">
-        <v>18844</v>
+        <v>18849</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>1.0086714484530563</v>
+        <v>1.0089390857509903</v>
       </c>
       <c r="M25" s="8">
         <v>25970</v>
@@ -4311,14 +4311,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>4721</v>
+        <v>4732</v>
       </c>
       <c r="P25" s="14">
-        <v>26222</v>
+        <v>26233</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>1.0097035040431266</v>
+        <v>1.0101270696958029</v>
       </c>
       <c r="R25" s="8">
         <v>18895</v>
@@ -4328,14 +4328,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>3728</v>
+        <v>3737</v>
       </c>
       <c r="U25" s="14">
-        <v>19051</v>
+        <v>19060</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>1.0082561524212754</v>
+        <v>1.0087324689071182</v>
       </c>
       <c r="W25" s="8">
         <v>19436</v>
@@ -4345,14 +4345,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>3758</v>
+        <v>3767</v>
       </c>
       <c r="Z25" s="14">
-        <v>19311</v>
+        <v>19320</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.99356863552171226</v>
+        <v>0.99403169376414902</v>
       </c>
       <c r="AB25" s="8">
         <v>26661</v>
@@ -4362,14 +4362,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>5234</v>
+        <v>5247</v>
       </c>
       <c r="AE25" s="14">
-        <v>26831</v>
+        <v>26844</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>1.0063763549754323</v>
+        <v>1.0068639585912007</v>
       </c>
       <c r="AG25" s="8">
         <v>19440</v>
@@ -4379,14 +4379,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>4228</v>
+        <v>4237</v>
       </c>
       <c r="AJ25" s="14">
-        <v>19506</v>
+        <v>19515</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>1.0033950617283951</v>
+        <v>1.003858024691358</v>
       </c>
       <c r="AL25" s="8">
         <v>19709</v>
@@ -4396,14 +4396,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>3689</v>
+        <v>3697</v>
       </c>
       <c r="AO25" s="14">
-        <v>19669</v>
+        <v>19677</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.99797047034349784</v>
+        <v>0.99837637627479836</v>
       </c>
       <c r="AQ25" s="8">
         <v>27081</v>
@@ -4413,14 +4413,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>5068</v>
+        <v>5081</v>
       </c>
       <c r="AT25" s="14">
-        <v>27262</v>
+        <v>27275</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>1.0066836527454672</v>
+        <v>1.0071636941028765</v>
       </c>
       <c r="AV25" s="8">
         <v>19795</v>
@@ -4430,14 +4430,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>3973</v>
+        <v>3983</v>
       </c>
       <c r="AY25" s="14">
-        <v>19916</v>
+        <v>19926</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>1.0061126547107855</v>
+        <v>1.0066178327860571</v>
       </c>
       <c r="BA25" s="8">
         <v>20139</v>
@@ -4447,14 +4447,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>3839</v>
+        <v>3851</v>
       </c>
       <c r="BD25" s="14">
-        <v>20113</v>
+        <v>20125</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>0.9987089726401509</v>
+        <v>0.99930483142161974</v>
       </c>
       <c r="BF25" s="8">
         <v>27639</v>
@@ -4464,14 +4464,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>7504</v>
+        <v>7523</v>
       </c>
       <c r="BI25" s="14">
-        <v>27742</v>
+        <v>27761</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>1.0037266181844495</v>
+        <v>1.0044140526068237</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3459</v>
+        <v>3461</v>
       </c>
       <c r="F26" s="14">
-        <v>13359</v>
+        <v>13361</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.98699667528629476</v>
+        <v>0.9871444403398596</v>
       </c>
       <c r="H26" s="8">
         <v>13884</v>
@@ -4506,14 +4506,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3303</v>
+        <v>3306</v>
       </c>
       <c r="K26" s="14">
-        <v>13931</v>
+        <v>13934</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>1.0033851915874388</v>
+        <v>1.0036012676462114</v>
       </c>
       <c r="M26" s="8">
         <v>25920</v>
@@ -4523,14 +4523,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5128</v>
+        <v>5137</v>
       </c>
       <c r="P26" s="14">
-        <v>26289</v>
+        <v>26298</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>1.0142361111111111</v>
+        <v>1.0145833333333334</v>
       </c>
       <c r="R26" s="8">
         <v>13869</v>
@@ -4540,14 +4540,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3697</v>
+        <v>3706</v>
       </c>
       <c r="U26" s="14">
-        <v>14158</v>
+        <v>14167</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>1.0208378397865743</v>
+        <v>1.0214867690532843</v>
       </c>
       <c r="W26" s="8">
         <v>14474</v>
@@ -4557,14 +4557,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3377</v>
+        <v>3385</v>
       </c>
       <c r="Z26" s="14">
-        <v>14422</v>
+        <v>14430</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.99640735111233936</v>
+        <v>0.99696006632582557</v>
       </c>
       <c r="AB26" s="8">
         <v>27035</v>
@@ -4574,14 +4574,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5617</v>
+        <v>5632</v>
       </c>
       <c r="AE26" s="14">
-        <v>26955</v>
+        <v>26970</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.997040872942482</v>
+        <v>0.99759570926576657</v>
       </c>
       <c r="AG26" s="8">
         <v>14053</v>
@@ -4591,14 +4591,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3362</v>
+        <v>3370</v>
       </c>
       <c r="AJ26" s="14">
-        <v>14083</v>
+        <v>14091</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>1.0021347754927774</v>
+        <v>1.0027040489575179</v>
       </c>
       <c r="AL26" s="8">
         <v>14372</v>
@@ -4608,14 +4608,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>3126</v>
+        <v>3135</v>
       </c>
       <c r="AO26" s="14">
-        <v>14210</v>
+        <v>14219</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.98872808238241028</v>
+        <v>0.98935430002783187</v>
       </c>
       <c r="AQ26" s="8">
         <v>27267</v>
@@ -4625,14 +4625,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5362</v>
+        <v>5378</v>
       </c>
       <c r="AT26" s="14">
-        <v>27055</v>
+        <v>27071</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.99222503392379069</v>
+        <v>0.99281182381633482</v>
       </c>
       <c r="AV26" s="8">
         <v>14007</v>
@@ -4642,14 +4642,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3120</v>
+        <v>3129</v>
       </c>
       <c r="AY26" s="14">
-        <v>14004</v>
+        <v>14013</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.99978582137502681</v>
+        <v>1.0004283572499464</v>
       </c>
       <c r="BA26" s="8">
         <v>14398</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3032</v>
+        <v>3040</v>
       </c>
       <c r="BD26" s="14">
-        <v>14084</v>
+        <v>14092</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.9781914154743715</v>
+        <v>0.978747048201139</v>
       </c>
       <c r="BF26" s="8">
         <v>27339</v>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6592</v>
+        <v>6612</v>
       </c>
       <c r="BI26" s="14">
-        <v>27068</v>
+        <v>27088</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.99008742090054502</v>
+        <v>0.99081897655364137</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4701,14 +4701,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>34596</v>
+        <v>34621</v>
       </c>
       <c r="F27" s="14">
-        <v>120673</v>
+        <v>120698</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>1.0015852990488205</v>
+        <v>1.0017927989243207</v>
       </c>
       <c r="H27" s="8">
         <v>123649</v>
@@ -4718,14 +4718,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>32413</v>
+        <v>32445</v>
       </c>
       <c r="K27" s="14">
-        <v>122515</v>
+        <v>122547</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.99082887851903367</v>
+        <v>0.99108767559786171</v>
       </c>
       <c r="M27" s="8">
         <v>182121</v>
@@ -4735,14 +4735,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>47412</v>
+        <v>47458</v>
       </c>
       <c r="P27" s="14">
-        <v>180903</v>
+        <v>180949</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99331213863310652</v>
+        <v>0.99356471796223389</v>
       </c>
       <c r="R27" s="8">
         <v>122848</v>
@@ -4752,14 +4752,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>33787</v>
+        <v>33817</v>
       </c>
       <c r="U27" s="14">
-        <v>122016</v>
+        <v>122046</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.99322740296952328</v>
+        <v>0.99347160718937222</v>
       </c>
       <c r="W27" s="8">
         <v>125846</v>
@@ -4769,14 +4769,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>34846</v>
+        <v>34881</v>
       </c>
       <c r="Z27" s="14">
-        <v>123294</v>
+        <v>123329</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.97972124660299098</v>
+        <v>0.97999936430240131</v>
       </c>
       <c r="AB27" s="8">
         <v>184102</v>
@@ -4786,14 +4786,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>50023</v>
+        <v>50081</v>
       </c>
       <c r="AE27" s="14">
-        <v>182605</v>
+        <v>182663</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.99186863803760961</v>
+        <v>0.99218368078565145</v>
       </c>
       <c r="AG27" s="8">
         <v>124176</v>
@@ -4803,14 +4803,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>34528</v>
+        <v>34569</v>
       </c>
       <c r="AJ27" s="14">
-        <v>123145</v>
+        <v>123186</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.99169726839324834</v>
+        <v>0.9920274449168921</v>
       </c>
       <c r="AL27" s="8">
         <v>126536</v>
@@ -4820,14 +4820,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>31789</v>
+        <v>31837</v>
       </c>
       <c r="AO27" s="14">
-        <v>123983</v>
+        <v>124031</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.97982392362647786</v>
+        <v>0.9802032623127015</v>
       </c>
       <c r="AQ27" s="8">
         <v>184835</v>
@@ -4837,14 +4837,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>47335</v>
+        <v>47420</v>
       </c>
       <c r="AT27" s="14">
-        <v>184174</v>
+        <v>184259</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.99642383747666841</v>
+        <v>0.99688370709010743</v>
       </c>
       <c r="AV27" s="8">
         <v>124975</v>
@@ -4854,14 +4854,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>31718</v>
+        <v>31785</v>
       </c>
       <c r="AY27" s="14">
-        <v>124258</v>
+        <v>124325</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.99426285257051406</v>
+        <v>0.99479895979195843</v>
       </c>
       <c r="BA27" s="8">
         <v>127493</v>
@@ -4871,14 +4871,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>31020</v>
+        <v>31097</v>
       </c>
       <c r="BD27" s="14">
-        <v>125301</v>
+        <v>125378</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.98280689920230913</v>
+        <v>0.98341085392923533</v>
       </c>
       <c r="BF27" s="8">
         <v>187636</v>
@@ -4888,14 +4888,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>62965</v>
+        <v>63093</v>
       </c>
       <c r="BI27" s="14">
-        <v>185518</v>
+        <v>185646</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.98871218742671985</v>
+        <v>0.98939435929139397</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4913,14 +4913,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>64575</v>
+        <v>64593</v>
       </c>
       <c r="F28" s="14">
-        <v>380017</v>
+        <v>380035</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.99426751925653045</v>
+        <v>0.99431461403215005</v>
       </c>
       <c r="H28" s="8">
         <v>389922</v>
@@ -4930,14 +4930,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>63247</v>
+        <v>63268</v>
       </c>
       <c r="K28" s="14">
-        <v>385040</v>
+        <v>385061</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.98747954719148956</v>
+        <v>0.98753340411672075</v>
       </c>
       <c r="M28" s="8">
         <v>650891</v>
@@ -4947,14 +4947,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>104659</v>
+        <v>104691</v>
       </c>
       <c r="P28" s="14">
-        <v>645732</v>
+        <v>645764</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.99207394171988861</v>
+        <v>0.99212310509747403</v>
       </c>
       <c r="R28" s="8">
         <v>389073</v>
@@ -4964,14 +4964,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>67501</v>
+        <v>67521</v>
       </c>
       <c r="U28" s="14">
-        <v>386505</v>
+        <v>386525</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.99339969620097002</v>
+        <v>0.99345110043616491</v>
       </c>
       <c r="W28" s="8">
         <v>397763</v>
@@ -4981,14 +4981,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>67006</v>
+        <v>67031</v>
       </c>
       <c r="Z28" s="14">
-        <v>391691</v>
+        <v>391716</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.98473462840937942</v>
+        <v>0.98479747990637645</v>
       </c>
       <c r="AB28" s="8">
         <v>660941</v>
@@ -4998,14 +4998,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>103823</v>
+        <v>103870</v>
       </c>
       <c r="AE28" s="14">
-        <v>656388</v>
+        <v>656435</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.99311133671537999</v>
+        <v>0.99318244744992368</v>
       </c>
       <c r="AG28" s="8">
         <v>397417</v>
@@ -5015,14 +5015,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>68349</v>
+        <v>68382</v>
       </c>
       <c r="AJ28" s="14">
-        <v>394553</v>
+        <v>394586</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.99279346379243971</v>
+        <v>0.99287649999874183</v>
       </c>
       <c r="AL28" s="8">
         <v>405895</v>
@@ -5032,14 +5032,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>61061</v>
+        <v>61105</v>
       </c>
       <c r="AO28" s="14">
-        <v>398856</v>
+        <v>398900</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.982658076596164</v>
+        <v>0.98276647901550895</v>
       </c>
       <c r="AQ28" s="8">
         <v>670091</v>
@@ -5049,14 +5049,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>95979</v>
+        <v>96049</v>
       </c>
       <c r="AT28" s="14">
-        <v>666051</v>
+        <v>666121</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.99397096812224006</v>
+        <v>0.99407543154586464</v>
       </c>
       <c r="AV28" s="8">
         <v>405395</v>
@@ -5066,14 +5066,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>60923</v>
+        <v>60974</v>
       </c>
       <c r="AY28" s="14">
-        <v>402723</v>
+        <v>402774</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.99340889749503569</v>
+        <v>0.9935347007239852</v>
       </c>
       <c r="BA28" s="8">
         <v>412255</v>
@@ -5083,14 +5083,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>59334</v>
+        <v>59391</v>
       </c>
       <c r="BD28" s="14">
-        <v>406819</v>
+        <v>406876</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98681398648894492</v>
+        <v>0.98695225042752666</v>
       </c>
       <c r="BF28" s="8">
         <v>680839</v>
@@ -5100,14 +5100,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>127257</v>
+        <v>127370</v>
       </c>
       <c r="BI28" s="14">
-        <v>676166</v>
+        <v>676279</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.99313640963575822</v>
+        <v>0.99330238132656912</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5125,14 +5125,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>24818</v>
+        <v>24824</v>
       </c>
       <c r="F29" s="14">
-        <v>126958</v>
+        <v>126964</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.99530406014566042</v>
+        <v>0.99535109794052856</v>
       </c>
       <c r="H29" s="8">
         <v>129829</v>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>23849</v>
+        <v>23855</v>
       </c>
       <c r="K29" s="14">
-        <v>128360</v>
+        <v>128366</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.98868511657641978</v>
+        <v>0.98873133121259504</v>
       </c>
       <c r="M29" s="8">
         <v>176637</v>
@@ -5159,14 +5159,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>30935</v>
+        <v>30946</v>
       </c>
       <c r="P29" s="14">
-        <v>174200</v>
+        <v>174211</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98620334358033712</v>
+        <v>0.98626561818871472</v>
       </c>
       <c r="R29" s="8">
         <v>129740</v>
@@ -5176,14 +5176,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>24231</v>
+        <v>24242</v>
       </c>
       <c r="U29" s="14">
-        <v>128526</v>
+        <v>128537</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.99064282410975801</v>
+        <v>0.99072760906428237</v>
       </c>
       <c r="W29" s="8">
         <v>131766</v>
@@ -5193,14 +5193,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>23798</v>
+        <v>23810</v>
       </c>
       <c r="Z29" s="14">
-        <v>129560</v>
+        <v>129572</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.98325820014267717</v>
+        <v>0.98334927067680589</v>
       </c>
       <c r="AB29" s="8">
         <v>178083</v>
@@ -5210,14 +5210,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>32775</v>
+        <v>32797</v>
       </c>
       <c r="AE29" s="14">
-        <v>176329</v>
+        <v>176351</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.99015066008546582</v>
+        <v>0.99027419798633221</v>
       </c>
       <c r="AG29" s="8">
         <v>131984</v>
@@ -5227,14 +5227,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>28843</v>
+        <v>28862</v>
       </c>
       <c r="AJ29" s="14">
-        <v>130662</v>
+        <v>130681</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.98998363437992487</v>
+        <v>0.99012759122317862</v>
       </c>
       <c r="AL29" s="8">
         <v>133676</v>
@@ -5244,14 +5244,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>23019</v>
+        <v>23038</v>
       </c>
       <c r="AO29" s="14">
-        <v>131811</v>
+        <v>131830</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.98604835572578475</v>
+        <v>0.9861904904395703</v>
       </c>
       <c r="AQ29" s="8">
         <v>179800</v>
@@ -5261,14 +5261,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>29809</v>
+        <v>29840</v>
       </c>
       <c r="AT29" s="14">
-        <v>178939</v>
+        <v>178970</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.99521134593993321</v>
+        <v>0.99538375973303672</v>
       </c>
       <c r="AV29" s="8">
         <v>134089</v>
@@ -5278,14 +5278,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>22645</v>
+        <v>22665</v>
       </c>
       <c r="AY29" s="14">
-        <v>133137</v>
+        <v>133157</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.99290023790169213</v>
+        <v>0.99304939256762303</v>
       </c>
       <c r="BA29" s="8">
         <v>136058</v>
@@ -5295,14 +5295,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>22986</v>
+        <v>23008</v>
       </c>
       <c r="BD29" s="14">
-        <v>134449</v>
+        <v>134471</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.98817416101956523</v>
+        <v>0.988335856766967</v>
       </c>
       <c r="BF29" s="8">
         <v>182623</v>
@@ -5312,14 +5312,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>41902</v>
+        <v>41936</v>
       </c>
       <c r="BI29" s="14">
-        <v>181379</v>
+        <v>181413</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.99318815264232874</v>
+        <v>0.99337432853474095</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>39270</v>
+        <v>39281</v>
       </c>
       <c r="F30" s="14">
-        <v>166397</v>
+        <v>166408</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.99702206190755804</v>
+        <v>0.9970879720061836</v>
       </c>
       <c r="H30" s="8">
         <v>172134</v>
@@ -5354,14 +5354,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>41641</v>
+        <v>41653</v>
       </c>
       <c r="K30" s="14">
-        <v>169522</v>
+        <v>169534</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.98482577526810511</v>
+        <v>0.98489548839857322</v>
       </c>
       <c r="M30" s="8">
         <v>289249</v>
@@ -5371,14 +5371,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>59640</v>
+        <v>59672</v>
       </c>
       <c r="P30" s="14">
-        <v>286013</v>
+        <v>286045</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.98881240730305031</v>
+        <v>0.98892303862761843</v>
       </c>
       <c r="R30" s="8">
         <v>169142</v>
@@ -5388,14 +5388,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>37540</v>
+        <v>37558</v>
       </c>
       <c r="U30" s="14">
-        <v>167837</v>
+        <v>167855</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.99228458928001328</v>
+        <v>0.99239100873821995</v>
       </c>
       <c r="W30" s="8">
         <v>174259</v>
@@ -5405,14 +5405,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>41346</v>
+        <v>41370</v>
       </c>
       <c r="Z30" s="14">
-        <v>170970</v>
+        <v>170994</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.98112579551127921</v>
+        <v>0.98126352153977703</v>
       </c>
       <c r="AB30" s="8">
         <v>293307</v>
@@ -5422,14 +5422,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>62811</v>
+        <v>62857</v>
       </c>
       <c r="AE30" s="14">
-        <v>290449</v>
+        <v>290495</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.99025594343128531</v>
+        <v>0.9904127756923633</v>
       </c>
       <c r="AG30" s="8">
         <v>172053</v>
@@ -5439,14 +5439,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>37762</v>
+        <v>37793</v>
       </c>
       <c r="AJ30" s="14">
-        <v>170947</v>
+        <v>170978</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.99357174824036776</v>
+        <v>0.99375192527883849</v>
       </c>
       <c r="AL30" s="8">
         <v>176835</v>
@@ -5456,14 +5456,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>36079</v>
+        <v>36113</v>
       </c>
       <c r="AO30" s="14">
-        <v>173623</v>
+        <v>173657</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.98183617496536324</v>
+        <v>0.98202844459524419</v>
       </c>
       <c r="AQ30" s="8">
         <v>297651</v>
@@ -5473,14 +5473,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>57580</v>
+        <v>57647</v>
       </c>
       <c r="AT30" s="14">
-        <v>296171</v>
+        <v>296238</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.99502773382249676</v>
+        <v>0.99525282965620809</v>
       </c>
       <c r="AV30" s="8">
         <v>175428</v>
@@ -5490,14 +5490,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>36179</v>
+        <v>36219</v>
       </c>
       <c r="AY30" s="14">
-        <v>174325</v>
+        <v>174365</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.99371252023622225</v>
+        <v>0.99394053400825411</v>
       </c>
       <c r="BA30" s="8">
         <v>179593</v>
@@ -5507,14 +5507,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>35961</v>
+        <v>36001</v>
       </c>
       <c r="BD30" s="14">
-        <v>176189</v>
+        <v>176229</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.98104603186092998</v>
+        <v>0.9812687576910013</v>
       </c>
       <c r="BF30" s="8">
         <v>302258</v>
@@ -5524,14 +5524,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>72727</v>
+        <v>72817</v>
       </c>
       <c r="BI30" s="14">
-        <v>299346</v>
+        <v>299436</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.99036584639612513</v>
+        <v>0.9906636052643768</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5549,14 +5549,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>21211</v>
+        <v>21215</v>
       </c>
       <c r="F31" s="14">
-        <v>74591</v>
+        <v>74595</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>1.0010871024023622</v>
+        <v>1.0011407864716146</v>
       </c>
       <c r="H31" s="8">
         <v>76671</v>
@@ -5566,14 +5566,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>20121</v>
+        <v>20125</v>
       </c>
       <c r="K31" s="14">
-        <v>75767</v>
+        <v>75771</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.98820936207953458</v>
+        <v>0.9882615330437845</v>
       </c>
       <c r="M31" s="8">
         <v>133745</v>
@@ -5583,14 +5583,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>35660</v>
+        <v>35668</v>
       </c>
       <c r="P31" s="14">
-        <v>133527</v>
+        <v>133535</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>0.99837003252458034</v>
+        <v>0.99842984784477928</v>
       </c>
       <c r="R31" s="8">
         <v>74974</v>
@@ -5600,14 +5600,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>20611</v>
+        <v>20616</v>
       </c>
       <c r="U31" s="14">
-        <v>75026</v>
+        <v>75031</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>1.0006935737722411</v>
+        <v>1.0007602635580335</v>
       </c>
       <c r="W31" s="8">
         <v>77586</v>
@@ -5617,14 +5617,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>21071</v>
+        <v>21077</v>
       </c>
       <c r="Z31" s="14">
-        <v>76080</v>
+        <v>76086</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.98058928157141756</v>
+        <v>0.98066661511097364</v>
       </c>
       <c r="AB31" s="8">
         <v>135116</v>
@@ -5634,14 +5634,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>37176</v>
+        <v>37191</v>
       </c>
       <c r="AE31" s="14">
-        <v>135131</v>
+        <v>135146</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>1.0001110157198259</v>
+        <v>1.0002220314396519</v>
       </c>
       <c r="AG31" s="8">
         <v>76230</v>
@@ -5651,14 +5651,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>22380</v>
+        <v>22396</v>
       </c>
       <c r="AJ31" s="14">
-        <v>75979</v>
+        <v>75995</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>0.99670733307096948</v>
+        <v>0.99691722418995143</v>
       </c>
       <c r="AL31" s="8">
         <v>77611</v>
@@ -5668,14 +5668,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>18511</v>
+        <v>18525</v>
       </c>
       <c r="AO31" s="14">
-        <v>76825</v>
+        <v>76839</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.98987256960997794</v>
+        <v>0.99005295641081803</v>
       </c>
       <c r="AQ31" s="8">
         <v>136879</v>
@@ -5685,14 +5685,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>34695</v>
+        <v>34717</v>
       </c>
       <c r="AT31" s="14">
-        <v>137447</v>
+        <v>137469</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>1.0041496504211749</v>
+        <v>1.0043103763177696</v>
       </c>
       <c r="AV31" s="8">
         <v>76719</v>
@@ -5702,14 +5702,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>18029</v>
+        <v>18043</v>
       </c>
       <c r="AY31" s="14">
-        <v>76890</v>
+        <v>76904</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>1.0022289133070035</v>
+        <v>1.0024113974374014</v>
       </c>
       <c r="BA31" s="8">
         <v>78720</v>
@@ -5719,14 +5719,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>18488</v>
+        <v>18506</v>
       </c>
       <c r="BD31" s="14">
-        <v>78312</v>
+        <v>78330</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.99481707317073176</v>
+        <v>0.99504573170731703</v>
       </c>
       <c r="BF31" s="8">
         <v>140181</v>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>48173</v>
+        <v>48208</v>
       </c>
       <c r="BI31" s="14">
-        <v>140162</v>
+        <v>140197</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>0.99986446094691861</v>
+        <v>1.0001141381499632</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5761,14 +5761,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>45710</v>
+        <v>45720</v>
       </c>
       <c r="F32" s="14">
-        <v>203703</v>
+        <v>203713</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.99992636880393482</v>
+        <v>0.99997545626797824</v>
       </c>
       <c r="H32" s="8">
         <v>210874</v>
@@ -5778,14 +5778,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>42708</v>
+        <v>42717</v>
       </c>
       <c r="K32" s="14">
-        <v>208080</v>
+        <v>208089</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98675038174454888</v>
+        <v>0.9867930612593302</v>
       </c>
       <c r="M32" s="8">
         <v>441035</v>
@@ -5795,14 +5795,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>93369</v>
+        <v>93395</v>
       </c>
       <c r="P32" s="14">
-        <v>438287</v>
+        <v>438313</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.99376920199077168</v>
+        <v>0.99382815422812254</v>
       </c>
       <c r="R32" s="8">
         <v>206418</v>
@@ -5812,14 +5812,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>44042</v>
+        <v>44056</v>
       </c>
       <c r="U32" s="14">
-        <v>205083</v>
+        <v>205097</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99353254076679365</v>
+        <v>0.99360036430931409</v>
       </c>
       <c r="W32" s="8">
         <v>212709</v>
@@ -5829,14 +5829,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>45940</v>
+        <v>45954</v>
       </c>
       <c r="Z32" s="14">
-        <v>209127</v>
+        <v>209141</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.9831600919566168</v>
+        <v>0.98322590957599354</v>
       </c>
       <c r="AB32" s="8">
         <v>446806</v>
@@ -5846,14 +5846,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>97480</v>
+        <v>97525</v>
       </c>
       <c r="AE32" s="14">
-        <v>444904</v>
+        <v>444949</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.99574311893752543</v>
+        <v>0.9958438337891613</v>
       </c>
       <c r="AG32" s="8">
         <v>210129</v>
@@ -5863,14 +5863,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>49118</v>
+        <v>49141</v>
       </c>
       <c r="AJ32" s="14">
-        <v>209472</v>
+        <v>209495</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.99687334922833115</v>
+        <v>0.99698280580024656</v>
       </c>
       <c r="AL32" s="8">
         <v>217332</v>
@@ -5880,14 +5880,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>40319</v>
+        <v>40349</v>
       </c>
       <c r="AO32" s="14">
-        <v>212851</v>
+        <v>212881</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.97938177534831505</v>
+        <v>0.9795198130049878</v>
       </c>
       <c r="AQ32" s="8">
         <v>453805</v>
@@ -5897,14 +5897,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>93229</v>
+        <v>93285</v>
       </c>
       <c r="AT32" s="14">
-        <v>452748</v>
+        <v>452804</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.99767080574255462</v>
+        <v>0.9977942067628166</v>
       </c>
       <c r="AV32" s="8">
         <v>213428</v>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>40147</v>
+        <v>40173</v>
       </c>
       <c r="AY32" s="14">
-        <v>213372</v>
+        <v>213398</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.99973761643270798</v>
+        <v>0.99985943737466498</v>
       </c>
       <c r="BA32" s="8">
         <v>220509</v>
@@ -5931,14 +5931,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>39325</v>
+        <v>39354</v>
       </c>
       <c r="BD32" s="14">
-        <v>217567</v>
+        <v>217596</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.9866581409375581</v>
+        <v>0.98678965484401993</v>
       </c>
       <c r="BF32" s="8">
         <v>463937</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>127730</v>
+        <v>127795</v>
       </c>
       <c r="BI32" s="14">
-        <v>460932</v>
+        <v>460997</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99352282745286535</v>
+        <v>0.99366293268267025</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5973,14 +5973,14 @@
       </c>
       <c r="E33" s="4">
         <f t="shared" si="0"/>
-        <v>74078</v>
+        <v>74089</v>
       </c>
       <c r="F33" s="14">
-        <v>623250</v>
+        <v>623261</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>1.0036312691728597</v>
+        <v>1.00364898268102</v>
       </c>
       <c r="H33" s="8">
         <v>630476</v>
@@ -5990,14 +5990,14 @@
       </c>
       <c r="J33" s="4">
         <f t="shared" si="2"/>
-        <v>78129</v>
+        <v>78135</v>
       </c>
       <c r="K33" s="14">
-        <v>630441</v>
+        <v>630447</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="3"/>
-        <v>0.99994448638806233</v>
+        <v>0.99995400300725168</v>
       </c>
       <c r="M33" s="8">
         <v>1032030</v>
@@ -6007,14 +6007,14 @@
       </c>
       <c r="O33" s="4">
         <f t="shared" si="4"/>
-        <v>130764</v>
+        <v>130778</v>
       </c>
       <c r="P33" s="14">
-        <v>1032125</v>
+        <v>1032139</v>
       </c>
       <c r="Q33" s="5">
         <f t="shared" si="5"/>
-        <v>1.0000920515876477</v>
+        <v>1.0001056170847746</v>
       </c>
       <c r="R33" s="8">
         <v>629419</v>
@@ -6024,14 +6024,14 @@
       </c>
       <c r="T33" s="4">
         <f t="shared" si="6"/>
-        <v>79455</v>
+        <v>79466</v>
       </c>
       <c r="U33" s="14">
-        <v>629949</v>
+        <v>629960</v>
       </c>
       <c r="V33" s="5">
         <f t="shared" si="7"/>
-        <v>1.0008420463951677</v>
+        <v>1.0008595228297843</v>
       </c>
       <c r="W33" s="8">
         <v>637378</v>
@@ -6041,14 +6041,14 @@
       </c>
       <c r="Y33" s="4">
         <f t="shared" si="8"/>
-        <v>80041</v>
+        <v>80053</v>
       </c>
       <c r="Z33" s="14">
-        <v>635150</v>
+        <v>635162</v>
       </c>
       <c r="AA33" s="5">
         <f t="shared" si="9"/>
-        <v>0.99650442908289905</v>
+        <v>0.99652325621530713</v>
       </c>
       <c r="AB33" s="8">
         <v>1041984</v>
@@ -6058,14 +6058,14 @@
       </c>
       <c r="AD33" s="4">
         <f t="shared" si="10"/>
-        <v>142369</v>
+        <v>142386</v>
       </c>
       <c r="AE33" s="14">
-        <v>1042224</v>
+        <v>1042241</v>
       </c>
       <c r="AF33" s="5">
         <f t="shared" si="11"/>
-        <v>1.0002303298323199</v>
+        <v>1.0002466448621092</v>
       </c>
       <c r="AG33" s="8">
         <v>638215</v>
@@ -6075,14 +6075,14 @@
       </c>
       <c r="AI33" s="4">
         <f t="shared" si="12"/>
-        <v>115953</v>
+        <v>115966</v>
       </c>
       <c r="AJ33" s="14">
-        <v>638835</v>
+        <v>638848</v>
       </c>
       <c r="AK33" s="5">
         <f t="shared" si="13"/>
-        <v>1.0009714594611534</v>
+        <v>1.0009918287724355</v>
       </c>
       <c r="AL33" s="8">
         <v>645318</v>
@@ -6092,14 +6092,14 @@
       </c>
       <c r="AN33" s="4">
         <f t="shared" si="14"/>
-        <v>75248</v>
+        <v>75261</v>
       </c>
       <c r="AO33" s="14">
-        <v>642401</v>
+        <v>642414</v>
       </c>
       <c r="AP33" s="5">
         <f t="shared" si="15"/>
-        <v>0.99547974796921823</v>
+        <v>0.99549989307597186</v>
       </c>
       <c r="AQ33" s="8">
         <v>1053133</v>
@@ -6109,14 +6109,14 @@
       </c>
       <c r="AS33" s="4">
         <f t="shared" si="16"/>
-        <v>135405</v>
+        <v>135430</v>
       </c>
       <c r="AT33" s="14">
-        <v>1053991</v>
+        <v>1054016</v>
       </c>
       <c r="AU33" s="5">
         <f t="shared" si="17"/>
-        <v>1.0008147119119808</v>
+        <v>1.0008384506040549</v>
       </c>
       <c r="AV33" s="8">
         <v>647979</v>
@@ -6126,14 +6126,14 @@
       </c>
       <c r="AX33" s="4">
         <f t="shared" si="18"/>
-        <v>69676</v>
+        <v>69694</v>
       </c>
       <c r="AY33" s="14">
-        <v>649923</v>
+        <v>649941</v>
       </c>
       <c r="AZ33" s="5">
         <f t="shared" si="19"/>
-        <v>1.003000097225373</v>
+        <v>1.0030278759033857</v>
       </c>
       <c r="BA33" s="8">
         <v>657743</v>
@@ -6143,14 +6143,14 @@
       </c>
       <c r="BC33" s="4">
         <f t="shared" si="20"/>
-        <v>65926</v>
+        <v>65950</v>
       </c>
       <c r="BD33" s="14">
-        <v>657993</v>
+        <v>658017</v>
       </c>
       <c r="BE33" s="5">
         <f t="shared" si="21"/>
-        <v>1.0003800876634188</v>
+        <v>1.0004165760791068</v>
       </c>
       <c r="BF33" s="8">
         <v>1071541</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="BH33" s="4">
         <f t="shared" si="22"/>
-        <v>153801</v>
+        <v>153831</v>
       </c>
       <c r="BI33" s="14">
-        <v>1071045</v>
+        <v>1071075</v>
       </c>
       <c r="BJ33" s="5">
         <f t="shared" si="23"/>
-        <v>0.99953711523870759</v>
+        <v>0.99956511230088252</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6560,14 +6560,14 @@
       </c>
       <c r="BH35" s="4">
         <f t="shared" ref="BH35:BH48" si="45">BI35-BG35</f>
-        <v>2950</v>
+        <v>2952</v>
       </c>
       <c r="BI35" s="14">
-        <v>14694</v>
+        <v>14696</v>
       </c>
       <c r="BJ35" s="5">
         <f t="shared" ref="BJ35:BJ48" si="46">BI35/BF35</f>
-        <v>0.99721750933152353</v>
+        <v>0.99735324058364438</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="0"/>
-        <v>175027</v>
+        <v>175053</v>
       </c>
       <c r="F36" s="14">
-        <v>834205</v>
+        <v>834231</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="24"/>
-        <v>0.99780870942314759</v>
+        <v>0.99783980852522081</v>
       </c>
       <c r="H36" s="8">
         <v>854298</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="25"/>
-        <v>170013</v>
+        <v>170039</v>
       </c>
       <c r="K36" s="14">
-        <v>844018</v>
+        <v>844044</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="26"/>
-        <v>0.9879667282376875</v>
+        <v>0.98799716258261172</v>
       </c>
       <c r="M36" s="8">
         <v>1510524</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="27"/>
-        <v>313901</v>
+        <v>313963</v>
       </c>
       <c r="P36" s="14">
-        <v>1500899</v>
+        <v>1500961</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="28"/>
-        <v>0.99362803901162777</v>
+        <v>0.99366908437072166</v>
       </c>
       <c r="R36" s="8">
         <v>845008</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="29"/>
-        <v>178562</v>
+        <v>178604</v>
       </c>
       <c r="U36" s="14">
-        <v>840627</v>
+        <v>840669</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="30"/>
-        <v>0.994815433700036</v>
+        <v>0.99486513737148052</v>
       </c>
       <c r="W36" s="8">
         <v>865288</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="31"/>
-        <v>186810</v>
+        <v>186851</v>
       </c>
       <c r="Z36" s="14">
-        <v>849720</v>
+        <v>849761</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="32"/>
-        <v>0.98200830243803217</v>
+        <v>0.9820556855058663</v>
       </c>
       <c r="AB36" s="8">
         <v>1522408</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="33"/>
-        <v>327630</v>
+        <v>327715</v>
       </c>
       <c r="AE36" s="14">
-        <v>1514976</v>
+        <v>1515061</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="34"/>
-        <v>0.99511826001965309</v>
+        <v>0.99517409262168877</v>
       </c>
       <c r="AG36" s="8">
         <v>860909</v>
@@ -6687,14 +6687,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="35"/>
-        <v>196401</v>
+        <v>196457</v>
       </c>
       <c r="AJ36" s="14">
-        <v>856836</v>
+        <v>856892</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="36"/>
-        <v>0.99526895409387051</v>
+        <v>0.99533400161921881</v>
       </c>
       <c r="AL36" s="8">
         <v>879793</v>
@@ -6704,14 +6704,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="37"/>
-        <v>161964</v>
+        <v>162027</v>
       </c>
       <c r="AO36" s="14">
-        <v>866559</v>
+        <v>866622</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="38"/>
-        <v>0.98495782530663467</v>
+        <v>0.98502943305982205</v>
       </c>
       <c r="AQ36" s="8">
         <v>1539776</v>
@@ -6721,14 +6721,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="39"/>
-        <v>299932</v>
+        <v>300036</v>
       </c>
       <c r="AT36" s="14">
-        <v>1536543</v>
+        <v>1536647</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="40"/>
-        <v>0.99790034394613247</v>
+        <v>0.99796788623799826</v>
       </c>
       <c r="AV36" s="8">
         <v>875330</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="41"/>
-        <v>160907</v>
+        <v>160977</v>
       </c>
       <c r="AY36" s="14">
-        <v>873744</v>
+        <v>873814</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="42"/>
-        <v>0.9981881119120789</v>
+        <v>0.99826808175202497</v>
       </c>
       <c r="BA36" s="8">
         <v>893595</v>
@@ -6755,14 +6755,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="43"/>
-        <v>151714</v>
+        <v>151786</v>
       </c>
       <c r="BD36" s="14">
-        <v>883981</v>
+        <v>884053</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="44"/>
-        <v>0.98924121106317742</v>
+        <v>0.9893217844773079</v>
       </c>
       <c r="BF36" s="8">
         <v>1566403</v>
@@ -6772,14 +6772,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="45"/>
-        <v>365100</v>
+        <v>365268</v>
       </c>
       <c r="BI36" s="14">
-        <v>1556897</v>
+        <v>1557065</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="46"/>
-        <v>0.9939313190794451</v>
+        <v>0.99403857117229732</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6797,14 +6797,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="0"/>
-        <v>131166</v>
+        <v>131189</v>
       </c>
       <c r="F37" s="14">
-        <v>667605</v>
+        <v>667628</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="24"/>
-        <v>0.98824067536181681</v>
+        <v>0.98827472174483277</v>
       </c>
       <c r="H37" s="8">
         <v>681828</v>
@@ -6814,14 +6814,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="25"/>
-        <v>121616</v>
+        <v>121645</v>
       </c>
       <c r="K37" s="14">
-        <v>670281</v>
+        <v>670310</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="26"/>
-        <v>0.98306464386912829</v>
+        <v>0.98310717658999047</v>
       </c>
       <c r="M37" s="8">
         <v>856106</v>
@@ -6831,14 +6831,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="27"/>
-        <v>152329</v>
+        <v>152372</v>
       </c>
       <c r="P37" s="14">
-        <v>844535</v>
+        <v>844578</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="28"/>
-        <v>0.98648415032717907</v>
+        <v>0.98653437775228769</v>
       </c>
       <c r="R37" s="8">
         <v>679636</v>
@@ -6848,14 +6848,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="29"/>
-        <v>129320</v>
+        <v>129358</v>
       </c>
       <c r="U37" s="14">
-        <v>671283</v>
+        <v>671321</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="30"/>
-        <v>0.98770959749042131</v>
+        <v>0.98776550977287847</v>
       </c>
       <c r="W37" s="8">
         <v>687189</v>
@@ -6865,14 +6865,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="31"/>
-        <v>130938</v>
+        <v>130981</v>
       </c>
       <c r="Z37" s="14">
-        <v>676072</v>
+        <v>676115</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="32"/>
-        <v>0.9838225000691222</v>
+        <v>0.98388507382976154</v>
       </c>
       <c r="AB37" s="8">
         <v>863912</v>
@@ -6882,14 +6882,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="33"/>
-        <v>163567</v>
+        <v>163629</v>
       </c>
       <c r="AE37" s="14">
-        <v>853690</v>
+        <v>853752</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="34"/>
-        <v>0.98816777634759101</v>
+        <v>0.98823954291640814</v>
       </c>
       <c r="AG37" s="8">
         <v>690763</v>
@@ -6899,14 +6899,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="35"/>
-        <v>131941</v>
+        <v>131997</v>
       </c>
       <c r="AJ37" s="14">
-        <v>682508</v>
+        <v>682564</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="36"/>
-        <v>0.98804944677117912</v>
+        <v>0.98813051654474837</v>
       </c>
       <c r="AL37" s="8">
         <v>697437</v>
@@ -6916,14 +6916,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="37"/>
-        <v>116137</v>
+        <v>116195</v>
       </c>
       <c r="AO37" s="14">
-        <v>688108</v>
+        <v>688166</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="38"/>
-        <v>0.98662388144018742</v>
+        <v>0.98670704307342461</v>
       </c>
       <c r="AQ37" s="8">
         <v>873380</v>
@@ -6933,14 +6933,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="39"/>
-        <v>149934</v>
+        <v>150032</v>
       </c>
       <c r="AT37" s="14">
-        <v>867223</v>
+        <v>867321</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="40"/>
-        <v>0.99295037669742836</v>
+        <v>0.99306258444205275</v>
       </c>
       <c r="AV37" s="8">
         <v>700086</v>
@@ -6950,14 +6950,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="41"/>
-        <v>117037</v>
+        <v>117107</v>
       </c>
       <c r="AY37" s="14">
-        <v>694449</v>
+        <v>694519</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="42"/>
-        <v>0.99194813208662935</v>
+        <v>0.99204811980242424</v>
       </c>
       <c r="BA37" s="8">
         <v>708485</v>
@@ -6967,14 +6967,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="43"/>
-        <v>113088</v>
+        <v>113158</v>
       </c>
       <c r="BD37" s="14">
-        <v>698960</v>
+        <v>699030</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="44"/>
-        <v>0.98655581981269891</v>
+        <v>0.9866546221867788</v>
       </c>
       <c r="BF37" s="8">
         <v>887779</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="45"/>
-        <v>186499</v>
+        <v>186633</v>
       </c>
       <c r="BI37" s="14">
-        <v>876334</v>
+        <v>876468</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="46"/>
-        <v>0.98710827807370982</v>
+        <v>0.98725921653925131</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7009,14 +7009,14 @@
       </c>
       <c r="E38" s="4">
         <f t="shared" si="0"/>
-        <v>6078</v>
+        <v>6081</v>
       </c>
       <c r="F38" s="14">
-        <v>22912</v>
+        <v>22915</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="24"/>
-        <v>1.0076967058099133</v>
+        <v>1.0078286493380832</v>
       </c>
       <c r="H38" s="8">
         <v>23122</v>
@@ -7026,14 +7026,14 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" si="25"/>
-        <v>5823</v>
+        <v>5825</v>
       </c>
       <c r="K38" s="14">
-        <v>23187</v>
+        <v>23189</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="26"/>
-        <v>1.0028111755038491</v>
+        <v>1.0028976732116599</v>
       </c>
       <c r="M38" s="8">
         <v>35582</v>
@@ -7043,14 +7043,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="27"/>
-        <v>9156</v>
+        <v>9159</v>
       </c>
       <c r="P38" s="14">
-        <v>35778</v>
+        <v>35781</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="28"/>
-        <v>1.0055084031251758</v>
+        <v>1.0055927154179078</v>
       </c>
       <c r="R38" s="8">
         <v>22911</v>
@@ -7060,14 +7060,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="29"/>
-        <v>6107</v>
+        <v>6109</v>
       </c>
       <c r="U38" s="14">
-        <v>23137</v>
+        <v>23139</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="30"/>
-        <v>1.0098642573436341</v>
+        <v>1.0099515516564095</v>
       </c>
       <c r="W38" s="8">
         <v>23450</v>
@@ -7077,14 +7077,14 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="31"/>
-        <v>6340</v>
+        <v>6342</v>
       </c>
       <c r="Z38" s="14">
-        <v>23362</v>
+        <v>23364</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="32"/>
-        <v>0.99624733475479743</v>
+        <v>0.99633262260127931</v>
       </c>
       <c r="AB38" s="8">
         <v>35915</v>
@@ -7094,14 +7094,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="33"/>
-        <v>9126</v>
+        <v>9131</v>
       </c>
       <c r="AE38" s="14">
-        <v>36263</v>
+        <v>36268</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="34"/>
-        <v>1.0096895447584575</v>
+        <v>1.0098287623555617</v>
       </c>
       <c r="AG38" s="8">
         <v>23414</v>
@@ -7111,14 +7111,14 @@
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="35"/>
-        <v>5989</v>
+        <v>5993</v>
       </c>
       <c r="AJ38" s="14">
-        <v>23661</v>
+        <v>23665</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="36"/>
-        <v>1.0105492440420261</v>
+        <v>1.0107200820022209</v>
       </c>
       <c r="AL38" s="8">
         <v>23927</v>
@@ -7128,14 +7128,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="37"/>
-        <v>5871</v>
+        <v>5873</v>
       </c>
       <c r="AO38" s="14">
-        <v>23916</v>
+        <v>23918</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="38"/>
-        <v>0.99954026831612819</v>
+        <v>0.99962385589501401</v>
       </c>
       <c r="AQ38" s="8">
         <v>36551</v>
@@ -7145,14 +7145,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="39"/>
-        <v>8716</v>
+        <v>8723</v>
       </c>
       <c r="AT38" s="14">
-        <v>37030</v>
+        <v>37037</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="40"/>
-        <v>1.0131049766080271</v>
+        <v>1.0132964898361194</v>
       </c>
       <c r="AV38" s="8">
         <v>23833</v>
@@ -7162,14 +7162,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="41"/>
-        <v>5572</v>
+        <v>5576</v>
       </c>
       <c r="AY38" s="14">
-        <v>24165</v>
+        <v>24169</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="42"/>
-        <v>1.0139302647589477</v>
+        <v>1.0140980992741158</v>
       </c>
       <c r="BA38" s="8">
         <v>24292</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="BC38" s="4">
         <f t="shared" si="43"/>
-        <v>5298</v>
+        <v>5302</v>
       </c>
       <c r="BD38" s="14">
-        <v>24404</v>
+        <v>24408</v>
       </c>
       <c r="BE38" s="5">
         <f t="shared" si="44"/>
-        <v>1.0046105713815248</v>
+        <v>1.0047752346451506</v>
       </c>
       <c r="BF38" s="8">
         <v>37393</v>
@@ -7196,14 +7196,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="45"/>
-        <v>10290</v>
+        <v>10298</v>
       </c>
       <c r="BI38" s="14">
-        <v>37526</v>
+        <v>37534</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="46"/>
-        <v>1.0035568154467414</v>
+        <v>1.0037707592330116</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="0"/>
-        <v>58556</v>
+        <v>58577</v>
       </c>
       <c r="F40" s="14">
-        <v>275673</v>
+        <v>275694</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="24"/>
-        <v>0.99262211852139914</v>
+        <v>0.99269773370492798</v>
       </c>
       <c r="H40" s="8">
         <v>279588</v>
@@ -7450,14 +7450,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="25"/>
-        <v>56589</v>
+        <v>56610</v>
       </c>
       <c r="K40" s="14">
-        <v>277336</v>
+        <v>277357</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="26"/>
-        <v>0.99194529092807993</v>
+        <v>0.99202040144784465</v>
       </c>
       <c r="M40" s="8">
         <v>339205</v>
@@ -7467,14 +7467,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="27"/>
-        <v>71930</v>
+        <v>71960</v>
       </c>
       <c r="P40" s="14">
-        <v>336789</v>
+        <v>336819</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="28"/>
-        <v>0.99287746348078598</v>
+        <v>0.99296590557332587</v>
       </c>
       <c r="R40" s="8">
         <v>280405</v>
@@ -7484,14 +7484,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="29"/>
-        <v>61809</v>
+        <v>61842</v>
       </c>
       <c r="U40" s="14">
-        <v>278682</v>
+        <v>278715</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="30"/>
-        <v>0.99385531641732494</v>
+        <v>0.9939730033344627</v>
       </c>
       <c r="W40" s="8">
         <v>283529</v>
@@ -7501,14 +7501,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="31"/>
-        <v>57423</v>
+        <v>57453</v>
       </c>
       <c r="Z40" s="14">
-        <v>280581</v>
+        <v>280611</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="32"/>
-        <v>0.98960247452641525</v>
+        <v>0.9897082838087109</v>
       </c>
       <c r="AB40" s="8">
         <v>342699</v>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="33"/>
-        <v>73599</v>
+        <v>73640</v>
       </c>
       <c r="AE40" s="14">
-        <v>341038</v>
+        <v>341079</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="34"/>
-        <v>0.99515318107143591</v>
+        <v>0.99527281958803493</v>
       </c>
       <c r="AG40" s="8">
         <v>284836</v>
@@ -7535,14 +7535,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="35"/>
-        <v>61197</v>
+        <v>61236</v>
       </c>
       <c r="AJ40" s="14">
-        <v>283289</v>
+        <v>283328</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="36"/>
-        <v>0.99456880450504848</v>
+        <v>0.99470572539987923</v>
       </c>
       <c r="AL40" s="8">
         <v>287465</v>
@@ -7552,14 +7552,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="37"/>
-        <v>57506</v>
+        <v>57548</v>
       </c>
       <c r="AO40" s="14">
-        <v>285373</v>
+        <v>285415</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="38"/>
-        <v>0.99272259231558624</v>
+        <v>0.99286869705877234</v>
       </c>
       <c r="AQ40" s="8">
         <v>346543</v>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="39"/>
-        <v>69282</v>
+        <v>69333</v>
       </c>
       <c r="AT40" s="14">
-        <v>345772</v>
+        <v>345823</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="40"/>
-        <v>0.99777516787238529</v>
+        <v>0.99792233575631306</v>
       </c>
       <c r="AV40" s="8">
         <v>288959</v>
@@ -7586,14 +7586,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="41"/>
-        <v>60291</v>
+        <v>60340</v>
       </c>
       <c r="AY40" s="14">
-        <v>287597</v>
+        <v>287646</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="42"/>
-        <v>0.99528652853865085</v>
+        <v>0.99545610276890495</v>
       </c>
       <c r="BA40" s="8">
         <v>291465</v>
@@ -7603,14 +7603,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="43"/>
-        <v>55893</v>
+        <v>55944</v>
       </c>
       <c r="BD40" s="14">
-        <v>288740</v>
+        <v>288791</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="44"/>
-        <v>0.99065067846911292</v>
+        <v>0.99082565659684696</v>
       </c>
       <c r="BF40" s="8">
         <v>351557</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="45"/>
-        <v>85054</v>
+        <v>85115</v>
       </c>
       <c r="BI40" s="14">
-        <v>348646</v>
+        <v>348707</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="46"/>
-        <v>0.99171969268141436</v>
+        <v>0.99189320650705293</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="0"/>
-        <v>143317</v>
+        <v>143380</v>
       </c>
       <c r="F41" s="14">
-        <v>904604</v>
+        <v>904667</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="24"/>
-        <v>0.99176638007968299</v>
+        <v>0.99183545039326226</v>
       </c>
       <c r="H41" s="8">
         <v>920596</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="25"/>
-        <v>138928</v>
+        <v>139002</v>
       </c>
       <c r="K41" s="14">
-        <v>909622</v>
+        <v>909696</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="26"/>
-        <v>0.98807946156620274</v>
+        <v>0.98815984427479586</v>
       </c>
       <c r="M41" s="8">
         <v>1028922</v>
@@ -7679,14 +7679,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="27"/>
-        <v>156479</v>
+        <v>156571</v>
       </c>
       <c r="P41" s="14">
-        <v>1016616</v>
+        <v>1016708</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="28"/>
-        <v>0.98803990973076672</v>
+        <v>0.98812932369994999</v>
       </c>
       <c r="R41" s="8">
         <v>924082</v>
@@ -7696,14 +7696,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="29"/>
-        <v>157412</v>
+        <v>157498</v>
       </c>
       <c r="U41" s="14">
-        <v>914281</v>
+        <v>914367</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="30"/>
-        <v>0.9893937983858575</v>
+        <v>0.98948686371988637</v>
       </c>
       <c r="W41" s="8">
         <v>929406</v>
@@ -7713,14 +7713,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="31"/>
-        <v>146153</v>
+        <v>146237</v>
       </c>
       <c r="Z41" s="14">
-        <v>918056</v>
+        <v>918140</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="32"/>
-        <v>0.98778789893760099</v>
+        <v>0.98787827924502314</v>
       </c>
       <c r="AB41" s="8">
         <v>1036539</v>
@@ -7730,14 +7730,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="33"/>
-        <v>166382</v>
+        <v>166484</v>
       </c>
       <c r="AE41" s="14">
-        <v>1025740</v>
+        <v>1025842</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="34"/>
-        <v>0.98958167517092943</v>
+        <v>0.98968007957250037</v>
       </c>
       <c r="AG41" s="8">
         <v>935526</v>
@@ -7747,14 +7747,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="35"/>
-        <v>150377</v>
+        <v>150479</v>
       </c>
       <c r="AJ41" s="14">
-        <v>924840</v>
+        <v>924942</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="36"/>
-        <v>0.98857754888693639</v>
+        <v>0.9886865784596045</v>
       </c>
       <c r="AL41" s="8">
         <v>940174</v>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="37"/>
-        <v>143098</v>
+        <v>143207</v>
       </c>
       <c r="AO41" s="14">
-        <v>929304</v>
+        <v>929413</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="38"/>
-        <v>0.98843831035531726</v>
+        <v>0.98855424634163458</v>
       </c>
       <c r="AQ41" s="8">
         <v>1046219</v>
@@ -7781,14 +7781,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="39"/>
-        <v>165470</v>
+        <v>165595</v>
       </c>
       <c r="AT41" s="14">
-        <v>1037357</v>
+        <v>1037482</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="40"/>
-        <v>0.99152949812610935</v>
+        <v>0.99164897597921664</v>
       </c>
       <c r="AV41" s="8">
         <v>945246</v>
@@ -7798,14 +7798,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="41"/>
-        <v>138608</v>
+        <v>138728</v>
       </c>
       <c r="AY41" s="14">
-        <v>936318</v>
+        <v>936438</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="42"/>
-        <v>0.99055483969252445</v>
+        <v>0.99068179077192609</v>
       </c>
       <c r="BA41" s="8">
         <v>950318</v>
@@ -7815,14 +7815,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="43"/>
-        <v>134107</v>
+        <v>134235</v>
       </c>
       <c r="BD41" s="14">
-        <v>939912</v>
+        <v>940040</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="44"/>
-        <v>0.98904998116419973</v>
+        <v>0.989184672920012</v>
       </c>
       <c r="BF41" s="8">
         <v>1056723</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="45"/>
-        <v>199273</v>
+        <v>199438</v>
       </c>
       <c r="BI41" s="14">
-        <v>1047249</v>
+        <v>1047414</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="46"/>
-        <v>0.99103454736955665</v>
+        <v>0.99119069046476704</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7857,14 +7857,14 @@
       </c>
       <c r="E42" s="4">
         <f t="shared" si="0"/>
-        <v>3672</v>
+        <v>3673</v>
       </c>
       <c r="F42" s="14">
-        <v>18227</v>
+        <v>18228</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="24"/>
-        <v>0.9881810788831662</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="H42" s="8">
         <v>18615</v>
@@ -7874,14 +7874,14 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" si="25"/>
-        <v>3659</v>
+        <v>3660</v>
       </c>
       <c r="K42" s="14">
-        <v>18334</v>
+        <v>18335</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="26"/>
-        <v>0.98490464679022294</v>
+        <v>0.98495836690840721</v>
       </c>
       <c r="M42" s="8">
         <v>20702</v>
@@ -7891,14 +7891,14 @@
       </c>
       <c r="O42" s="4">
         <f t="shared" si="27"/>
-        <v>4075</v>
+        <v>4076</v>
       </c>
       <c r="P42" s="14">
-        <v>20358</v>
+        <v>20359</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" si="28"/>
-        <v>0.98338324799536281</v>
+        <v>0.9834315525070042</v>
       </c>
       <c r="R42" s="8">
         <v>18543</v>
@@ -7908,14 +7908,14 @@
       </c>
       <c r="T42" s="4">
         <f t="shared" si="29"/>
-        <v>4113</v>
+        <v>4114</v>
       </c>
       <c r="U42" s="14">
-        <v>18330</v>
+        <v>18331</v>
       </c>
       <c r="V42" s="5">
         <f t="shared" si="30"/>
-        <v>0.98851318556867818</v>
+        <v>0.98856711427492849</v>
       </c>
       <c r="W42" s="8">
         <v>18720</v>
@@ -7925,14 +7925,14 @@
       </c>
       <c r="Y42" s="4">
         <f t="shared" si="31"/>
-        <v>3881</v>
+        <v>3882</v>
       </c>
       <c r="Z42" s="14">
-        <v>18377</v>
+        <v>18378</v>
       </c>
       <c r="AA42" s="5">
         <f t="shared" si="32"/>
-        <v>0.98167735042735038</v>
+        <v>0.98173076923076918</v>
       </c>
       <c r="AB42" s="8">
         <v>20718</v>
@@ -7942,14 +7942,14 @@
       </c>
       <c r="AD42" s="4">
         <f t="shared" si="33"/>
-        <v>4358</v>
+        <v>4360</v>
       </c>
       <c r="AE42" s="14">
-        <v>20311</v>
+        <v>20313</v>
       </c>
       <c r="AF42" s="5">
         <f t="shared" si="34"/>
-        <v>0.98035524664542906</v>
+        <v>0.9804517810599479</v>
       </c>
       <c r="AG42" s="8">
         <v>18665</v>
@@ -7959,14 +7959,14 @@
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="35"/>
-        <v>3825</v>
+        <v>3826</v>
       </c>
       <c r="AJ42" s="14">
-        <v>18389</v>
+        <v>18390</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="36"/>
-        <v>0.98521296544334314</v>
+        <v>0.98526654165550498</v>
       </c>
       <c r="AL42" s="8">
         <v>18792</v>
@@ -7976,14 +7976,14 @@
       </c>
       <c r="AN42" s="4">
         <f t="shared" si="37"/>
-        <v>3428</v>
+        <v>3430</v>
       </c>
       <c r="AO42" s="14">
-        <v>18510</v>
+        <v>18512</v>
       </c>
       <c r="AP42" s="5">
         <f t="shared" si="38"/>
-        <v>0.98499361430395915</v>
+        <v>0.9851000425713069</v>
       </c>
       <c r="AQ42" s="8">
         <v>20796</v>
@@ -7993,14 +7993,14 @@
       </c>
       <c r="AS42" s="4">
         <f t="shared" si="39"/>
-        <v>4231</v>
+        <v>4234</v>
       </c>
       <c r="AT42" s="14">
-        <v>20549</v>
+        <v>20552</v>
       </c>
       <c r="AU42" s="5">
         <f t="shared" si="40"/>
-        <v>0.98812271590690515</v>
+        <v>0.98826697441815736</v>
       </c>
       <c r="AV42" s="8">
         <v>18829</v>
@@ -8010,14 +8010,14 @@
       </c>
       <c r="AX42" s="4">
         <f t="shared" si="41"/>
-        <v>3671</v>
+        <v>3674</v>
       </c>
       <c r="AY42" s="14">
-        <v>18586</v>
+        <v>18589</v>
       </c>
       <c r="AZ42" s="5">
         <f t="shared" si="42"/>
-        <v>0.98709437569706304</v>
+        <v>0.98725370439216098</v>
       </c>
       <c r="BA42" s="8">
         <v>18938</v>
@@ -8027,14 +8027,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="43"/>
-        <v>3509</v>
+        <v>3513</v>
       </c>
       <c r="BD42" s="14">
-        <v>18691</v>
+        <v>18695</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="44"/>
-        <v>0.98695744006758901</v>
+        <v>0.98716865561305311</v>
       </c>
       <c r="BF42" s="8">
         <v>21042</v>
@@ -8044,14 +8044,14 @@
       </c>
       <c r="BH42" s="4">
         <f t="shared" si="45"/>
-        <v>4844</v>
+        <v>4848</v>
       </c>
       <c r="BI42" s="14">
-        <v>20774</v>
+        <v>20778</v>
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="46"/>
-        <v>0.98726356810189142</v>
+        <v>0.98745366410037072</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8103,14 +8103,14 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" si="27"/>
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="P43" s="14">
-        <v>4339</v>
+        <v>4340</v>
       </c>
       <c r="Q43" s="5">
         <f t="shared" si="28"/>
-        <v>0.98725824800910122</v>
+        <v>0.98748577929465298</v>
       </c>
       <c r="R43" s="8">
         <v>3498</v>
@@ -8137,14 +8137,14 @@
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="31"/>
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="Z43" s="14">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="32"/>
-        <v>0.98929878907350044</v>
+        <v>0.98958039988735569</v>
       </c>
       <c r="AB43" s="8">
         <v>4429</v>
@@ -8154,14 +8154,14 @@
       </c>
       <c r="AD43" s="4">
         <f t="shared" si="33"/>
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="AE43" s="14">
-        <v>4380</v>
+        <v>4382</v>
       </c>
       <c r="AF43" s="5">
         <f t="shared" si="34"/>
-        <v>0.98893655452698126</v>
+        <v>0.98938812372996165</v>
       </c>
       <c r="AG43" s="8">
         <v>3560</v>
@@ -8171,14 +8171,14 @@
       </c>
       <c r="AI43" s="4">
         <f t="shared" si="35"/>
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="AJ43" s="14">
-        <v>3546</v>
+        <v>3547</v>
       </c>
       <c r="AK43" s="5">
         <f t="shared" si="36"/>
-        <v>0.99606741573033708</v>
+        <v>0.99634831460674156</v>
       </c>
       <c r="AL43" s="8">
         <v>3588</v>
@@ -8188,14 +8188,14 @@
       </c>
       <c r="AN43" s="4">
         <f t="shared" si="37"/>
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AO43" s="14">
-        <v>3583</v>
+        <v>3584</v>
       </c>
       <c r="AP43" s="5">
         <f t="shared" si="38"/>
-        <v>0.99860646599777037</v>
+        <v>0.99888517279821631</v>
       </c>
       <c r="AQ43" s="8">
         <v>4449</v>
@@ -8205,14 +8205,14 @@
       </c>
       <c r="AS43" s="4">
         <f t="shared" si="39"/>
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="AT43" s="14">
-        <v>4463</v>
+        <v>4465</v>
       </c>
       <c r="AU43" s="5">
         <f t="shared" si="40"/>
-        <v>1.00314677455608</v>
+        <v>1.0035963137783772</v>
       </c>
       <c r="AV43" s="8">
         <v>3616</v>
@@ -8222,14 +8222,14 @@
       </c>
       <c r="AX43" s="4">
         <f t="shared" si="41"/>
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="AY43" s="14">
-        <v>3635</v>
+        <v>3636</v>
       </c>
       <c r="AZ43" s="5">
         <f t="shared" si="42"/>
-        <v>1.0052544247787611</v>
+        <v>1.0055309734513274</v>
       </c>
       <c r="BA43" s="8">
         <v>3655</v>
@@ -8239,14 +8239,14 @@
       </c>
       <c r="BC43" s="4">
         <f t="shared" si="43"/>
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="BD43" s="14">
-        <v>3649</v>
+        <v>3650</v>
       </c>
       <c r="BE43" s="5">
         <f t="shared" si="44"/>
-        <v>0.99835841313269491</v>
+        <v>0.99863201094391241</v>
       </c>
       <c r="BF43" s="8">
         <v>4544</v>
@@ -8256,14 +8256,14 @@
       </c>
       <c r="BH43" s="4">
         <f t="shared" si="45"/>
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="BI43" s="14">
-        <v>4539</v>
+        <v>4540</v>
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="46"/>
-        <v>0.99889964788732399</v>
+        <v>0.99911971830985913</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8281,14 +8281,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="0"/>
-        <v>76600</v>
+        <v>76616</v>
       </c>
       <c r="F44" s="14">
-        <v>333301</v>
+        <v>333317</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="24"/>
-        <v>0.99129459771345629</v>
+        <v>0.99134218447006195</v>
       </c>
       <c r="H44" s="8">
         <v>340996</v>
@@ -8298,14 +8298,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="25"/>
-        <v>75646</v>
+        <v>75667</v>
       </c>
       <c r="K44" s="14">
-        <v>337259</v>
+        <v>337280</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="26"/>
-        <v>0.9890409271663011</v>
+        <v>0.98910251146641015</v>
       </c>
       <c r="M44" s="8">
         <v>408512</v>
@@ -8315,14 +8315,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="27"/>
-        <v>87256</v>
+        <v>87279</v>
       </c>
       <c r="P44" s="14">
-        <v>403967</v>
+        <v>403990</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="28"/>
-        <v>0.9888742558358139</v>
+        <v>0.9889305577314742</v>
       </c>
       <c r="R44" s="8">
         <v>342556</v>
@@ -8332,14 +8332,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="29"/>
-        <v>80278</v>
+        <v>80300</v>
       </c>
       <c r="U44" s="14">
-        <v>339366</v>
+        <v>339388</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="30"/>
-        <v>0.99068765398942071</v>
+        <v>0.99075187706535572</v>
       </c>
       <c r="W44" s="8">
         <v>347597</v>
@@ -8349,14 +8349,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="31"/>
-        <v>78988</v>
+        <v>79014</v>
       </c>
       <c r="Z44" s="14">
-        <v>343131</v>
+        <v>343157</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="32"/>
-        <v>0.98715178784627022</v>
+        <v>0.98722658711093592</v>
       </c>
       <c r="AB44" s="8">
         <v>416340</v>
@@ -8366,14 +8366,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="33"/>
-        <v>92021</v>
+        <v>92053</v>
       </c>
       <c r="AE44" s="14">
-        <v>412321</v>
+        <v>412353</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="34"/>
-        <v>0.9903468319162223</v>
+        <v>0.99042369217466497</v>
       </c>
       <c r="AG44" s="8">
         <v>350469</v>
@@ -8383,14 +8383,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="35"/>
-        <v>79536</v>
+        <v>79567</v>
       </c>
       <c r="AJ44" s="14">
-        <v>347308</v>
+        <v>347339</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="36"/>
-        <v>0.99098065734772545</v>
+        <v>0.99106911024940869</v>
       </c>
       <c r="AL44" s="8">
         <v>355186</v>
@@ -8400,14 +8400,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="37"/>
-        <v>72493</v>
+        <v>72527</v>
       </c>
       <c r="AO44" s="14">
-        <v>350774</v>
+        <v>350808</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="38"/>
-        <v>0.98757833923634375</v>
+        <v>0.98767406372998934</v>
       </c>
       <c r="AQ44" s="8">
         <v>424208</v>
@@ -8417,14 +8417,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="39"/>
-        <v>85670</v>
+        <v>85711</v>
       </c>
       <c r="AT44" s="14">
-        <v>420906</v>
+        <v>420947</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="40"/>
-        <v>0.99221608267642292</v>
+        <v>0.99231273337607961</v>
       </c>
       <c r="AV44" s="8">
         <v>358114</v>
@@ -8434,14 +8434,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="41"/>
-        <v>72265</v>
+        <v>72307</v>
       </c>
       <c r="AY44" s="14">
-        <v>354380</v>
+        <v>354422</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="42"/>
-        <v>0.98957315268322377</v>
+        <v>0.98969043377248589</v>
       </c>
       <c r="BA44" s="8">
         <v>361984</v>
@@ -8451,14 +8451,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="43"/>
-        <v>71152</v>
+        <v>71195</v>
       </c>
       <c r="BD44" s="14">
-        <v>357340</v>
+        <v>357383</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="44"/>
-        <v>0.98717070367751059</v>
+        <v>0.98728949345827444</v>
       </c>
       <c r="BF44" s="8">
         <v>432310</v>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="45"/>
-        <v>106788</v>
+        <v>106850</v>
       </c>
       <c r="BI44" s="14">
-        <v>426965</v>
+        <v>427027</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="46"/>
-        <v>0.98763618699544309</v>
+        <v>0.9877796025999861</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8493,14 +8493,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="0"/>
-        <v>52292</v>
+        <v>52302</v>
       </c>
       <c r="F45" s="14">
-        <v>251286</v>
+        <v>251296</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="24"/>
-        <v>0.98328363815650455</v>
+        <v>0.98332276821699971</v>
       </c>
       <c r="H45" s="8">
         <v>257610</v>
@@ -8510,14 +8510,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="25"/>
-        <v>49775</v>
+        <v>49787</v>
       </c>
       <c r="K45" s="14">
-        <v>253158</v>
+        <v>253170</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="26"/>
-        <v>0.98271806218702695</v>
+        <v>0.98276464422964949</v>
       </c>
       <c r="M45" s="8">
         <v>310366</v>
@@ -8527,14 +8527,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="27"/>
-        <v>59518</v>
+        <v>59533</v>
       </c>
       <c r="P45" s="14">
-        <v>304790</v>
+        <v>304805</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="28"/>
-        <v>0.98203411456151768</v>
+        <v>0.98208244459766858</v>
       </c>
       <c r="R45" s="8">
         <v>257356</v>
@@ -8544,14 +8544,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="29"/>
-        <v>53280</v>
+        <v>53293</v>
       </c>
       <c r="U45" s="14">
-        <v>253701</v>
+        <v>253714</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="30"/>
-        <v>0.98579788308801819</v>
+        <v>0.98584839677334124</v>
       </c>
       <c r="W45" s="8">
         <v>260553</v>
@@ -8561,14 +8561,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="31"/>
-        <v>55315</v>
+        <v>55331</v>
       </c>
       <c r="Z45" s="14">
-        <v>255659</v>
+        <v>255675</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="32"/>
-        <v>0.98121687334246777</v>
+        <v>0.98127828119422922</v>
       </c>
       <c r="AB45" s="8">
         <v>313911</v>
@@ -8578,14 +8578,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="33"/>
-        <v>64995</v>
+        <v>65024</v>
       </c>
       <c r="AE45" s="14">
-        <v>308402</v>
+        <v>308431</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="34"/>
-        <v>0.98245043977433089</v>
+        <v>0.9825428226471834</v>
       </c>
       <c r="AG45" s="8">
         <v>261210</v>
@@ -8595,14 +8595,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="35"/>
-        <v>53712</v>
+        <v>53736</v>
       </c>
       <c r="AJ45" s="14">
-        <v>257042</v>
+        <v>257066</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="36"/>
-        <v>0.98404348991233104</v>
+        <v>0.98413537000880513</v>
       </c>
       <c r="AL45" s="8">
         <v>264020</v>
@@ -8612,14 +8612,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="37"/>
-        <v>48948</v>
+        <v>48974</v>
       </c>
       <c r="AO45" s="14">
-        <v>259357</v>
+        <v>259383</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="38"/>
-        <v>0.98233845920763574</v>
+        <v>0.98243693659571241</v>
       </c>
       <c r="AQ45" s="8">
         <v>317407</v>
@@ -8629,14 +8629,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="39"/>
-        <v>63247</v>
+        <v>63286</v>
       </c>
       <c r="AT45" s="14">
-        <v>311437</v>
+        <v>311476</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="40"/>
-        <v>0.98119134108573536</v>
+        <v>0.98131421172185873</v>
       </c>
       <c r="AV45" s="8">
         <v>263886</v>
@@ -8646,14 +8646,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="41"/>
-        <v>51075</v>
+        <v>51105</v>
       </c>
       <c r="AY45" s="14">
-        <v>259501</v>
+        <v>259531</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="42"/>
-        <v>0.98338297598205282</v>
+        <v>0.98349666143713577</v>
       </c>
       <c r="BA45" s="8">
         <v>265781</v>
@@ -8663,14 +8663,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="43"/>
-        <v>49527</v>
+        <v>49556</v>
       </c>
       <c r="BD45" s="14">
-        <v>261215</v>
+        <v>261244</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="44"/>
-        <v>0.98282044239430211</v>
+        <v>0.98292955478382582</v>
       </c>
       <c r="BF45" s="8">
         <v>319799</v>
@@ -8680,14 +8680,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="45"/>
-        <v>79686</v>
+        <v>79735</v>
       </c>
       <c r="BI45" s="14">
-        <v>314495</v>
+        <v>314544</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="46"/>
-        <v>0.98341458228449741</v>
+        <v>0.98356780352659012</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8705,14 +8705,14 @@
       </c>
       <c r="E46" s="4">
         <f t="shared" si="0"/>
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F46" s="14">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="24"/>
-        <v>1.0713640469738031</v>
+        <v>1.0718157181571815</v>
       </c>
       <c r="H46" s="8">
         <v>2377</v>
@@ -8739,14 +8739,14 @@
       </c>
       <c r="O46" s="4">
         <f t="shared" si="27"/>
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="P46" s="14">
-        <v>6868</v>
+        <v>6869</v>
       </c>
       <c r="Q46" s="5">
         <f t="shared" si="28"/>
-        <v>1.0267603528180596</v>
+        <v>1.026909851995814</v>
       </c>
       <c r="R46" s="8">
         <v>2186</v>
@@ -8790,14 +8790,14 @@
       </c>
       <c r="AD46" s="4">
         <f t="shared" si="33"/>
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="AE46" s="14">
-        <v>7155</v>
+        <v>7156</v>
       </c>
       <c r="AF46" s="5">
         <f t="shared" si="34"/>
-        <v>1.0339595375722543</v>
+        <v>1.0341040462427746</v>
       </c>
       <c r="AG46" s="8">
         <v>2260</v>
@@ -8841,14 +8841,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="39"/>
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="AT46" s="14">
-        <v>7356</v>
+        <v>7358</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="40"/>
-        <v>1.0298194036119277</v>
+        <v>1.0300993980120399</v>
       </c>
       <c r="AV46" s="8">
         <v>2225</v>
@@ -8892,14 +8892,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="45"/>
-        <v>1789</v>
+        <v>1792</v>
       </c>
       <c r="BI46" s="14">
-        <v>7547</v>
+        <v>7550</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="46"/>
-        <v>1.0189010395571756</v>
+        <v>1.0193060618334009</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9115,10 +9115,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="27"/>
+      <c r="B48" s="22"/>
       <c r="C48" s="10">
         <f>SUM(C10:C47)</f>
         <v>7712416</v>
@@ -9129,15 +9129,15 @@
       </c>
       <c r="E48" s="12">
         <f t="shared" ref="E48" si="47">F48-D48</f>
-        <v>1449387</v>
+        <v>1449776</v>
       </c>
       <c r="F48" s="11">
         <f>SUM(F10:F47)</f>
-        <v>7677082</v>
+        <v>7677471</v>
       </c>
       <c r="G48" s="13">
         <f t="shared" ref="G48" si="48">F48/C48</f>
-        <v>0.99541855626045073</v>
+        <v>0.99546899441108982</v>
       </c>
       <c r="H48" s="10">
         <f>SUM(H10:H47)</f>
@@ -9149,15 +9149,15 @@
       </c>
       <c r="J48" s="12">
         <f t="shared" si="25"/>
-        <v>1415701</v>
+        <v>1416144</v>
       </c>
       <c r="K48" s="11">
         <f>SUM(K10:K47)</f>
-        <v>7772336</v>
+        <v>7772779</v>
       </c>
       <c r="L48" s="13">
         <f t="shared" si="26"/>
-        <v>0.98792375164985791</v>
+        <v>0.98798006036090447</v>
       </c>
       <c r="M48" s="10">
         <f>SUM(M10:M47)</f>
@@ -9169,15 +9169,15 @@
       </c>
       <c r="O48" s="12">
         <f t="shared" si="27"/>
-        <v>2192050</v>
+        <v>2192810</v>
       </c>
       <c r="P48" s="11">
         <f>SUM(P10:P47)</f>
-        <v>12049107</v>
+        <v>12049867</v>
       </c>
       <c r="Q48" s="13">
         <f t="shared" si="28"/>
-        <v>0.99151227278696985</v>
+        <v>0.99157481263555103</v>
       </c>
       <c r="R48" s="10">
         <f>SUM(R10:R47)</f>
@@ -9189,15 +9189,15 @@
       </c>
       <c r="T48" s="12">
         <f t="shared" ref="T48" si="49">U48-S48</f>
-        <v>1488482</v>
+        <v>1489053</v>
       </c>
       <c r="U48" s="11">
         <f>SUM(U10:U47)</f>
-        <v>7742934</v>
+        <v>7743505</v>
       </c>
       <c r="V48" s="13">
         <f t="shared" si="30"/>
-        <v>0.99193442697715684</v>
+        <v>0.99200757683970298</v>
       </c>
       <c r="W48" s="10">
         <f>SUM(W10:W47)</f>
@@ -9209,15 +9209,15 @@
       </c>
       <c r="Y48" s="12">
         <f t="shared" si="31"/>
-        <v>1483954</v>
+        <v>1484581</v>
       </c>
       <c r="Z48" s="11">
         <f>SUM(Z10:Z47)</f>
-        <v>7827398</v>
+        <v>7828025</v>
       </c>
       <c r="AA48" s="13">
         <f t="shared" si="32"/>
-        <v>0.98484706078928952</v>
+        <v>0.98492595023724083</v>
       </c>
       <c r="AB48" s="10">
         <f>SUM(AB10:AB47)</f>
@@ -9229,15 +9229,15 @@
       </c>
       <c r="AD48" s="12">
         <f t="shared" si="33"/>
-        <v>2327768</v>
+        <v>2328872</v>
       </c>
       <c r="AE48" s="11">
         <f>SUM(AE10:AE47)</f>
-        <v>12194615</v>
+        <v>12195719</v>
       </c>
       <c r="AF48" s="13">
         <f t="shared" si="34"/>
-        <v>0.99270899585556349</v>
+        <v>0.9927988675515067</v>
       </c>
       <c r="AG48" s="10">
         <f>SUM(AG10:AG47)</f>
@@ -9249,15 +9249,15 @@
       </c>
       <c r="AI48" s="12">
         <f t="shared" si="35"/>
-        <v>1607855</v>
+        <v>1608662</v>
       </c>
       <c r="AJ48" s="11">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7874033</v>
+        <v>7874840</v>
       </c>
       <c r="AK48" s="13">
         <f t="shared" si="36"/>
-        <v>0.99239348829260388</v>
+        <v>0.9924951974859807</v>
       </c>
       <c r="AL48" s="10">
         <f>SUM(AL10:AL47)</f>
@@ -9269,15 +9269,15 @@
       </c>
       <c r="AN48" s="12">
         <f t="shared" si="37"/>
-        <v>1381766</v>
+        <v>1382649</v>
       </c>
       <c r="AO48" s="11">
         <f>SUM(AO10:AO47)</f>
-        <v>7956145</v>
+        <v>7957028</v>
       </c>
       <c r="AP48" s="13">
         <f t="shared" si="38"/>
-        <v>0.98485704669333096</v>
+        <v>0.98496634947404071</v>
       </c>
       <c r="AQ48" s="10">
         <f>SUM(AQ10:AQ47)</f>
@@ -9289,15 +9289,15 @@
       </c>
       <c r="AS48" s="12">
         <f t="shared" si="39"/>
-        <v>2137572</v>
+        <v>2139071</v>
       </c>
       <c r="AT48" s="11">
         <f>SUM(AT10:AT47)</f>
-        <v>12386289</v>
+        <v>12387788</v>
       </c>
       <c r="AU48" s="13">
         <f t="shared" si="40"/>
-        <v>0.99526268906215276</v>
+        <v>0.99538313666117972</v>
       </c>
       <c r="AV48" s="10">
         <f>SUM(AV10:AV47)</f>
@@ -9309,15 +9309,15 @@
       </c>
       <c r="AX48" s="12">
         <f t="shared" si="41"/>
-        <v>1371617</v>
+        <v>1372653</v>
       </c>
       <c r="AY48" s="11">
         <f>SUM(AY10:AY47)</f>
-        <v>8012832</v>
+        <v>8013868</v>
       </c>
       <c r="AZ48" s="13">
         <f t="shared" si="42"/>
-        <v>0.99398313133207694</v>
+        <v>0.99411164601004098</v>
       </c>
       <c r="BA48" s="10">
         <f>SUM(BA10:BA47)</f>
@@ -9329,15 +9329,15 @@
       </c>
       <c r="BC48" s="12">
         <f t="shared" si="43"/>
-        <v>1319735</v>
+        <v>1320879</v>
       </c>
       <c r="BD48" s="11">
         <f>SUM(BD10:BD47)</f>
-        <v>8096913</v>
+        <v>8098057</v>
       </c>
       <c r="BE48" s="13">
         <f t="shared" si="44"/>
-        <v>0.98713287668143257</v>
+        <v>0.98727234712046574</v>
       </c>
       <c r="BF48" s="10">
         <f>SUM(BF10:BF47)</f>
@@ -9349,15 +9349,15 @@
       </c>
       <c r="BH48" s="12">
         <f t="shared" si="45"/>
-        <v>2707309</v>
+        <v>2709422</v>
       </c>
       <c r="BI48" s="11">
         <f>SUM(BI10:BI47)</f>
-        <v>12553790</v>
+        <v>12555903</v>
       </c>
       <c r="BJ48" s="13">
         <f t="shared" si="46"/>
-        <v>0.99191928609693691</v>
+        <v>0.99208624168975179</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
@@ -9496,6 +9496,61 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
+      <c r="AC51" s="1"/>
+      <c r="AD51" s="1"/>
+      <c r="AE51" s="1"/>
+      <c r="AF51" s="1"/>
+      <c r="AG51" s="1"/>
+      <c r="AH51" s="1"/>
+      <c r="AI51" s="1"/>
+      <c r="AJ51" s="1"/>
+      <c r="AK51" s="1"/>
+      <c r="AL51" s="1"/>
+      <c r="AM51" s="1"/>
+      <c r="AN51" s="1"/>
+      <c r="AO51" s="1"/>
+      <c r="AP51" s="1"/>
+      <c r="AQ51" s="1"/>
+      <c r="AR51" s="1"/>
+      <c r="AS51" s="1"/>
+      <c r="AT51" s="1"/>
+      <c r="AU51" s="1"/>
+      <c r="AV51" s="1"/>
+      <c r="AW51" s="1"/>
+      <c r="AX51" s="1"/>
+      <c r="AY51" s="1"/>
+      <c r="AZ51" s="1"/>
+      <c r="BA51" s="1"/>
+      <c r="BB51" s="1"/>
+      <c r="BC51" s="1"/>
+      <c r="BD51" s="1"/>
+      <c r="BE51" s="1"/>
+      <c r="BF51" s="1"/>
+      <c r="BG51" s="1"/>
+      <c r="BH51" s="1"/>
+      <c r="BI51" s="1"/>
+      <c r="BJ51" s="1"/>
     </row>
     <row r="52" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -9525,23 +9580,18 @@
       <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A55" s="26" t="s">
+      <c r="A55" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
       <c r="F55" s="6"/>
       <c r="G55" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="AV8:AZ8"/>
@@ -9555,6 +9605,11 @@
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2023-2024.xlsx
+++ b/gstdatabase/GSTR-3B-2023-2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F3E939-B3FB-4D22-BEB0-C6378C21B7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC45CEA-3FAA-4FC4-966E-C5E70D1F95F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2023-2024</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -415,6 +415,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -426,21 +441,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -741,12 +741,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -758,10 +758,10 @@
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="28"/>
+      <c r="B3" s="21"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -807,100 +807,100 @@
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:62" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="23">
         <v>45017</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="25">
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="23">
         <v>45047</v>
       </c>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="25">
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="23">
         <v>45078</v>
       </c>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="25">
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="23">
         <v>45108</v>
       </c>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-      <c r="V8" s="27"/>
-      <c r="W8" s="25">
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="23">
         <v>45139</v>
       </c>
-      <c r="X8" s="26"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="27"/>
-      <c r="AB8" s="25">
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="23">
         <v>45170</v>
       </c>
-      <c r="AC8" s="26"/>
-      <c r="AD8" s="26"/>
-      <c r="AE8" s="26"/>
-      <c r="AF8" s="27"/>
-      <c r="AG8" s="25">
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="23">
         <v>45200</v>
       </c>
-      <c r="AH8" s="26"/>
-      <c r="AI8" s="26"/>
-      <c r="AJ8" s="26"/>
-      <c r="AK8" s="27"/>
-      <c r="AL8" s="25">
+      <c r="AH8" s="24"/>
+      <c r="AI8" s="24"/>
+      <c r="AJ8" s="24"/>
+      <c r="AK8" s="25"/>
+      <c r="AL8" s="23">
         <v>45231</v>
       </c>
-      <c r="AM8" s="26"/>
-      <c r="AN8" s="26"/>
-      <c r="AO8" s="26"/>
-      <c r="AP8" s="27"/>
-      <c r="AQ8" s="25">
+      <c r="AM8" s="24"/>
+      <c r="AN8" s="24"/>
+      <c r="AO8" s="24"/>
+      <c r="AP8" s="25"/>
+      <c r="AQ8" s="23">
         <v>45261</v>
       </c>
-      <c r="AR8" s="26"/>
-      <c r="AS8" s="26"/>
-      <c r="AT8" s="26"/>
-      <c r="AU8" s="27"/>
-      <c r="AV8" s="25">
+      <c r="AR8" s="24"/>
+      <c r="AS8" s="24"/>
+      <c r="AT8" s="24"/>
+      <c r="AU8" s="25"/>
+      <c r="AV8" s="23">
         <v>45292</v>
       </c>
-      <c r="AW8" s="26"/>
-      <c r="AX8" s="26"/>
-      <c r="AY8" s="26"/>
-      <c r="AZ8" s="27"/>
-      <c r="BA8" s="25">
+      <c r="AW8" s="24"/>
+      <c r="AX8" s="24"/>
+      <c r="AY8" s="24"/>
+      <c r="AZ8" s="25"/>
+      <c r="BA8" s="23">
         <v>45323</v>
       </c>
-      <c r="BB8" s="26"/>
-      <c r="BC8" s="26"/>
-      <c r="BD8" s="26"/>
-      <c r="BE8" s="27"/>
-      <c r="BF8" s="25">
+      <c r="BB8" s="24"/>
+      <c r="BC8" s="24"/>
+      <c r="BD8" s="24"/>
+      <c r="BE8" s="25"/>
+      <c r="BF8" s="23">
         <v>45352</v>
       </c>
-      <c r="BG8" s="26"/>
-      <c r="BH8" s="26"/>
-      <c r="BI8" s="26"/>
-      <c r="BJ8" s="27"/>
+      <c r="BG8" s="24"/>
+      <c r="BH8" s="24"/>
+      <c r="BI8" s="24"/>
+      <c r="BJ8" s="25"/>
     </row>
     <row r="9" spans="1:62" s="16" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="24"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="17" t="s">
         <v>2</v>
       </c>
@@ -1165,14 +1165,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>14963</v>
+        <v>14964</v>
       </c>
       <c r="Z10" s="14">
-        <v>72991</v>
+        <v>72992</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>0.99513279162349344</v>
+        <v>0.99514642526040242</v>
       </c>
       <c r="AB10" s="8">
         <v>123554</v>
@@ -1182,14 +1182,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>25350</v>
+        <v>25351</v>
       </c>
       <c r="AE10" s="14">
-        <v>123354</v>
+        <v>123355</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.9983812745843923</v>
+        <v>0.99838936821147028</v>
       </c>
       <c r="AG10" s="8">
         <v>71950</v>
@@ -1284,14 +1284,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>30702</v>
+        <v>30704</v>
       </c>
       <c r="BI10" s="14">
-        <v>127902</v>
+        <v>127904</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.99822834799303828</v>
+        <v>0.99824395726182202</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1343,14 +1343,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>17896</v>
+        <v>17897</v>
       </c>
       <c r="P11" s="14">
-        <v>102362</v>
+        <v>102363</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>1.0011736859607598</v>
+        <v>1.0011834666770993</v>
       </c>
       <c r="R11" s="8">
         <v>44890</v>
@@ -1360,14 +1360,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>8657</v>
+        <v>8658</v>
       </c>
       <c r="U11" s="14">
-        <v>45094</v>
+        <v>45095</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>1.0045444419692582</v>
+        <v>1.004566718645578</v>
       </c>
       <c r="W11" s="8">
         <v>46425</v>
@@ -1377,14 +1377,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8815</v>
+        <v>8817</v>
       </c>
       <c r="Z11" s="14">
-        <v>46019</v>
+        <v>46021</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.99125471190091541</v>
+        <v>0.99129779213785674</v>
       </c>
       <c r="AB11" s="8">
         <v>103964</v>
@@ -1394,14 +1394,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>17247</v>
+        <v>17249</v>
       </c>
       <c r="AE11" s="14">
-        <v>104132</v>
+        <v>104134</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>1.0016159439806087</v>
+        <v>1.0016351814089492</v>
       </c>
       <c r="AG11" s="8">
         <v>45569</v>
@@ -1411,14 +1411,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>8682</v>
+        <v>8684</v>
       </c>
       <c r="AJ11" s="14">
-        <v>45671</v>
+        <v>45673</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>1.0022383637999517</v>
+        <v>1.0022822532862252</v>
       </c>
       <c r="AL11" s="8">
         <v>46951</v>
@@ -1428,14 +1428,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>7782</v>
+        <v>7784</v>
       </c>
       <c r="AO11" s="14">
-        <v>46367</v>
+        <v>46369</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.98756150028753387</v>
+        <v>0.98760409788928882</v>
       </c>
       <c r="AQ11" s="8">
         <v>105644</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>15131</v>
+        <v>15137</v>
       </c>
       <c r="AT11" s="14">
-        <v>105845</v>
+        <v>105851</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>1.0019026163341032</v>
+        <v>1.0019594108515391</v>
       </c>
       <c r="AV11" s="8">
         <v>46072</v>
@@ -1462,14 +1462,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>7550</v>
+        <v>7553</v>
       </c>
       <c r="AY11" s="14">
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>1.0027782601146031</v>
+        <v>1.0028433755860393</v>
       </c>
       <c r="BA11" s="8">
         <v>47252</v>
@@ -1479,14 +1479,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>7186</v>
+        <v>7187</v>
       </c>
       <c r="BD11" s="14">
-        <v>47001</v>
+        <v>47002</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.99468805553204098</v>
+        <v>0.99470921865741135</v>
       </c>
       <c r="BF11" s="8">
         <v>107665</v>
@@ -1496,14 +1496,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>19639</v>
+        <v>19643</v>
       </c>
       <c r="BI11" s="14">
-        <v>107529</v>
+        <v>107533</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.9987368225514327</v>
+        <v>0.99877397482933172</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1555,14 +1555,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>54200</v>
+        <v>54202</v>
       </c>
       <c r="P12" s="14">
-        <v>343202</v>
+        <v>343204</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.99514896701703515</v>
+        <v>0.99515476621964483</v>
       </c>
       <c r="R12" s="8">
         <v>167705</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>27008</v>
+        <v>27009</v>
       </c>
       <c r="U12" s="14">
-        <v>167150</v>
+        <v>167151</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.99669061745326615</v>
+        <v>0.99669658030470176</v>
       </c>
       <c r="W12" s="8">
         <v>171864</v>
@@ -1606,14 +1606,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>58554</v>
+        <v>58558</v>
       </c>
       <c r="AE12" s="14">
-        <v>348023</v>
+        <v>348027</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.99706344113130574</v>
+        <v>0.99707490087323236</v>
       </c>
       <c r="AG12" s="8">
         <v>170526</v>
@@ -1623,14 +1623,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>27740</v>
+        <v>27744</v>
       </c>
       <c r="AJ12" s="14">
-        <v>170184</v>
+        <v>170188</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.99799444073044574</v>
+        <v>0.99801789756400783</v>
       </c>
       <c r="AL12" s="8">
         <v>174892</v>
@@ -1657,14 +1657,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>50886</v>
+        <v>50894</v>
       </c>
       <c r="AT12" s="14">
-        <v>352796</v>
+        <v>352804</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.99775728317340184</v>
+        <v>0.99777990831162733</v>
       </c>
       <c r="AV12" s="8">
         <v>172980</v>
@@ -1674,14 +1674,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>24625</v>
+        <v>24627</v>
       </c>
       <c r="AY12" s="14">
-        <v>172342</v>
+        <v>172344</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.99631171233668636</v>
+        <v>0.99632327436697887</v>
       </c>
       <c r="BA12" s="8">
         <v>177212</v>
@@ -1691,14 +1691,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>24036</v>
+        <v>24040</v>
       </c>
       <c r="BD12" s="14">
-        <v>174787</v>
+        <v>174791</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.98631582511342342</v>
+        <v>0.98633839694828795</v>
       </c>
       <c r="BF12" s="8">
         <v>359260</v>
@@ -1708,14 +1708,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>65701</v>
+        <v>65710</v>
       </c>
       <c r="BI12" s="14">
-        <v>357407</v>
+        <v>357416</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.99484217558314314</v>
+        <v>0.99486722707788233</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1945,14 +1945,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>18157</v>
+        <v>18160</v>
       </c>
       <c r="F14" s="14">
-        <v>85316</v>
+        <v>85319</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.99921530046964857</v>
+        <v>0.99925043626951504</v>
       </c>
       <c r="H14" s="8">
         <v>88261</v>
@@ -1962,14 +1962,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18270</v>
+        <v>18273</v>
       </c>
       <c r="K14" s="14">
-        <v>87139</v>
+        <v>87142</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.98728770351570905</v>
+        <v>0.98732169361326072</v>
       </c>
       <c r="M14" s="8">
         <v>157146</v>
@@ -1979,14 +1979,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>32103</v>
+        <v>32108</v>
       </c>
       <c r="P14" s="14">
-        <v>155504</v>
+        <v>155509</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.98955111806854767</v>
+        <v>0.989582935614015</v>
       </c>
       <c r="R14" s="8">
         <v>86469</v>
@@ -1996,14 +1996,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18341</v>
+        <v>18345</v>
       </c>
       <c r="U14" s="14">
-        <v>85406</v>
+        <v>85410</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.98770657692352171</v>
+        <v>0.98775283627658472</v>
       </c>
       <c r="W14" s="8">
         <v>88169</v>
@@ -2013,14 +2013,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>17855</v>
+        <v>17862</v>
       </c>
       <c r="Z14" s="14">
-        <v>86563</v>
+        <v>86570</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.98178498111581169</v>
+        <v>0.98186437409974026</v>
       </c>
       <c r="AB14" s="8">
         <v>157930</v>
@@ -2030,14 +2030,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>33743</v>
+        <v>33751</v>
       </c>
       <c r="AE14" s="14">
-        <v>157168</v>
+        <v>157176</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.9951750775660102</v>
+        <v>0.995225732919648</v>
       </c>
       <c r="AG14" s="8">
         <v>87312</v>
@@ -2047,14 +2047,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>19589</v>
+        <v>19597</v>
       </c>
       <c r="AJ14" s="14">
-        <v>86921</v>
+        <v>86929</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.9955218068535826</v>
+        <v>0.99561343228880339</v>
       </c>
       <c r="AL14" s="8">
         <v>89337</v>
@@ -2064,14 +2064,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>16985</v>
+        <v>16995</v>
       </c>
       <c r="AO14" s="14">
-        <v>87925</v>
+        <v>87935</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.98419467857662557</v>
+        <v>0.98430661428075716</v>
       </c>
       <c r="AQ14" s="8">
         <v>160173</v>
@@ -2081,14 +2081,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>29850</v>
+        <v>29862</v>
       </c>
       <c r="AT14" s="14">
-        <v>160291</v>
+        <v>160303</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>1.0007367034394061</v>
+        <v>1.000811622433244</v>
       </c>
       <c r="AV14" s="8">
         <v>88523</v>
@@ -2098,14 +2098,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>17220</v>
+        <v>17229</v>
       </c>
       <c r="AY14" s="14">
-        <v>88580</v>
+        <v>88589</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>1.000643900455249</v>
+        <v>1.000745568948183</v>
       </c>
       <c r="BA14" s="8">
         <v>90782</v>
@@ -2115,14 +2115,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>16185</v>
+        <v>16194</v>
       </c>
       <c r="BD14" s="14">
-        <v>89766</v>
+        <v>89775</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.98880835407900247</v>
+        <v>0.9889074926747593</v>
       </c>
       <c r="BF14" s="8">
         <v>163900</v>
@@ -2132,14 +2132,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>39478</v>
+        <v>39490</v>
       </c>
       <c r="BI14" s="14">
-        <v>162838</v>
+        <v>162850</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.99352043929225142</v>
+        <v>0.99359365466748018</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2259,14 +2259,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>54939</v>
+        <v>54940</v>
       </c>
       <c r="AJ15" s="14">
-        <v>289857</v>
+        <v>289858</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.99241965138613553</v>
+        <v>0.99242307521116446</v>
       </c>
       <c r="AL15" s="8">
         <v>298411</v>
@@ -2276,14 +2276,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>47361</v>
+        <v>47362</v>
       </c>
       <c r="AO15" s="14">
-        <v>293455</v>
+        <v>293456</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>0.98339203313550771</v>
+        <v>0.98339538421841022</v>
       </c>
       <c r="AQ15" s="8">
         <v>502913</v>
@@ -2293,14 +2293,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>75295</v>
+        <v>75296</v>
       </c>
       <c r="AT15" s="14">
-        <v>498854</v>
+        <v>498855</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.9919290215206209</v>
+        <v>0.99193100993611216</v>
       </c>
       <c r="AV15" s="8">
         <v>298012</v>
@@ -2310,14 +2310,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>47948</v>
+        <v>47949</v>
       </c>
       <c r="AY15" s="14">
-        <v>295215</v>
+        <v>295216</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>0.99061447190046037</v>
+        <v>0.9906178274700348</v>
       </c>
       <c r="BA15" s="8">
         <v>303376</v>
@@ -2327,14 +2327,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>45511</v>
+        <v>45513</v>
       </c>
       <c r="BD15" s="14">
-        <v>299089</v>
+        <v>299091</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.98586902062127524</v>
+        <v>0.98587561310057481</v>
       </c>
       <c r="BF15" s="8">
         <v>511329</v>
@@ -2344,14 +2344,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>92291</v>
+        <v>92296</v>
       </c>
       <c r="BI15" s="14">
-        <v>506557</v>
+        <v>506562</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.99066745676462709</v>
+        <v>0.99067723520473117</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2369,14 +2369,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>73101</v>
+        <v>73108</v>
       </c>
       <c r="F16" s="14">
-        <v>427868</v>
+        <v>427875</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.99357460494386196</v>
+        <v>0.99359086000905639</v>
       </c>
       <c r="H16" s="8">
         <v>441093</v>
@@ -2386,14 +2386,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>74301</v>
+        <v>74308</v>
       </c>
       <c r="K16" s="14">
-        <v>432686</v>
+        <v>432693</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.98094052728109493</v>
+        <v>0.98095639695030301</v>
       </c>
       <c r="M16" s="8">
         <v>754668</v>
@@ -2403,14 +2403,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>125371</v>
+        <v>125384</v>
       </c>
       <c r="P16" s="14">
-        <v>749341</v>
+        <v>749354</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.99294126688822104</v>
+        <v>0.9929584930061961</v>
       </c>
       <c r="R16" s="8">
         <v>429537</v>
@@ -2420,14 +2420,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>78662</v>
+        <v>78671</v>
       </c>
       <c r="U16" s="14">
-        <v>424912</v>
+        <v>424921</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.98923259230287497</v>
+        <v>0.98925354509623153</v>
       </c>
       <c r="W16" s="8">
         <v>433887</v>
@@ -2437,14 +2437,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>76001</v>
+        <v>76011</v>
       </c>
       <c r="Z16" s="14">
-        <v>427127</v>
+        <v>427137</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.98441990656553435</v>
+        <v>0.98444295404102911</v>
       </c>
       <c r="AB16" s="8">
         <v>753330</v>
@@ -2454,14 +2454,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>135871</v>
+        <v>135891</v>
       </c>
       <c r="AE16" s="14">
-        <v>750076</v>
+        <v>750096</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.99568051186067197</v>
+        <v>0.9957070606507108</v>
       </c>
       <c r="AG16" s="8">
         <v>431686</v>
@@ -2471,14 +2471,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>82759</v>
+        <v>82772</v>
       </c>
       <c r="AJ16" s="14">
-        <v>426937</v>
+        <v>426950</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.98899894830965096</v>
+        <v>0.98902906279101011</v>
       </c>
       <c r="AL16" s="8">
         <v>438911</v>
@@ -2488,14 +2488,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>73998</v>
+        <v>74016</v>
       </c>
       <c r="AO16" s="14">
-        <v>430579</v>
+        <v>430597</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.9810166525787688</v>
+        <v>0.98105766317089338</v>
       </c>
       <c r="AQ16" s="8">
         <v>759875</v>
@@ -2505,14 +2505,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>119968</v>
+        <v>119995</v>
       </c>
       <c r="AT16" s="14">
-        <v>756863</v>
+        <v>756890</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.99603619016285572</v>
+        <v>0.99607172232275043</v>
       </c>
       <c r="AV16" s="8">
         <v>437477</v>
@@ -2522,14 +2522,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>69851</v>
+        <v>69872</v>
       </c>
       <c r="AY16" s="14">
-        <v>432328</v>
+        <v>432349</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.98823023838967539</v>
+        <v>0.98827824091323657</v>
       </c>
       <c r="BA16" s="8">
         <v>445887</v>
@@ -2539,14 +2539,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>70489</v>
+        <v>70511</v>
       </c>
       <c r="BD16" s="14">
-        <v>437154</v>
+        <v>437176</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98041432022014541</v>
+        <v>0.98046366007531061</v>
       </c>
       <c r="BF16" s="8">
         <v>770088</v>
@@ -2556,14 +2556,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>139349</v>
+        <v>139390</v>
       </c>
       <c r="BI16" s="14">
-        <v>762904</v>
+        <v>762945</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.99067119601915621</v>
+        <v>0.99072443668775512</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2581,14 +2581,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>52698</v>
+        <v>52702</v>
       </c>
       <c r="F17" s="14">
-        <v>303716</v>
+        <v>303720</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>1.003774283315817</v>
+        <v>1.0037875032223522</v>
       </c>
       <c r="H17" s="8">
         <v>314962</v>
@@ -2598,14 +2598,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>52682</v>
+        <v>52687</v>
       </c>
       <c r="K17" s="14">
-        <v>311309</v>
+        <v>311314</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98840177545227681</v>
+        <v>0.98841765038322082</v>
       </c>
       <c r="M17" s="8">
         <v>695415</v>
@@ -2615,14 +2615,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>119289</v>
+        <v>119307</v>
       </c>
       <c r="P17" s="14">
-        <v>689950</v>
+        <v>689968</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.99214138320283574</v>
+        <v>0.99216726702760227</v>
       </c>
       <c r="R17" s="8">
         <v>305324</v>
@@ -2632,14 +2632,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>55815</v>
+        <v>55821</v>
       </c>
       <c r="U17" s="14">
-        <v>304483</v>
+        <v>304489</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>0.99724554899058049</v>
+        <v>0.99726520024629572</v>
       </c>
       <c r="W17" s="8">
         <v>316716</v>
@@ -2649,14 +2649,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>55803</v>
+        <v>55809</v>
       </c>
       <c r="Z17" s="14">
-        <v>310515</v>
+        <v>310521</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.98042094494752396</v>
+        <v>0.98043988936460424</v>
       </c>
       <c r="AB17" s="8">
         <v>703511</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>130776</v>
+        <v>130800</v>
       </c>
       <c r="AE17" s="14">
-        <v>698060</v>
+        <v>698084</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.99225172030003794</v>
+        <v>0.99228583490521116</v>
       </c>
       <c r="AG17" s="8">
         <v>311084</v>
@@ -2683,14 +2683,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>63023</v>
+        <v>63034</v>
       </c>
       <c r="AJ17" s="14">
-        <v>310702</v>
+        <v>310713</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.99877203584883822</v>
+        <v>0.99880739607308633</v>
       </c>
       <c r="AL17" s="8">
         <v>323550</v>
@@ -2700,14 +2700,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>52091</v>
+        <v>52100</v>
       </c>
       <c r="AO17" s="14">
-        <v>317162</v>
+        <v>317171</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.98025652912996442</v>
+        <v>0.98028434554164734</v>
       </c>
       <c r="AQ17" s="8">
         <v>714257</v>
@@ -2717,14 +2717,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>112841</v>
+        <v>112870</v>
       </c>
       <c r="AT17" s="14">
-        <v>712789</v>
+        <v>712818</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.99794471737763857</v>
+        <v>0.99798531900982423</v>
       </c>
       <c r="AV17" s="8">
         <v>316308</v>
@@ -2734,14 +2734,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>51096</v>
+        <v>51105</v>
       </c>
       <c r="AY17" s="14">
-        <v>316428</v>
+        <v>316437</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>1.0003793770628628</v>
+        <v>1.0004078303425774</v>
       </c>
       <c r="BA17" s="8">
         <v>328067</v>
@@ -2751,14 +2751,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>47144</v>
+        <v>47157</v>
       </c>
       <c r="BD17" s="14">
-        <v>322698</v>
+        <v>322711</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.98363444052586824</v>
+        <v>0.98367406657786371</v>
       </c>
       <c r="BF17" s="8">
         <v>726752</v>
@@ -2768,14 +2768,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>143821</v>
+        <v>143860</v>
       </c>
       <c r="BI17" s="14">
-        <v>723873</v>
+        <v>723912</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.996038538593633</v>
+        <v>0.99609220201664395</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2793,14 +2793,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>166631</v>
+        <v>166635</v>
       </c>
       <c r="F18" s="14">
-        <v>919262</v>
+        <v>919266</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99785722659557374</v>
+        <v>0.99786156858828789</v>
       </c>
       <c r="H18" s="8">
         <v>943261</v>
@@ -2810,14 +2810,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>163833</v>
+        <v>163842</v>
       </c>
       <c r="K18" s="14">
-        <v>933261</v>
+        <v>933270</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.98939848037817746</v>
+        <v>0.98940802174583709</v>
       </c>
       <c r="M18" s="8">
         <v>1440086</v>
@@ -2827,14 +2827,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>251730</v>
+        <v>251750</v>
       </c>
       <c r="P18" s="14">
-        <v>1426788</v>
+        <v>1426808</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.99076582926297452</v>
+        <v>0.99077971732243764</v>
       </c>
       <c r="R18" s="8">
         <v>938677</v>
@@ -2844,14 +2844,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>170662</v>
+        <v>170672</v>
       </c>
       <c r="U18" s="14">
-        <v>929330</v>
+        <v>929340</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.99004236814154389</v>
+        <v>0.99005302143335783</v>
       </c>
       <c r="W18" s="8">
         <v>958009</v>
@@ -2861,14 +2861,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>169064</v>
+        <v>169075</v>
       </c>
       <c r="Z18" s="14">
-        <v>943635</v>
+        <v>943646</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.98499596559113745</v>
+        <v>0.98500744773796489</v>
       </c>
       <c r="AB18" s="8">
         <v>1463397</v>
@@ -2878,14 +2878,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>274167</v>
+        <v>274193</v>
       </c>
       <c r="AE18" s="14">
-        <v>1451159</v>
+        <v>1451185</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.99163726589572077</v>
+        <v>0.99165503277647826</v>
       </c>
       <c r="AG18" s="8">
         <v>959088</v>
@@ -2895,14 +2895,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>195097</v>
+        <v>195115</v>
       </c>
       <c r="AJ18" s="14">
-        <v>951950</v>
+        <v>951968</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.99255751297065542</v>
+        <v>0.99257628080009341</v>
       </c>
       <c r="AL18" s="8">
         <v>980581</v>
@@ -2912,14 +2912,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>166785</v>
+        <v>166809</v>
       </c>
       <c r="AO18" s="14">
-        <v>964327</v>
+        <v>964351</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.98342411284738329</v>
+        <v>0.98344858813295388</v>
       </c>
       <c r="AQ18" s="8">
         <v>1490329</v>
@@ -2929,14 +2929,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>246061</v>
+        <v>246097</v>
       </c>
       <c r="AT18" s="14">
-        <v>1482537</v>
+        <v>1482573</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.99477162425209464</v>
+        <v>0.99479577999220303</v>
       </c>
       <c r="AV18" s="8">
         <v>983291</v>
@@ -2946,14 +2946,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>170108</v>
+        <v>170134</v>
       </c>
       <c r="AY18" s="14">
-        <v>975864</v>
+        <v>975890</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.99244679347212572</v>
+        <v>0.99247323528843445</v>
       </c>
       <c r="BA18" s="8">
         <v>1002255</v>
@@ -2963,14 +2963,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>160619</v>
+        <v>160648</v>
       </c>
       <c r="BD18" s="14">
-        <v>988220</v>
+        <v>988249</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.98599657771724758</v>
+        <v>0.98602551246938153</v>
       </c>
       <c r="BF18" s="8">
         <v>1522890</v>
@@ -2980,14 +2980,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>329235</v>
+        <v>329290</v>
       </c>
       <c r="BI18" s="14">
-        <v>1508976</v>
+        <v>1509031</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.99086342414750905</v>
+        <v>0.99089953969098232</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3005,14 +3005,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>63737</v>
+        <v>63743</v>
       </c>
       <c r="F19" s="14">
-        <v>271480</v>
+        <v>271486</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.98650048147677105</v>
+        <v>0.98652228419847743</v>
       </c>
       <c r="H19" s="8">
         <v>285702</v>
@@ -3022,14 +3022,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>60450</v>
+        <v>60457</v>
       </c>
       <c r="K19" s="14">
-        <v>277212</v>
+        <v>277219</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.97028372220005465</v>
+        <v>0.97030822325359989</v>
       </c>
       <c r="M19" s="8">
         <v>479092</v>
@@ -3039,14 +3039,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>93773</v>
+        <v>93783</v>
       </c>
       <c r="P19" s="14">
-        <v>468678</v>
+        <v>468688</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.97826304759837357</v>
+        <v>0.97828392041612044</v>
       </c>
       <c r="R19" s="8">
         <v>279649</v>
@@ -3056,14 +3056,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>57739</v>
+        <v>57749</v>
       </c>
       <c r="U19" s="14">
-        <v>272783</v>
+        <v>272793</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.97544779348397459</v>
+        <v>0.97548355259629038</v>
       </c>
       <c r="W19" s="8">
         <v>287758</v>
@@ -3073,14 +3073,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>59210</v>
+        <v>59222</v>
       </c>
       <c r="Z19" s="14">
-        <v>276630</v>
+        <v>276642</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.96132861640684186</v>
+        <v>0.96137031811452678</v>
       </c>
       <c r="AB19" s="8">
         <v>485015</v>
@@ -3090,14 +3090,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>101764</v>
+        <v>101779</v>
       </c>
       <c r="AE19" s="14">
-        <v>474950</v>
+        <v>474965</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.97924806449285073</v>
+        <v>0.97927899137140084</v>
       </c>
       <c r="AG19" s="8">
         <v>283525</v>
@@ -3107,14 +3107,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>74591</v>
+        <v>74607</v>
       </c>
       <c r="AJ19" s="14">
-        <v>276694</v>
+        <v>276710</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.97590688651794377</v>
+        <v>0.97596331893131116</v>
       </c>
       <c r="AL19" s="8">
         <v>295027</v>
@@ -3124,14 +3124,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>58060</v>
+        <v>58079</v>
       </c>
       <c r="AO19" s="14">
-        <v>282138</v>
+        <v>282157</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.95631247309568279</v>
+        <v>0.95637687398102544</v>
       </c>
       <c r="AQ19" s="8">
         <v>494059</v>
@@ -3141,14 +3141,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>91547</v>
+        <v>91580</v>
       </c>
       <c r="AT19" s="14">
-        <v>486335</v>
+        <v>486368</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.98436623965963577</v>
+        <v>0.98443303330169074</v>
       </c>
       <c r="AV19" s="8">
         <v>287237</v>
@@ -3158,14 +3158,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>56617</v>
+        <v>56638</v>
       </c>
       <c r="AY19" s="14">
-        <v>283367</v>
+        <v>283388</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.98652680539067039</v>
+        <v>0.98659991574901562</v>
       </c>
       <c r="BA19" s="8">
         <v>298081</v>
@@ -3175,14 +3175,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>54972</v>
+        <v>54995</v>
       </c>
       <c r="BD19" s="14">
-        <v>287483</v>
+        <v>287506</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.96444590564309696</v>
+        <v>0.96452306587806669</v>
       </c>
       <c r="BF19" s="8">
         <v>503654</v>
@@ -3192,14 +3192,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>132271</v>
+        <v>132311</v>
       </c>
       <c r="BI19" s="14">
-        <v>492667</v>
+        <v>492707</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.97818542094374317</v>
+        <v>0.97826484054529494</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3336,14 +3336,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="AO20" s="14">
-        <v>6244</v>
+        <v>6245</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.99904000000000004</v>
+        <v>0.99919999999999998</v>
       </c>
       <c r="AQ20" s="8">
         <v>9632</v>
@@ -3353,14 +3353,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="AT20" s="14">
-        <v>9729</v>
+        <v>9730</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>1.0100705980066444</v>
+        <v>1.0101744186046511</v>
       </c>
       <c r="AV20" s="8">
         <v>6297</v>
@@ -3387,14 +3387,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="BD20" s="14">
-        <v>6298</v>
+        <v>6299</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>0.98931825322023248</v>
+        <v>0.9894753377316996</v>
       </c>
       <c r="BF20" s="8">
         <v>9853</v>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="BI20" s="14">
-        <v>9880</v>
+        <v>9881</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>1.0027402821475693</v>
+        <v>1.0028417740789608</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3429,14 +3429,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>3692</v>
+        <v>3695</v>
       </c>
       <c r="F21" s="14">
-        <v>9826</v>
+        <v>9829</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>1.0266429840142095</v>
+        <v>1.026956430884965</v>
       </c>
       <c r="H21" s="8">
         <v>10057</v>
@@ -3446,14 +3446,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3490</v>
+        <v>3493</v>
       </c>
       <c r="K21" s="14">
-        <v>9969</v>
+        <v>9972</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.99124987570846179</v>
+        <v>0.99154817540021878</v>
       </c>
       <c r="M21" s="8">
         <v>12982</v>
@@ -3463,14 +3463,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>4291</v>
+        <v>4298</v>
       </c>
       <c r="P21" s="14">
-        <v>13232</v>
+        <v>13239</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>1.0192574333692805</v>
+        <v>1.0197966415036204</v>
       </c>
       <c r="R21" s="8">
         <v>9811</v>
@@ -3480,14 +3480,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3468</v>
+        <v>3473</v>
       </c>
       <c r="U21" s="14">
-        <v>10029</v>
+        <v>10034</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>1.0222199571909081</v>
+        <v>1.0227295892365711</v>
       </c>
       <c r="W21" s="8">
         <v>10152</v>
@@ -3497,14 +3497,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3288</v>
+        <v>3292</v>
       </c>
       <c r="Z21" s="14">
-        <v>10174</v>
+        <v>10178</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>1.0021670606776989</v>
+        <v>1.002561071710008</v>
       </c>
       <c r="AB21" s="8">
         <v>13231</v>
@@ -3514,14 +3514,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4348</v>
+        <v>4355</v>
       </c>
       <c r="AE21" s="14">
-        <v>13558</v>
+        <v>13565</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>1.024714685208979</v>
+        <v>1.0252437457486208</v>
       </c>
       <c r="AG21" s="8">
         <v>10040</v>
@@ -3531,14 +3531,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3816</v>
+        <v>3821</v>
       </c>
       <c r="AJ21" s="14">
-        <v>10244</v>
+        <v>10249</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>1.0203187250996015</v>
+        <v>1.0208167330677291</v>
       </c>
       <c r="AL21" s="8">
         <v>10211</v>
@@ -3548,14 +3548,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3448</v>
+        <v>3453</v>
       </c>
       <c r="AO21" s="14">
-        <v>10395</v>
+        <v>10400</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>1.0180197825874058</v>
+        <v>1.0185094505924983</v>
       </c>
       <c r="AQ21" s="8">
         <v>13473</v>
@@ -3565,14 +3565,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4281</v>
+        <v>4289</v>
       </c>
       <c r="AT21" s="14">
-        <v>13884</v>
+        <v>13892</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>1.0305054553551547</v>
+        <v>1.031099235508053</v>
       </c>
       <c r="AV21" s="8">
         <v>10213</v>
@@ -3582,14 +3582,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3522</v>
+        <v>3528</v>
       </c>
       <c r="AY21" s="14">
-        <v>10505</v>
+        <v>10511</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>1.0285910114559875</v>
+        <v>1.0291784979927543</v>
       </c>
       <c r="BA21" s="8">
         <v>10449</v>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3332</v>
+        <v>3338</v>
       </c>
       <c r="BD21" s="14">
-        <v>10630</v>
+        <v>10636</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>1.0173222317925161</v>
+        <v>1.0178964494209972</v>
       </c>
       <c r="BF21" s="8">
         <v>13925</v>
@@ -3616,14 +3616,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>6485</v>
+        <v>6496</v>
       </c>
       <c r="BI21" s="14">
-        <v>14312</v>
+        <v>14323</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>1.0277917414721724</v>
+        <v>1.0285816876122083</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3641,14 +3641,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="F22" s="14">
-        <v>6225</v>
+        <v>6227</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>1.0107160253287872</v>
+        <v>1.0110407533690535</v>
       </c>
       <c r="H22" s="8">
         <v>6265</v>
@@ -3658,14 +3658,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="K22" s="14">
-        <v>6307</v>
+        <v>6309</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>1.0067039106145252</v>
+        <v>1.007023144453312</v>
       </c>
       <c r="M22" s="8">
         <v>7537</v>
@@ -3675,14 +3675,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="P22" s="14">
-        <v>7595</v>
+        <v>7597</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>1.0076953695104154</v>
+        <v>1.0079607270797399</v>
       </c>
       <c r="R22" s="8">
         <v>6306</v>
@@ -3692,14 +3692,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="U22" s="14">
-        <v>6362</v>
+        <v>6364</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>1.0088804313352362</v>
+        <v>1.009197589597209</v>
       </c>
       <c r="W22" s="8">
         <v>6435</v>
@@ -3709,14 +3709,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="Z22" s="14">
-        <v>6435</v>
+        <v>6437</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0003108003108003</v>
       </c>
       <c r="AB22" s="8">
         <v>7668</v>
@@ -3726,14 +3726,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="AE22" s="14">
-        <v>7710</v>
+        <v>7712</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>1.0054773082942097</v>
+        <v>1.0057381324986958</v>
       </c>
       <c r="AG22" s="8">
         <v>6422</v>
@@ -3743,14 +3743,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="AJ22" s="14">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>1.004827156649019</v>
+        <v>1.005138586110246</v>
       </c>
       <c r="AL22" s="8">
         <v>6508</v>
@@ -3760,14 +3760,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="AO22" s="14">
-        <v>6501</v>
+        <v>6502</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.99892440073755373</v>
+        <v>0.9990780577750461</v>
       </c>
       <c r="AQ22" s="8">
         <v>7781</v>
@@ -3777,14 +3777,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="AT22" s="14">
-        <v>7808</v>
+        <v>7809</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>1.003469991003727</v>
+        <v>1.0035985091890502</v>
       </c>
       <c r="AV22" s="8">
         <v>6603</v>
@@ -3794,14 +3794,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="AY22" s="14">
-        <v>6517</v>
+        <v>6518</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.98697561714372251</v>
+        <v>0.98712706345600487</v>
       </c>
       <c r="BA22" s="8">
         <v>6608</v>
@@ -3811,14 +3811,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="BD22" s="14">
-        <v>6557</v>
+        <v>6559</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>0.99228208232445525</v>
+        <v>0.99258474576271183</v>
       </c>
       <c r="BF22" s="8">
         <v>7906</v>
@@ -3828,14 +3828,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2449</v>
+        <v>2452</v>
       </c>
       <c r="BI22" s="14">
-        <v>7947</v>
+        <v>7950</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>1.005185934733114</v>
+        <v>1.0055653933721225</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3853,14 +3853,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>5983</v>
+        <v>5984</v>
       </c>
       <c r="F23" s="14">
-        <v>8470</v>
+        <v>8471</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.96250000000000002</v>
+        <v>0.96261363636363639</v>
       </c>
       <c r="H23" s="8">
         <v>8763</v>
@@ -3870,14 +3870,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>5147</v>
+        <v>5148</v>
       </c>
       <c r="K23" s="14">
-        <v>8499</v>
+        <v>8500</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.96987333105100992</v>
+        <v>0.96998744722127128</v>
       </c>
       <c r="M23" s="8">
         <v>10654</v>
@@ -3887,14 +3887,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>5544</v>
+        <v>5545</v>
       </c>
       <c r="P23" s="14">
-        <v>10476</v>
+        <v>10477</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.98329266003379012</v>
+        <v>0.98338652149427441</v>
       </c>
       <c r="R23" s="8">
         <v>8621</v>
@@ -3904,14 +3904,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>3749</v>
+        <v>3750</v>
       </c>
       <c r="U23" s="14">
-        <v>8393</v>
+        <v>8394</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.97355295209372461</v>
+        <v>0.97366894791787495</v>
       </c>
       <c r="W23" s="8">
         <v>8774</v>
@@ -3921,14 +3921,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>3698</v>
+        <v>3699</v>
       </c>
       <c r="Z23" s="14">
-        <v>8429</v>
+        <v>8430</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.96067927968999312</v>
+        <v>0.96079325279234096</v>
       </c>
       <c r="AB23" s="8">
         <v>10734</v>
@@ -3938,14 +3938,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3663</v>
+        <v>3664</v>
       </c>
       <c r="AE23" s="14">
-        <v>10551</v>
+        <v>10552</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.98295136948015649</v>
+        <v>0.98304453139556547</v>
       </c>
       <c r="AG23" s="8">
         <v>8589</v>
@@ -3955,14 +3955,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="AJ23" s="14">
-        <v>8440</v>
+        <v>8441</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.98265222959599485</v>
+        <v>0.98276865758528353</v>
       </c>
       <c r="AL23" s="8">
         <v>8660</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="AO23" s="14">
-        <v>8501</v>
+        <v>8502</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.98163972286374135</v>
+        <v>0.98175519630484986</v>
       </c>
       <c r="AQ23" s="8">
         <v>10698</v>
@@ -3989,14 +3989,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="AT23" s="14">
-        <v>10733</v>
+        <v>10734</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>1.0032716395587959</v>
+        <v>1.0033651149747616</v>
       </c>
       <c r="AV23" s="8">
         <v>8445</v>
@@ -4006,14 +4006,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2796</v>
+        <v>2797</v>
       </c>
       <c r="AY23" s="14">
-        <v>8494</v>
+        <v>8495</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>1.0058022498519834</v>
+        <v>1.0059206631142688</v>
       </c>
       <c r="BA23" s="8">
         <v>8623</v>
@@ -4023,14 +4023,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="BD23" s="14">
-        <v>8541</v>
+        <v>8542</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.99049054853299312</v>
+        <v>0.99060651745332251</v>
       </c>
       <c r="BF23" s="8">
         <v>11023</v>
@@ -4040,14 +4040,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4231</v>
+        <v>4232</v>
       </c>
       <c r="BI23" s="14">
-        <v>10902</v>
+        <v>10903</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.9890229520094348</v>
+        <v>0.9891136714143155</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4116,14 +4116,14 @@
       </c>
       <c r="T24" s="4">
         <f t="shared" si="6"/>
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="U24" s="14">
-        <v>5732</v>
+        <v>5733</v>
       </c>
       <c r="V24" s="5">
         <f t="shared" si="7"/>
-        <v>0.98471053083662596</v>
+        <v>0.98488232262497855</v>
       </c>
       <c r="W24" s="8">
         <v>5925</v>
@@ -4133,14 +4133,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="Z24" s="14">
-        <v>5807</v>
+        <v>5808</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.98008438818565402</v>
+        <v>0.98025316455696199</v>
       </c>
       <c r="AB24" s="8">
         <v>6940</v>
@@ -4150,14 +4150,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="AE24" s="14">
-        <v>6801</v>
+        <v>6802</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.979971181556196</v>
+        <v>0.98011527377521612</v>
       </c>
       <c r="AG24" s="8">
         <v>6076</v>
@@ -4167,14 +4167,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="AJ24" s="14">
-        <v>5950</v>
+        <v>5951</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.97926267281105994</v>
+        <v>0.97942725477287684</v>
       </c>
       <c r="AL24" s="8">
         <v>6181</v>
@@ -4464,14 +4464,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>7523</v>
+        <v>7525</v>
       </c>
       <c r="BI25" s="14">
-        <v>27761</v>
+        <v>27763</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>1.0044140526068237</v>
+        <v>1.0044864141249683</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3461</v>
+        <v>3464</v>
       </c>
       <c r="F26" s="14">
-        <v>13361</v>
+        <v>13364</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.9871444403398596</v>
+        <v>0.98736608792020686</v>
       </c>
       <c r="H26" s="8">
         <v>13884</v>
@@ -4506,14 +4506,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3306</v>
+        <v>3309</v>
       </c>
       <c r="K26" s="14">
-        <v>13934</v>
+        <v>13937</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>1.0036012676462114</v>
+        <v>1.0038173437049842</v>
       </c>
       <c r="M26" s="8">
         <v>25920</v>
@@ -4523,14 +4523,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5137</v>
+        <v>5143</v>
       </c>
       <c r="P26" s="14">
-        <v>26298</v>
+        <v>26304</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>1.0145833333333334</v>
+        <v>1.0148148148148148</v>
       </c>
       <c r="R26" s="8">
         <v>13869</v>
@@ -4540,14 +4540,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3706</v>
+        <v>3710</v>
       </c>
       <c r="U26" s="14">
-        <v>14167</v>
+        <v>14171</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>1.0214867690532843</v>
+        <v>1.0217751820607108</v>
       </c>
       <c r="W26" s="8">
         <v>14474</v>
@@ -4557,14 +4557,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3385</v>
+        <v>3391</v>
       </c>
       <c r="Z26" s="14">
-        <v>14430</v>
+        <v>14436</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.99696006632582557</v>
+        <v>0.99737460273594025</v>
       </c>
       <c r="AB26" s="8">
         <v>27035</v>
@@ -4574,14 +4574,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5632</v>
+        <v>5642</v>
       </c>
       <c r="AE26" s="14">
-        <v>26970</v>
+        <v>26980</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.99759570926576657</v>
+        <v>0.99796560014795632</v>
       </c>
       <c r="AG26" s="8">
         <v>14053</v>
@@ -4591,14 +4591,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3370</v>
+        <v>3375</v>
       </c>
       <c r="AJ26" s="14">
-        <v>14091</v>
+        <v>14096</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>1.0027040489575179</v>
+        <v>1.0030598448729808</v>
       </c>
       <c r="AL26" s="8">
         <v>14372</v>
@@ -4608,14 +4608,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>3135</v>
+        <v>3140</v>
       </c>
       <c r="AO26" s="14">
-        <v>14219</v>
+        <v>14224</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.98935430002783187</v>
+        <v>0.98970219871973286</v>
       </c>
       <c r="AQ26" s="8">
         <v>27267</v>
@@ -4625,14 +4625,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5378</v>
+        <v>5388</v>
       </c>
       <c r="AT26" s="14">
-        <v>27071</v>
+        <v>27081</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.99281182381633482</v>
+        <v>0.99317856749917488</v>
       </c>
       <c r="AV26" s="8">
         <v>14007</v>
@@ -4642,14 +4642,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3129</v>
+        <v>3135</v>
       </c>
       <c r="AY26" s="14">
-        <v>14013</v>
+        <v>14019</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>1.0004283572499464</v>
+        <v>1.000856714499893</v>
       </c>
       <c r="BA26" s="8">
         <v>14398</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3040</v>
+        <v>3046</v>
       </c>
       <c r="BD26" s="14">
-        <v>14092</v>
+        <v>14098</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.978747048201139</v>
+        <v>0.9791637727462148</v>
       </c>
       <c r="BF26" s="8">
         <v>27339</v>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6612</v>
+        <v>6623</v>
       </c>
       <c r="BI26" s="14">
-        <v>27088</v>
+        <v>27099</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.99081897655364137</v>
+        <v>0.99122133216284425</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4701,14 +4701,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>34621</v>
+        <v>34627</v>
       </c>
       <c r="F27" s="14">
-        <v>120698</v>
+        <v>120704</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>1.0017927989243207</v>
+        <v>1.0018425988944406</v>
       </c>
       <c r="H27" s="8">
         <v>123649</v>
@@ -4718,14 +4718,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>32445</v>
+        <v>32451</v>
       </c>
       <c r="K27" s="14">
-        <v>122547</v>
+        <v>122553</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.99108767559786171</v>
+        <v>0.99113620005014191</v>
       </c>
       <c r="M27" s="8">
         <v>182121</v>
@@ -4735,14 +4735,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>47458</v>
+        <v>47472</v>
       </c>
       <c r="P27" s="14">
-        <v>180949</v>
+        <v>180963</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99356471796223389</v>
+        <v>0.99364158993196827</v>
       </c>
       <c r="R27" s="8">
         <v>122848</v>
@@ -4752,14 +4752,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>33817</v>
+        <v>33827</v>
       </c>
       <c r="U27" s="14">
-        <v>122046</v>
+        <v>122056</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.99347160718937222</v>
+        <v>0.9935530085959885</v>
       </c>
       <c r="W27" s="8">
         <v>125846</v>
@@ -4769,14 +4769,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>34881</v>
+        <v>34894</v>
       </c>
       <c r="Z27" s="14">
-        <v>123329</v>
+        <v>123342</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.97999936430240131</v>
+        <v>0.98010266516218236</v>
       </c>
       <c r="AB27" s="8">
         <v>184102</v>
@@ -4786,14 +4786,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>50081</v>
+        <v>50104</v>
       </c>
       <c r="AE27" s="14">
-        <v>182663</v>
+        <v>182686</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.99218368078565145</v>
+        <v>0.9923086115305646</v>
       </c>
       <c r="AG27" s="8">
         <v>124176</v>
@@ -4803,14 +4803,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>34569</v>
+        <v>34586</v>
       </c>
       <c r="AJ27" s="14">
-        <v>123186</v>
+        <v>123203</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.9920274449168921</v>
+        <v>0.99216434737791526</v>
       </c>
       <c r="AL27" s="8">
         <v>126536</v>
@@ -4820,14 +4820,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>31837</v>
+        <v>31854</v>
       </c>
       <c r="AO27" s="14">
-        <v>124031</v>
+        <v>124048</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.9802032623127015</v>
+        <v>0.98033761143073905</v>
       </c>
       <c r="AQ27" s="8">
         <v>184835</v>
@@ -4837,14 +4837,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>47420</v>
+        <v>47452</v>
       </c>
       <c r="AT27" s="14">
-        <v>184259</v>
+        <v>184291</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.99688370709010743</v>
+        <v>0.99705683447399029</v>
       </c>
       <c r="AV27" s="8">
         <v>124975</v>
@@ -4854,14 +4854,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>31785</v>
+        <v>31808</v>
       </c>
       <c r="AY27" s="14">
-        <v>124325</v>
+        <v>124348</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.99479895979195843</v>
+        <v>0.99498299659931988</v>
       </c>
       <c r="BA27" s="8">
         <v>127493</v>
@@ -4871,14 +4871,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>31097</v>
+        <v>31121</v>
       </c>
       <c r="BD27" s="14">
-        <v>125378</v>
+        <v>125402</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.98341085392923533</v>
+        <v>0.98359909955840708</v>
       </c>
       <c r="BF27" s="8">
         <v>187636</v>
@@ -4888,14 +4888,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>63093</v>
+        <v>63136</v>
       </c>
       <c r="BI27" s="14">
-        <v>185646</v>
+        <v>185689</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.98939435929139397</v>
+        <v>0.98962352640218298</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4913,14 +4913,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>64593</v>
+        <v>64594</v>
       </c>
       <c r="F28" s="14">
-        <v>380035</v>
+        <v>380036</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.99431461403215005</v>
+        <v>0.99431723040857334</v>
       </c>
       <c r="H28" s="8">
         <v>389922</v>
@@ -4930,14 +4930,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>63268</v>
+        <v>63270</v>
       </c>
       <c r="K28" s="14">
-        <v>385061</v>
+        <v>385063</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.98753340411672075</v>
+        <v>0.98753853334769515</v>
       </c>
       <c r="M28" s="8">
         <v>650891</v>
@@ -4947,14 +4947,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>104691</v>
+        <v>104700</v>
       </c>
       <c r="P28" s="14">
-        <v>645764</v>
+        <v>645773</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.99212310509747403</v>
+        <v>0.99213693229741995</v>
       </c>
       <c r="R28" s="8">
         <v>389073</v>
@@ -4964,14 +4964,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>67521</v>
+        <v>67527</v>
       </c>
       <c r="U28" s="14">
-        <v>386525</v>
+        <v>386531</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.99345110043616491</v>
+        <v>0.99346652170672345</v>
       </c>
       <c r="W28" s="8">
         <v>397763</v>
@@ -4981,14 +4981,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>67031</v>
+        <v>67040</v>
       </c>
       <c r="Z28" s="14">
-        <v>391716</v>
+        <v>391725</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.98479747990637645</v>
+        <v>0.98482010644529527</v>
       </c>
       <c r="AB28" s="8">
         <v>660941</v>
@@ -4998,14 +4998,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>103870</v>
+        <v>103887</v>
       </c>
       <c r="AE28" s="14">
-        <v>656435</v>
+        <v>656452</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.99318244744992368</v>
+        <v>0.99320816835390757</v>
       </c>
       <c r="AG28" s="8">
         <v>397417</v>
@@ -5015,14 +5015,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>68382</v>
+        <v>68391</v>
       </c>
       <c r="AJ28" s="14">
-        <v>394586</v>
+        <v>394595</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.99287649999874183</v>
+        <v>0.99289914623682429</v>
       </c>
       <c r="AL28" s="8">
         <v>405895</v>
@@ -5032,14 +5032,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>61105</v>
+        <v>61114</v>
       </c>
       <c r="AO28" s="14">
-        <v>398900</v>
+        <v>398909</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.98276647901550895</v>
+        <v>0.98278865223764766</v>
       </c>
       <c r="AQ28" s="8">
         <v>670091</v>
@@ -5049,14 +5049,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>96049</v>
+        <v>96078</v>
       </c>
       <c r="AT28" s="14">
-        <v>666121</v>
+        <v>666150</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.99407543154586464</v>
+        <v>0.99411870924993773</v>
       </c>
       <c r="AV28" s="8">
         <v>405395</v>
@@ -5066,14 +5066,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>60974</v>
+        <v>60991</v>
       </c>
       <c r="AY28" s="14">
-        <v>402774</v>
+        <v>402791</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.9935347007239852</v>
+        <v>0.99357663513363514</v>
       </c>
       <c r="BA28" s="8">
         <v>412255</v>
@@ -5083,14 +5083,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>59391</v>
+        <v>59410</v>
       </c>
       <c r="BD28" s="14">
-        <v>406876</v>
+        <v>406895</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98695225042752666</v>
+        <v>0.98699833840705387</v>
       </c>
       <c r="BF28" s="8">
         <v>680839</v>
@@ -5100,14 +5100,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>127370</v>
+        <v>127410</v>
       </c>
       <c r="BI28" s="14">
-        <v>676279</v>
+        <v>676319</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.99330238132656912</v>
+        <v>0.99336113236756418</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5159,14 +5159,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>30946</v>
+        <v>30949</v>
       </c>
       <c r="P29" s="14">
-        <v>174211</v>
+        <v>174214</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98626561818871472</v>
+        <v>0.98628260217281771</v>
       </c>
       <c r="R29" s="8">
         <v>129740</v>
@@ -5193,14 +5193,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>23810</v>
+        <v>23812</v>
       </c>
       <c r="Z29" s="14">
-        <v>129572</v>
+        <v>129574</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.98334927067680589</v>
+        <v>0.98336444909916065</v>
       </c>
       <c r="AB29" s="8">
         <v>178083</v>
@@ -5210,14 +5210,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>32797</v>
+        <v>32802</v>
       </c>
       <c r="AE29" s="14">
-        <v>176351</v>
+        <v>176356</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.99027419798633221</v>
+        <v>0.99030227478198363</v>
       </c>
       <c r="AG29" s="8">
         <v>131984</v>
@@ -5227,14 +5227,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>28862</v>
+        <v>28864</v>
       </c>
       <c r="AJ29" s="14">
-        <v>130681</v>
+        <v>130683</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.99012759122317862</v>
+        <v>0.99014274457509999</v>
       </c>
       <c r="AL29" s="8">
         <v>133676</v>
@@ -5244,14 +5244,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>23038</v>
+        <v>23040</v>
       </c>
       <c r="AO29" s="14">
-        <v>131830</v>
+        <v>131832</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.9861904904395703</v>
+        <v>0.98620545198838983</v>
       </c>
       <c r="AQ29" s="8">
         <v>179800</v>
@@ -5261,14 +5261,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>29840</v>
+        <v>29843</v>
       </c>
       <c r="AT29" s="14">
-        <v>178970</v>
+        <v>178973</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.99538375973303672</v>
+        <v>0.99540044493882096</v>
       </c>
       <c r="AV29" s="8">
         <v>134089</v>
@@ -5278,14 +5278,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>22665</v>
+        <v>22667</v>
       </c>
       <c r="AY29" s="14">
-        <v>133157</v>
+        <v>133159</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.99304939256762303</v>
+        <v>0.99306430803421608</v>
       </c>
       <c r="BA29" s="8">
         <v>136058</v>
@@ -5295,14 +5295,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>23008</v>
+        <v>23009</v>
       </c>
       <c r="BD29" s="14">
-        <v>134471</v>
+        <v>134472</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.988335856766967</v>
+        <v>0.98834320657366714</v>
       </c>
       <c r="BF29" s="8">
         <v>182623</v>
@@ -5312,14 +5312,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>41936</v>
+        <v>41939</v>
       </c>
       <c r="BI29" s="14">
-        <v>181413</v>
+        <v>181416</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.99337432853474095</v>
+        <v>0.99339075581936553</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>39281</v>
+        <v>39283</v>
       </c>
       <c r="F30" s="14">
-        <v>166408</v>
+        <v>166410</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.9970879720061836</v>
+        <v>0.99709995566047915</v>
       </c>
       <c r="H30" s="8">
         <v>172134</v>
@@ -5354,14 +5354,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>41653</v>
+        <v>41656</v>
       </c>
       <c r="K30" s="14">
-        <v>169534</v>
+        <v>169537</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.98489548839857322</v>
+        <v>0.98491291668119019</v>
       </c>
       <c r="M30" s="8">
         <v>289249</v>
@@ -5371,14 +5371,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>59672</v>
+        <v>59680</v>
       </c>
       <c r="P30" s="14">
-        <v>286045</v>
+        <v>286053</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.98892303862761843</v>
+        <v>0.98895069645876044</v>
       </c>
       <c r="R30" s="8">
         <v>169142</v>
@@ -5388,14 +5388,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>37558</v>
+        <v>37562</v>
       </c>
       <c r="U30" s="14">
-        <v>167855</v>
+        <v>167859</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.99239100873821995</v>
+        <v>0.99241465750671032</v>
       </c>
       <c r="W30" s="8">
         <v>174259</v>
@@ -5405,14 +5405,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>41370</v>
+        <v>41375</v>
       </c>
       <c r="Z30" s="14">
-        <v>170994</v>
+        <v>170999</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.98126352153977703</v>
+        <v>0.98129221446238069</v>
       </c>
       <c r="AB30" s="8">
         <v>293307</v>
@@ -5422,14 +5422,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>62857</v>
+        <v>62868</v>
       </c>
       <c r="AE30" s="14">
-        <v>290495</v>
+        <v>290506</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.9904127756923633</v>
+        <v>0.99045027905914285</v>
       </c>
       <c r="AG30" s="8">
         <v>172053</v>
@@ -5439,14 +5439,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>37793</v>
+        <v>37797</v>
       </c>
       <c r="AJ30" s="14">
-        <v>170978</v>
+        <v>170982</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.99375192527883849</v>
+        <v>0.99377517392896375</v>
       </c>
       <c r="AL30" s="8">
         <v>176835</v>
@@ -5456,14 +5456,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>36113</v>
+        <v>36119</v>
       </c>
       <c r="AO30" s="14">
-        <v>173657</v>
+        <v>173663</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.98202844459524419</v>
+        <v>0.98206237452992906</v>
       </c>
       <c r="AQ30" s="8">
         <v>297651</v>
@@ -5473,14 +5473,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>57647</v>
+        <v>57664</v>
       </c>
       <c r="AT30" s="14">
-        <v>296238</v>
+        <v>296255</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.99525282965620809</v>
+        <v>0.99530994352446323</v>
       </c>
       <c r="AV30" s="8">
         <v>175428</v>
@@ -5490,14 +5490,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>36219</v>
+        <v>36229</v>
       </c>
       <c r="AY30" s="14">
-        <v>174365</v>
+        <v>174375</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.99394053400825411</v>
+        <v>0.99399753745126207</v>
       </c>
       <c r="BA30" s="8">
         <v>179593</v>
@@ -5507,14 +5507,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>36001</v>
+        <v>36013</v>
       </c>
       <c r="BD30" s="14">
-        <v>176229</v>
+        <v>176241</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.9812687576910013</v>
+        <v>0.9813355754400227</v>
       </c>
       <c r="BF30" s="8">
         <v>302258</v>
@@ -5524,14 +5524,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>72817</v>
+        <v>72838</v>
       </c>
       <c r="BI30" s="14">
-        <v>299436</v>
+        <v>299457</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.9906636052643768</v>
+        <v>0.99073308233363555</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5549,14 +5549,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>21215</v>
+        <v>21218</v>
       </c>
       <c r="F31" s="14">
-        <v>74595</v>
+        <v>74598</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>1.0011407864716146</v>
+        <v>1.0011810495235538</v>
       </c>
       <c r="H31" s="8">
         <v>76671</v>
@@ -5566,14 +5566,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>20125</v>
+        <v>20127</v>
       </c>
       <c r="K31" s="14">
-        <v>75771</v>
+        <v>75773</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.9882615330437845</v>
+        <v>0.98828761852590941</v>
       </c>
       <c r="M31" s="8">
         <v>133745</v>
@@ -5583,14 +5583,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>35668</v>
+        <v>35674</v>
       </c>
       <c r="P31" s="14">
-        <v>133535</v>
+        <v>133541</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>0.99842984784477928</v>
+        <v>0.99847470933492843</v>
       </c>
       <c r="R31" s="8">
         <v>74974</v>
@@ -5600,14 +5600,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>20616</v>
+        <v>20618</v>
       </c>
       <c r="U31" s="14">
-        <v>75031</v>
+        <v>75033</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>1.0007602635580335</v>
+        <v>1.0007869394723503</v>
       </c>
       <c r="W31" s="8">
         <v>77586</v>
@@ -5617,14 +5617,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>21077</v>
+        <v>21081</v>
       </c>
       <c r="Z31" s="14">
-        <v>76086</v>
+        <v>76090</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.98066661511097364</v>
+        <v>0.98071817080401102</v>
       </c>
       <c r="AB31" s="8">
         <v>135116</v>
@@ -5634,14 +5634,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>37191</v>
+        <v>37196</v>
       </c>
       <c r="AE31" s="14">
-        <v>135146</v>
+        <v>135151</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>1.0002220314396519</v>
+        <v>1.0002590366795938</v>
       </c>
       <c r="AG31" s="8">
         <v>76230</v>
@@ -5651,14 +5651,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>22396</v>
+        <v>22398</v>
       </c>
       <c r="AJ31" s="14">
-        <v>75995</v>
+        <v>75997</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>0.99691722418995143</v>
+        <v>0.99694346057982419</v>
       </c>
       <c r="AL31" s="8">
         <v>77611</v>
@@ -5668,14 +5668,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>18525</v>
+        <v>18529</v>
       </c>
       <c r="AO31" s="14">
-        <v>76839</v>
+        <v>76843</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.99005295641081803</v>
+        <v>0.99010449549677237</v>
       </c>
       <c r="AQ31" s="8">
         <v>136879</v>
@@ -5685,14 +5685,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>34717</v>
+        <v>34722</v>
       </c>
       <c r="AT31" s="14">
-        <v>137469</v>
+        <v>137474</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>1.0043103763177696</v>
+        <v>1.0043469049306322</v>
       </c>
       <c r="AV31" s="8">
         <v>76719</v>
@@ -5702,14 +5702,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>18043</v>
+        <v>18046</v>
       </c>
       <c r="AY31" s="14">
-        <v>76904</v>
+        <v>76907</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>1.0024113974374014</v>
+        <v>1.0024505011796296</v>
       </c>
       <c r="BA31" s="8">
         <v>78720</v>
@@ -5719,14 +5719,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>18506</v>
+        <v>18509</v>
       </c>
       <c r="BD31" s="14">
-        <v>78330</v>
+        <v>78333</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.99504573170731703</v>
+        <v>0.99508384146341466</v>
       </c>
       <c r="BF31" s="8">
         <v>140181</v>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>48208</v>
+        <v>48216</v>
       </c>
       <c r="BI31" s="14">
-        <v>140197</v>
+        <v>140205</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>1.0001141381499632</v>
+        <v>1.0001712072249449</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5795,14 +5795,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>93395</v>
+        <v>93397</v>
       </c>
       <c r="P32" s="14">
-        <v>438313</v>
+        <v>438315</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.99382815422812254</v>
+        <v>0.99383268901561106</v>
       </c>
       <c r="R32" s="8">
         <v>206418</v>
@@ -5812,14 +5812,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>44056</v>
+        <v>44058</v>
       </c>
       <c r="U32" s="14">
-        <v>205097</v>
+        <v>205099</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99360036430931409</v>
+        <v>0.99361005338681707</v>
       </c>
       <c r="W32" s="8">
         <v>212709</v>
@@ -5829,14 +5829,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>45954</v>
+        <v>45956</v>
       </c>
       <c r="Z32" s="14">
-        <v>209141</v>
+        <v>209143</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.98322590957599354</v>
+        <v>0.98323531209304726</v>
       </c>
       <c r="AB32" s="8">
         <v>446806</v>
@@ -5846,14 +5846,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="AE32" s="14">
-        <v>444949</v>
+        <v>444957</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.9958438337891613</v>
+        <v>0.99586173865167438</v>
       </c>
       <c r="AG32" s="8">
         <v>210129</v>
@@ -5863,14 +5863,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>49141</v>
+        <v>49144</v>
       </c>
       <c r="AJ32" s="14">
-        <v>209495</v>
+        <v>209498</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.99698280580024656</v>
+        <v>0.99699708274440935</v>
       </c>
       <c r="AL32" s="8">
         <v>217332</v>
@@ -5880,14 +5880,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>40349</v>
+        <v>40351</v>
       </c>
       <c r="AO32" s="14">
-        <v>212881</v>
+        <v>212883</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.9795198130049878</v>
+        <v>0.97952901551543259</v>
       </c>
       <c r="AQ32" s="8">
         <v>453805</v>
@@ -5897,14 +5897,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>93285</v>
+        <v>93295</v>
       </c>
       <c r="AT32" s="14">
-        <v>452804</v>
+        <v>452814</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.9977942067628166</v>
+        <v>0.99781624265929203</v>
       </c>
       <c r="AV32" s="8">
         <v>213428</v>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>40173</v>
+        <v>40176</v>
       </c>
       <c r="AY32" s="14">
-        <v>213398</v>
+        <v>213401</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.99985943737466498</v>
+        <v>0.99987349363719846</v>
       </c>
       <c r="BA32" s="8">
         <v>220509</v>
@@ -5931,14 +5931,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>39354</v>
+        <v>39357</v>
       </c>
       <c r="BD32" s="14">
-        <v>217596</v>
+        <v>217599</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98678965484401993</v>
+        <v>0.98680325973089533</v>
       </c>
       <c r="BF32" s="8">
         <v>463937</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>127795</v>
+        <v>127812</v>
       </c>
       <c r="BI32" s="14">
-        <v>460997</v>
+        <v>461014</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99366293268267025</v>
+        <v>0.99369957558892696</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5973,14 +5973,14 @@
       </c>
       <c r="E33" s="4">
         <f t="shared" si="0"/>
-        <v>74089</v>
+        <v>74090</v>
       </c>
       <c r="F33" s="14">
-        <v>623261</v>
+        <v>623262</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>1.00364898268102</v>
+        <v>1.0036505929999437</v>
       </c>
       <c r="H33" s="8">
         <v>630476</v>
@@ -5990,14 +5990,14 @@
       </c>
       <c r="J33" s="4">
         <f t="shared" si="2"/>
-        <v>78135</v>
+        <v>78136</v>
       </c>
       <c r="K33" s="14">
-        <v>630447</v>
+        <v>630448</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="3"/>
-        <v>0.99995400300725168</v>
+        <v>0.99995558911044991</v>
       </c>
       <c r="M33" s="8">
         <v>1032030</v>
@@ -6007,14 +6007,14 @@
       </c>
       <c r="O33" s="4">
         <f t="shared" si="4"/>
-        <v>130778</v>
+        <v>130781</v>
       </c>
       <c r="P33" s="14">
-        <v>1032139</v>
+        <v>1032142</v>
       </c>
       <c r="Q33" s="5">
         <f t="shared" si="5"/>
-        <v>1.0001056170847746</v>
+        <v>1.0001085239770162</v>
       </c>
       <c r="R33" s="8">
         <v>629419</v>
@@ -6024,14 +6024,14 @@
       </c>
       <c r="T33" s="4">
         <f t="shared" si="6"/>
-        <v>79466</v>
+        <v>79468</v>
       </c>
       <c r="U33" s="14">
-        <v>629960</v>
+        <v>629962</v>
       </c>
       <c r="V33" s="5">
         <f t="shared" si="7"/>
-        <v>1.0008595228297843</v>
+        <v>1.000862700363351</v>
       </c>
       <c r="W33" s="8">
         <v>637378</v>
@@ -6041,14 +6041,14 @@
       </c>
       <c r="Y33" s="4">
         <f t="shared" si="8"/>
-        <v>80053</v>
+        <v>80054</v>
       </c>
       <c r="Z33" s="14">
-        <v>635162</v>
+        <v>635163</v>
       </c>
       <c r="AA33" s="5">
         <f t="shared" si="9"/>
-        <v>0.99652325621530713</v>
+        <v>0.99652482514300778</v>
       </c>
       <c r="AB33" s="8">
         <v>1041984</v>
@@ -6058,14 +6058,14 @@
       </c>
       <c r="AD33" s="4">
         <f t="shared" si="10"/>
-        <v>142386</v>
+        <v>142388</v>
       </c>
       <c r="AE33" s="14">
-        <v>1042241</v>
+        <v>1042243</v>
       </c>
       <c r="AF33" s="5">
         <f t="shared" si="11"/>
-        <v>1.0002466448621092</v>
+        <v>1.0002485642773786</v>
       </c>
       <c r="AG33" s="8">
         <v>638215</v>
@@ -6075,14 +6075,14 @@
       </c>
       <c r="AI33" s="4">
         <f t="shared" si="12"/>
-        <v>115966</v>
+        <v>115968</v>
       </c>
       <c r="AJ33" s="14">
-        <v>638848</v>
+        <v>638850</v>
       </c>
       <c r="AK33" s="5">
         <f t="shared" si="13"/>
-        <v>1.0009918287724355</v>
+        <v>1.0009949625126329</v>
       </c>
       <c r="AL33" s="8">
         <v>645318</v>
@@ -6092,14 +6092,14 @@
       </c>
       <c r="AN33" s="4">
         <f t="shared" si="14"/>
-        <v>75261</v>
+        <v>75266</v>
       </c>
       <c r="AO33" s="14">
-        <v>642414</v>
+        <v>642419</v>
       </c>
       <c r="AP33" s="5">
         <f t="shared" si="15"/>
-        <v>0.99549989307597186</v>
+        <v>0.99550764119395396</v>
       </c>
       <c r="AQ33" s="8">
         <v>1053133</v>
@@ -6109,14 +6109,14 @@
       </c>
       <c r="AS33" s="4">
         <f t="shared" si="16"/>
-        <v>135430</v>
+        <v>135437</v>
       </c>
       <c r="AT33" s="14">
-        <v>1054016</v>
+        <v>1054023</v>
       </c>
       <c r="AU33" s="5">
         <f t="shared" si="17"/>
-        <v>1.0008384506040549</v>
+        <v>1.0008450974378356</v>
       </c>
       <c r="AV33" s="8">
         <v>647979</v>
@@ -6126,14 +6126,14 @@
       </c>
       <c r="AX33" s="4">
         <f t="shared" si="18"/>
-        <v>69694</v>
+        <v>69701</v>
       </c>
       <c r="AY33" s="14">
-        <v>649941</v>
+        <v>649948</v>
       </c>
       <c r="AZ33" s="5">
         <f t="shared" si="19"/>
-        <v>1.0030278759033857</v>
+        <v>1.0030386787226129</v>
       </c>
       <c r="BA33" s="8">
         <v>657743</v>
@@ -6143,14 +6143,14 @@
       </c>
       <c r="BC33" s="4">
         <f t="shared" si="20"/>
-        <v>65950</v>
+        <v>65956</v>
       </c>
       <c r="BD33" s="14">
-        <v>658017</v>
+        <v>658023</v>
       </c>
       <c r="BE33" s="5">
         <f t="shared" si="21"/>
-        <v>1.0004165760791068</v>
+        <v>1.0004256981830288</v>
       </c>
       <c r="BF33" s="8">
         <v>1071541</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="BH33" s="4">
         <f t="shared" si="22"/>
-        <v>153831</v>
+        <v>153839</v>
       </c>
       <c r="BI33" s="14">
-        <v>1071075</v>
+        <v>1071083</v>
       </c>
       <c r="BJ33" s="5">
         <f t="shared" si="23"/>
-        <v>0.99956511230088252</v>
+        <v>0.99957257818412926</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="0"/>
-        <v>175053</v>
+        <v>175060</v>
       </c>
       <c r="F36" s="14">
-        <v>834231</v>
+        <v>834238</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="24"/>
-        <v>0.99783980852522081</v>
+        <v>0.99784818136039433</v>
       </c>
       <c r="H36" s="8">
         <v>854298</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="25"/>
-        <v>170039</v>
+        <v>170047</v>
       </c>
       <c r="K36" s="14">
-        <v>844044</v>
+        <v>844052</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="26"/>
-        <v>0.98799716258261172</v>
+        <v>0.98800652699643454</v>
       </c>
       <c r="M36" s="8">
         <v>1510524</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="27"/>
-        <v>313963</v>
+        <v>313986</v>
       </c>
       <c r="P36" s="14">
-        <v>1500961</v>
+        <v>1500984</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="28"/>
-        <v>0.99366908437072166</v>
+        <v>0.99368431087490172</v>
       </c>
       <c r="R36" s="8">
         <v>845008</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="29"/>
-        <v>178604</v>
+        <v>178616</v>
       </c>
       <c r="U36" s="14">
-        <v>840669</v>
+        <v>840681</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="30"/>
-        <v>0.99486513737148052</v>
+        <v>0.99487933842046461</v>
       </c>
       <c r="W36" s="8">
         <v>865288</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="31"/>
-        <v>186851</v>
+        <v>186864</v>
       </c>
       <c r="Z36" s="14">
-        <v>849761</v>
+        <v>849774</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="32"/>
-        <v>0.9820556855058663</v>
+        <v>0.9820707094054234</v>
       </c>
       <c r="AB36" s="8">
         <v>1522408</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="33"/>
-        <v>327715</v>
+        <v>327740</v>
       </c>
       <c r="AE36" s="14">
-        <v>1515061</v>
+        <v>1515086</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="34"/>
-        <v>0.99517409262168877</v>
+        <v>0.99519051397522873</v>
       </c>
       <c r="AG36" s="8">
         <v>860909</v>
@@ -6687,14 +6687,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="35"/>
-        <v>196457</v>
+        <v>196479</v>
       </c>
       <c r="AJ36" s="14">
-        <v>856892</v>
+        <v>856914</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="36"/>
-        <v>0.99533400161921881</v>
+        <v>0.99535955600417703</v>
       </c>
       <c r="AL36" s="8">
         <v>879793</v>
@@ -6704,14 +6704,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="37"/>
-        <v>162027</v>
+        <v>162051</v>
       </c>
       <c r="AO36" s="14">
-        <v>866622</v>
+        <v>866646</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="38"/>
-        <v>0.98502943305982205</v>
+        <v>0.98505671220389346</v>
       </c>
       <c r="AQ36" s="8">
         <v>1539776</v>
@@ -6721,14 +6721,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="39"/>
-        <v>300036</v>
+        <v>300071</v>
       </c>
       <c r="AT36" s="14">
-        <v>1536647</v>
+        <v>1536682</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="40"/>
-        <v>0.99796788623799826</v>
+        <v>0.99799061681699153</v>
       </c>
       <c r="AV36" s="8">
         <v>875330</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="41"/>
-        <v>160977</v>
+        <v>161002</v>
       </c>
       <c r="AY36" s="14">
-        <v>873814</v>
+        <v>873839</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="42"/>
-        <v>0.99826808175202497</v>
+        <v>0.9982966424091485</v>
       </c>
       <c r="BA36" s="8">
         <v>893595</v>
@@ -6755,14 +6755,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="43"/>
-        <v>151786</v>
+        <v>151810</v>
       </c>
       <c r="BD36" s="14">
-        <v>884053</v>
+        <v>884077</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="44"/>
-        <v>0.9893217844773079</v>
+        <v>0.98934864228201813</v>
       </c>
       <c r="BF36" s="8">
         <v>1566403</v>
@@ -6772,14 +6772,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="45"/>
-        <v>365268</v>
+        <v>365321</v>
       </c>
       <c r="BI36" s="14">
-        <v>1557065</v>
+        <v>1557118</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="46"/>
-        <v>0.99403857117229732</v>
+        <v>0.9940724066539709</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6797,14 +6797,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="0"/>
-        <v>131189</v>
+        <v>131197</v>
       </c>
       <c r="F37" s="14">
-        <v>667628</v>
+        <v>667636</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="24"/>
-        <v>0.98827472174483277</v>
+        <v>0.98828656396501213</v>
       </c>
       <c r="H37" s="8">
         <v>681828</v>
@@ -6814,14 +6814,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="25"/>
-        <v>121645</v>
+        <v>121654</v>
       </c>
       <c r="K37" s="14">
-        <v>670310</v>
+        <v>670319</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="26"/>
-        <v>0.98310717658999047</v>
+        <v>0.98312037639991312</v>
       </c>
       <c r="M37" s="8">
         <v>856106</v>
@@ -6831,14 +6831,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="27"/>
-        <v>152372</v>
+        <v>152385</v>
       </c>
       <c r="P37" s="14">
-        <v>844578</v>
+        <v>844591</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="28"/>
-        <v>0.98653437775228769</v>
+        <v>0.98654956278778561</v>
       </c>
       <c r="R37" s="8">
         <v>679636</v>
@@ -6848,14 +6848,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="29"/>
-        <v>129358</v>
+        <v>129369</v>
       </c>
       <c r="U37" s="14">
-        <v>671321</v>
+        <v>671332</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="30"/>
-        <v>0.98776550977287847</v>
+        <v>0.98778169490727386</v>
       </c>
       <c r="W37" s="8">
         <v>687189</v>
@@ -6865,14 +6865,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="31"/>
-        <v>130981</v>
+        <v>130992</v>
       </c>
       <c r="Z37" s="14">
-        <v>676115</v>
+        <v>676126</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="32"/>
-        <v>0.98388507382976154</v>
+        <v>0.98390108107085528</v>
       </c>
       <c r="AB37" s="8">
         <v>863912</v>
@@ -6882,14 +6882,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="33"/>
-        <v>163629</v>
+        <v>163647</v>
       </c>
       <c r="AE37" s="14">
-        <v>853752</v>
+        <v>853770</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="34"/>
-        <v>0.98823954291640814</v>
+        <v>0.9882603783718712</v>
       </c>
       <c r="AG37" s="8">
         <v>690763</v>
@@ -6899,14 +6899,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="35"/>
-        <v>131997</v>
+        <v>132013</v>
       </c>
       <c r="AJ37" s="14">
-        <v>682564</v>
+        <v>682580</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="36"/>
-        <v>0.98813051654474837</v>
+        <v>0.98815367933719667</v>
       </c>
       <c r="AL37" s="8">
         <v>697437</v>
@@ -6916,14 +6916,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="37"/>
-        <v>116195</v>
+        <v>116215</v>
       </c>
       <c r="AO37" s="14">
-        <v>688166</v>
+        <v>688186</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="38"/>
-        <v>0.98670704307342461</v>
+        <v>0.98673571949867878</v>
       </c>
       <c r="AQ37" s="8">
         <v>873380</v>
@@ -6933,14 +6933,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="39"/>
-        <v>150032</v>
+        <v>150058</v>
       </c>
       <c r="AT37" s="14">
-        <v>867321</v>
+        <v>867347</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="40"/>
-        <v>0.99306258444205275</v>
+        <v>0.99309235384368777</v>
       </c>
       <c r="AV37" s="8">
         <v>700086</v>
@@ -6950,14 +6950,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="41"/>
-        <v>117107</v>
+        <v>117130</v>
       </c>
       <c r="AY37" s="14">
-        <v>694519</v>
+        <v>694542</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="42"/>
-        <v>0.99204811980242424</v>
+        <v>0.99208097290904262</v>
       </c>
       <c r="BA37" s="8">
         <v>708485</v>
@@ -6967,14 +6967,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="43"/>
-        <v>113158</v>
+        <v>113183</v>
       </c>
       <c r="BD37" s="14">
-        <v>699030</v>
+        <v>699055</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="44"/>
-        <v>0.9866546221867788</v>
+        <v>0.98668990874895024</v>
       </c>
       <c r="BF37" s="8">
         <v>887779</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="45"/>
-        <v>186633</v>
+        <v>186668</v>
       </c>
       <c r="BI37" s="14">
-        <v>876468</v>
+        <v>876503</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="46"/>
-        <v>0.98725921653925131</v>
+        <v>0.98729864076532559</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7043,14 +7043,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="27"/>
-        <v>9159</v>
+        <v>9160</v>
       </c>
       <c r="P38" s="14">
-        <v>35781</v>
+        <v>35782</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="28"/>
-        <v>1.0055927154179078</v>
+        <v>1.0056208195154854</v>
       </c>
       <c r="R38" s="8">
         <v>22911</v>
@@ -7060,14 +7060,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="29"/>
-        <v>6109</v>
+        <v>6110</v>
       </c>
       <c r="U38" s="14">
-        <v>23139</v>
+        <v>23140</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="30"/>
-        <v>1.0099515516564095</v>
+        <v>1.0099951988127973</v>
       </c>
       <c r="W38" s="8">
         <v>23450</v>
@@ -7077,14 +7077,14 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="31"/>
-        <v>6342</v>
+        <v>6343</v>
       </c>
       <c r="Z38" s="14">
-        <v>23364</v>
+        <v>23365</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="32"/>
-        <v>0.99633262260127931</v>
+        <v>0.99637526652452024</v>
       </c>
       <c r="AB38" s="8">
         <v>35915</v>
@@ -7094,14 +7094,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="33"/>
-        <v>9131</v>
+        <v>9133</v>
       </c>
       <c r="AE38" s="14">
-        <v>36268</v>
+        <v>36270</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="34"/>
-        <v>1.0098287623555617</v>
+        <v>1.0098844493944035</v>
       </c>
       <c r="AG38" s="8">
         <v>23414</v>
@@ -7111,14 +7111,14 @@
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="35"/>
-        <v>5993</v>
+        <v>5995</v>
       </c>
       <c r="AJ38" s="14">
-        <v>23665</v>
+        <v>23667</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="36"/>
-        <v>1.0107200820022209</v>
+        <v>1.0108055009823183</v>
       </c>
       <c r="AL38" s="8">
         <v>23927</v>
@@ -7128,14 +7128,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="37"/>
-        <v>5873</v>
+        <v>5875</v>
       </c>
       <c r="AO38" s="14">
-        <v>23918</v>
+        <v>23920</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="38"/>
-        <v>0.99962385589501401</v>
+        <v>0.99970744347389973</v>
       </c>
       <c r="AQ38" s="8">
         <v>36551</v>
@@ -7145,14 +7145,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="39"/>
-        <v>8723</v>
+        <v>8726</v>
       </c>
       <c r="AT38" s="14">
-        <v>37037</v>
+        <v>37040</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="40"/>
-        <v>1.0132964898361194</v>
+        <v>1.0133785669338733</v>
       </c>
       <c r="AV38" s="8">
         <v>23833</v>
@@ -7162,14 +7162,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="41"/>
-        <v>5576</v>
+        <v>5578</v>
       </c>
       <c r="AY38" s="14">
-        <v>24169</v>
+        <v>24171</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="42"/>
-        <v>1.0140980992741158</v>
+        <v>1.0141820165316997</v>
       </c>
       <c r="BA38" s="8">
         <v>24292</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="BC38" s="4">
         <f t="shared" si="43"/>
-        <v>5302</v>
+        <v>5304</v>
       </c>
       <c r="BD38" s="14">
-        <v>24408</v>
+        <v>24410</v>
       </c>
       <c r="BE38" s="5">
         <f t="shared" si="44"/>
-        <v>1.0047752346451506</v>
+        <v>1.0048575662769637</v>
       </c>
       <c r="BF38" s="8">
         <v>37393</v>
@@ -7196,14 +7196,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="45"/>
-        <v>10298</v>
+        <v>10300</v>
       </c>
       <c r="BI38" s="14">
-        <v>37534</v>
+        <v>37536</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="46"/>
-        <v>1.0037707592330116</v>
+        <v>1.0038242451795791</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="0"/>
-        <v>58577</v>
+        <v>58586</v>
       </c>
       <c r="F40" s="14">
-        <v>275694</v>
+        <v>275703</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="24"/>
-        <v>0.99269773370492798</v>
+        <v>0.99273014021215455</v>
       </c>
       <c r="H40" s="8">
         <v>279588</v>
@@ -7450,14 +7450,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="25"/>
-        <v>56610</v>
+        <v>56618</v>
       </c>
       <c r="K40" s="14">
-        <v>277357</v>
+        <v>277365</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="26"/>
-        <v>0.99202040144784465</v>
+        <v>0.99204901497918363</v>
       </c>
       <c r="M40" s="8">
         <v>339205</v>
@@ -7467,14 +7467,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="27"/>
-        <v>71960</v>
+        <v>71969</v>
       </c>
       <c r="P40" s="14">
-        <v>336819</v>
+        <v>336828</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="28"/>
-        <v>0.99296590557332587</v>
+        <v>0.99299243820108785</v>
       </c>
       <c r="R40" s="8">
         <v>280405</v>
@@ -7484,14 +7484,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="29"/>
-        <v>61842</v>
+        <v>61852</v>
       </c>
       <c r="U40" s="14">
-        <v>278715</v>
+        <v>278725</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="30"/>
-        <v>0.9939730033344627</v>
+        <v>0.99400866603662563</v>
       </c>
       <c r="W40" s="8">
         <v>283529</v>
@@ -7501,14 +7501,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="31"/>
-        <v>57453</v>
+        <v>57461</v>
       </c>
       <c r="Z40" s="14">
-        <v>280611</v>
+        <v>280619</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="32"/>
-        <v>0.9897082838087109</v>
+        <v>0.98973649961732313</v>
       </c>
       <c r="AB40" s="8">
         <v>342699</v>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="33"/>
-        <v>73640</v>
+        <v>73646</v>
       </c>
       <c r="AE40" s="14">
-        <v>341079</v>
+        <v>341085</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="34"/>
-        <v>0.99527281958803493</v>
+        <v>0.9952903276636349</v>
       </c>
       <c r="AG40" s="8">
         <v>284836</v>
@@ -7535,14 +7535,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="35"/>
-        <v>61236</v>
+        <v>61244</v>
       </c>
       <c r="AJ40" s="14">
-        <v>283328</v>
+        <v>283336</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="36"/>
-        <v>0.99470572539987923</v>
+        <v>0.99473381173728037</v>
       </c>
       <c r="AL40" s="8">
         <v>287465</v>
@@ -7552,14 +7552,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="37"/>
-        <v>57548</v>
+        <v>57558</v>
       </c>
       <c r="AO40" s="14">
-        <v>285415</v>
+        <v>285425</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="38"/>
-        <v>0.99286869705877234</v>
+        <v>0.99290348390238814</v>
       </c>
       <c r="AQ40" s="8">
         <v>346543</v>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="39"/>
-        <v>69333</v>
+        <v>69344</v>
       </c>
       <c r="AT40" s="14">
-        <v>345823</v>
+        <v>345834</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="40"/>
-        <v>0.99792233575631306</v>
+        <v>0.99795407784892498</v>
       </c>
       <c r="AV40" s="8">
         <v>288959</v>
@@ -7586,14 +7586,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="41"/>
-        <v>60340</v>
+        <v>60351</v>
       </c>
       <c r="AY40" s="14">
-        <v>287646</v>
+        <v>287657</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="42"/>
-        <v>0.99545610276890495</v>
+        <v>0.99549417045324773</v>
       </c>
       <c r="BA40" s="8">
         <v>291465</v>
@@ -7603,14 +7603,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="43"/>
-        <v>55944</v>
+        <v>55959</v>
       </c>
       <c r="BD40" s="14">
-        <v>288791</v>
+        <v>288806</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="44"/>
-        <v>0.99082565659684696</v>
+        <v>0.9908771207520628</v>
       </c>
       <c r="BF40" s="8">
         <v>351557</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="45"/>
-        <v>85115</v>
+        <v>85138</v>
       </c>
       <c r="BI40" s="14">
-        <v>348707</v>
+        <v>348730</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="46"/>
-        <v>0.99189320650705293</v>
+        <v>0.99195862975278548</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="0"/>
-        <v>143380</v>
+        <v>143395</v>
       </c>
       <c r="F41" s="14">
-        <v>904667</v>
+        <v>904682</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="24"/>
-        <v>0.99183545039326226</v>
+        <v>0.99185189570601917</v>
       </c>
       <c r="H41" s="8">
         <v>920596</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="25"/>
-        <v>139002</v>
+        <v>139017</v>
       </c>
       <c r="K41" s="14">
-        <v>909696</v>
+        <v>909711</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="26"/>
-        <v>0.98815984427479586</v>
+        <v>0.98817613806707827</v>
       </c>
       <c r="M41" s="8">
         <v>1028922</v>
@@ -7679,14 +7679,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="27"/>
-        <v>156571</v>
+        <v>156584</v>
       </c>
       <c r="P41" s="14">
-        <v>1016708</v>
+        <v>1016721</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="28"/>
-        <v>0.98812932369994999</v>
+        <v>0.98814195828255202</v>
       </c>
       <c r="R41" s="8">
         <v>924082</v>
@@ -7696,14 +7696,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="29"/>
-        <v>157498</v>
+        <v>157513</v>
       </c>
       <c r="U41" s="14">
-        <v>914367</v>
+        <v>914382</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="30"/>
-        <v>0.98948686371988637</v>
+        <v>0.98950309604558906</v>
       </c>
       <c r="W41" s="8">
         <v>929406</v>
@@ -7713,14 +7713,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="31"/>
-        <v>146237</v>
+        <v>146255</v>
       </c>
       <c r="Z41" s="14">
-        <v>918140</v>
+        <v>918158</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="32"/>
-        <v>0.98787827924502314</v>
+        <v>0.98789764645375644</v>
       </c>
       <c r="AB41" s="8">
         <v>1036539</v>
@@ -7730,14 +7730,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="33"/>
-        <v>166484</v>
+        <v>166510</v>
       </c>
       <c r="AE41" s="14">
-        <v>1025842</v>
+        <v>1025868</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="34"/>
-        <v>0.98968007957250037</v>
+        <v>0.98970516304741063</v>
       </c>
       <c r="AG41" s="8">
         <v>935526</v>
@@ -7747,14 +7747,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="35"/>
-        <v>150479</v>
+        <v>150502</v>
       </c>
       <c r="AJ41" s="14">
-        <v>924942</v>
+        <v>924965</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="36"/>
-        <v>0.9886865784596045</v>
+        <v>0.98871116355932387</v>
       </c>
       <c r="AL41" s="8">
         <v>940174</v>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="37"/>
-        <v>143207</v>
+        <v>143230</v>
       </c>
       <c r="AO41" s="14">
-        <v>929413</v>
+        <v>929436</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="38"/>
-        <v>0.98855424634163458</v>
+        <v>0.98857870989838048</v>
       </c>
       <c r="AQ41" s="8">
         <v>1046219</v>
@@ -7781,14 +7781,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="39"/>
-        <v>165595</v>
+        <v>165626</v>
       </c>
       <c r="AT41" s="14">
-        <v>1037482</v>
+        <v>1037513</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="40"/>
-        <v>0.99164897597921664</v>
+        <v>0.99167860648678718</v>
       </c>
       <c r="AV41" s="8">
         <v>945246</v>
@@ -7798,14 +7798,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="41"/>
-        <v>138728</v>
+        <v>138763</v>
       </c>
       <c r="AY41" s="14">
-        <v>936438</v>
+        <v>936473</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="42"/>
-        <v>0.99068179077192609</v>
+        <v>0.99071881817008478</v>
       </c>
       <c r="BA41" s="8">
         <v>950318</v>
@@ -7815,14 +7815,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="43"/>
-        <v>134235</v>
+        <v>134265</v>
       </c>
       <c r="BD41" s="14">
-        <v>940040</v>
+        <v>940070</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="44"/>
-        <v>0.989184672920012</v>
+        <v>0.98921624130028052</v>
       </c>
       <c r="BF41" s="8">
         <v>1056723</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="45"/>
-        <v>199438</v>
+        <v>199485</v>
       </c>
       <c r="BI41" s="14">
-        <v>1047414</v>
+        <v>1047461</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="46"/>
-        <v>0.99119069046476704</v>
+        <v>0.99123516758885721</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7891,14 +7891,14 @@
       </c>
       <c r="O42" s="4">
         <f t="shared" si="27"/>
-        <v>4076</v>
+        <v>4077</v>
       </c>
       <c r="P42" s="14">
-        <v>20359</v>
+        <v>20360</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" si="28"/>
-        <v>0.9834315525070042</v>
+        <v>0.98347985701864549</v>
       </c>
       <c r="R42" s="8">
         <v>18543</v>
@@ -7908,14 +7908,14 @@
       </c>
       <c r="T42" s="4">
         <f t="shared" si="29"/>
-        <v>4114</v>
+        <v>4115</v>
       </c>
       <c r="U42" s="14">
-        <v>18331</v>
+        <v>18332</v>
       </c>
       <c r="V42" s="5">
         <f t="shared" si="30"/>
-        <v>0.98856711427492849</v>
+        <v>0.98862104298117892</v>
       </c>
       <c r="W42" s="8">
         <v>18720</v>
@@ -7925,14 +7925,14 @@
       </c>
       <c r="Y42" s="4">
         <f t="shared" si="31"/>
-        <v>3882</v>
+        <v>3883</v>
       </c>
       <c r="Z42" s="14">
-        <v>18378</v>
+        <v>18379</v>
       </c>
       <c r="AA42" s="5">
         <f t="shared" si="32"/>
-        <v>0.98173076923076918</v>
+        <v>0.98178418803418799</v>
       </c>
       <c r="AB42" s="8">
         <v>20718</v>
@@ -7942,14 +7942,14 @@
       </c>
       <c r="AD42" s="4">
         <f t="shared" si="33"/>
-        <v>4360</v>
+        <v>4361</v>
       </c>
       <c r="AE42" s="14">
-        <v>20313</v>
+        <v>20314</v>
       </c>
       <c r="AF42" s="5">
         <f t="shared" si="34"/>
-        <v>0.9804517810599479</v>
+        <v>0.98050004826720727</v>
       </c>
       <c r="AG42" s="8">
         <v>18665</v>
@@ -7959,14 +7959,14 @@
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="35"/>
-        <v>3826</v>
+        <v>3827</v>
       </c>
       <c r="AJ42" s="14">
-        <v>18390</v>
+        <v>18391</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="36"/>
-        <v>0.98526654165550498</v>
+        <v>0.98532011786766671</v>
       </c>
       <c r="AL42" s="8">
         <v>18792</v>
@@ -7976,14 +7976,14 @@
       </c>
       <c r="AN42" s="4">
         <f t="shared" si="37"/>
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="AO42" s="14">
-        <v>18512</v>
+        <v>18514</v>
       </c>
       <c r="AP42" s="5">
         <f t="shared" si="38"/>
-        <v>0.9851000425713069</v>
+        <v>0.98520647083865476</v>
       </c>
       <c r="AQ42" s="8">
         <v>20796</v>
@@ -7993,14 +7993,14 @@
       </c>
       <c r="AS42" s="4">
         <f t="shared" si="39"/>
-        <v>4234</v>
+        <v>4236</v>
       </c>
       <c r="AT42" s="14">
-        <v>20552</v>
+        <v>20554</v>
       </c>
       <c r="AU42" s="5">
         <f t="shared" si="40"/>
-        <v>0.98826697441815736</v>
+        <v>0.98836314675899206</v>
       </c>
       <c r="AV42" s="8">
         <v>18829</v>
@@ -8010,14 +8010,14 @@
       </c>
       <c r="AX42" s="4">
         <f t="shared" si="41"/>
-        <v>3674</v>
+        <v>3675</v>
       </c>
       <c r="AY42" s="14">
-        <v>18589</v>
+        <v>18590</v>
       </c>
       <c r="AZ42" s="5">
         <f t="shared" si="42"/>
-        <v>0.98725370439216098</v>
+        <v>0.98730681395719366</v>
       </c>
       <c r="BA42" s="8">
         <v>18938</v>
@@ -8027,14 +8027,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="43"/>
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="BD42" s="14">
-        <v>18695</v>
+        <v>18696</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="44"/>
-        <v>0.98716865561305311</v>
+        <v>0.9872214594994192</v>
       </c>
       <c r="BF42" s="8">
         <v>21042</v>
@@ -8044,14 +8044,14 @@
       </c>
       <c r="BH42" s="4">
         <f t="shared" si="45"/>
-        <v>4848</v>
+        <v>4849</v>
       </c>
       <c r="BI42" s="14">
-        <v>20778</v>
+        <v>20779</v>
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="46"/>
-        <v>0.98745366410037072</v>
+        <v>0.98750118809999055</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8069,14 +8069,14 @@
       </c>
       <c r="E43" s="4">
         <f t="shared" si="0"/>
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="F43" s="14">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="24"/>
-        <v>0.99913169319826334</v>
+        <v>0.99942112879884226</v>
       </c>
       <c r="H43" s="8">
         <v>3541</v>
@@ -8086,14 +8086,14 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" si="25"/>
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="K43" s="14">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="26"/>
-        <v>0.98164360350183566</v>
+        <v>0.98192600960180743</v>
       </c>
       <c r="M43" s="8">
         <v>4395</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" si="27"/>
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="P43" s="14">
-        <v>4340</v>
+        <v>4341</v>
       </c>
       <c r="Q43" s="5">
         <f t="shared" si="28"/>
-        <v>0.98748577929465298</v>
+        <v>0.98771331058020473</v>
       </c>
       <c r="R43" s="8">
         <v>3498</v>
@@ -8281,14 +8281,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="0"/>
-        <v>76616</v>
+        <v>76621</v>
       </c>
       <c r="F44" s="14">
-        <v>333317</v>
+        <v>333322</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="24"/>
-        <v>0.99134218447006195</v>
+        <v>0.9913570553315012</v>
       </c>
       <c r="H44" s="8">
         <v>340996</v>
@@ -8298,14 +8298,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="25"/>
-        <v>75667</v>
+        <v>75672</v>
       </c>
       <c r="K44" s="14">
-        <v>337280</v>
+        <v>337285</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="26"/>
-        <v>0.98910251146641015</v>
+        <v>0.98911717439500757</v>
       </c>
       <c r="M44" s="8">
         <v>408512</v>
@@ -8315,14 +8315,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="27"/>
-        <v>87279</v>
+        <v>87285</v>
       </c>
       <c r="P44" s="14">
-        <v>403990</v>
+        <v>403996</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="28"/>
-        <v>0.9889305577314742</v>
+        <v>0.98894524518251603</v>
       </c>
       <c r="R44" s="8">
         <v>342556</v>
@@ -8332,14 +8332,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="29"/>
-        <v>80300</v>
+        <v>80308</v>
       </c>
       <c r="U44" s="14">
-        <v>339388</v>
+        <v>339396</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="30"/>
-        <v>0.99075187706535572</v>
+        <v>0.99077523091115027</v>
       </c>
       <c r="W44" s="8">
         <v>347597</v>
@@ -8349,14 +8349,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="31"/>
-        <v>79014</v>
+        <v>79021</v>
       </c>
       <c r="Z44" s="14">
-        <v>343157</v>
+        <v>343164</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="32"/>
-        <v>0.98722658711093592</v>
+        <v>0.98724672537449976</v>
       </c>
       <c r="AB44" s="8">
         <v>416340</v>
@@ -8366,14 +8366,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="33"/>
-        <v>92053</v>
+        <v>92061</v>
       </c>
       <c r="AE44" s="14">
-        <v>412353</v>
+        <v>412361</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="34"/>
-        <v>0.99042369217466497</v>
+        <v>0.99044290723927564</v>
       </c>
       <c r="AG44" s="8">
         <v>350469</v>
@@ -8383,14 +8383,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="35"/>
-        <v>79567</v>
+        <v>79576</v>
       </c>
       <c r="AJ44" s="14">
-        <v>347339</v>
+        <v>347348</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="36"/>
-        <v>0.99106911024940869</v>
+        <v>0.99109479012409085</v>
       </c>
       <c r="AL44" s="8">
         <v>355186</v>
@@ -8400,14 +8400,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="37"/>
-        <v>72527</v>
+        <v>72537</v>
       </c>
       <c r="AO44" s="14">
-        <v>350808</v>
+        <v>350818</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="38"/>
-        <v>0.98767406372998934</v>
+        <v>0.98770221799282631</v>
       </c>
       <c r="AQ44" s="8">
         <v>424208</v>
@@ -8417,14 +8417,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="39"/>
-        <v>85711</v>
+        <v>85721</v>
       </c>
       <c r="AT44" s="14">
-        <v>420947</v>
+        <v>420957</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="40"/>
-        <v>0.99231273337607961</v>
+        <v>0.99233630671745932</v>
       </c>
       <c r="AV44" s="8">
         <v>358114</v>
@@ -8434,14 +8434,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="41"/>
-        <v>72307</v>
+        <v>72317</v>
       </c>
       <c r="AY44" s="14">
-        <v>354422</v>
+        <v>354432</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="42"/>
-        <v>0.98969043377248589</v>
+        <v>0.98971835784135775</v>
       </c>
       <c r="BA44" s="8">
         <v>361984</v>
@@ -8451,14 +8451,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="43"/>
-        <v>71195</v>
+        <v>71204</v>
       </c>
       <c r="BD44" s="14">
-        <v>357383</v>
+        <v>357392</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="44"/>
-        <v>0.98728949345827444</v>
+        <v>0.98731435643564358</v>
       </c>
       <c r="BF44" s="8">
         <v>432310</v>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="45"/>
-        <v>106850</v>
+        <v>106866</v>
       </c>
       <c r="BI44" s="14">
-        <v>427027</v>
+        <v>427043</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="46"/>
-        <v>0.9877796025999861</v>
+        <v>0.98781661307857782</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8493,14 +8493,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="0"/>
-        <v>52302</v>
+        <v>52303</v>
       </c>
       <c r="F45" s="14">
-        <v>251296</v>
+        <v>251297</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="24"/>
-        <v>0.98332276821699971</v>
+        <v>0.98332668122304923</v>
       </c>
       <c r="H45" s="8">
         <v>257610</v>
@@ -8527,14 +8527,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="27"/>
-        <v>59533</v>
+        <v>59537</v>
       </c>
       <c r="P45" s="14">
-        <v>304805</v>
+        <v>304809</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="28"/>
-        <v>0.98208244459766858</v>
+        <v>0.98209533260730875</v>
       </c>
       <c r="R45" s="8">
         <v>257356</v>
@@ -8544,14 +8544,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="29"/>
-        <v>53293</v>
+        <v>53296</v>
       </c>
       <c r="U45" s="14">
-        <v>253714</v>
+        <v>253717</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="30"/>
-        <v>0.98584839677334124</v>
+        <v>0.98586005377764652</v>
       </c>
       <c r="W45" s="8">
         <v>260553</v>
@@ -8561,14 +8561,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="31"/>
-        <v>55331</v>
+        <v>55334</v>
       </c>
       <c r="Z45" s="14">
-        <v>255675</v>
+        <v>255678</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="32"/>
-        <v>0.98127828119422922</v>
+        <v>0.98128979516643444</v>
       </c>
       <c r="AB45" s="8">
         <v>313911</v>
@@ -8578,14 +8578,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="33"/>
-        <v>65024</v>
+        <v>65028</v>
       </c>
       <c r="AE45" s="14">
-        <v>308431</v>
+        <v>308435</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="34"/>
-        <v>0.9825428226471834</v>
+        <v>0.98255556511240449</v>
       </c>
       <c r="AG45" s="8">
         <v>261210</v>
@@ -8595,14 +8595,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="35"/>
-        <v>53736</v>
+        <v>53744</v>
       </c>
       <c r="AJ45" s="14">
-        <v>257066</v>
+        <v>257074</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="36"/>
-        <v>0.98413537000880513</v>
+        <v>0.98416599670762983</v>
       </c>
       <c r="AL45" s="8">
         <v>264020</v>
@@ -8612,14 +8612,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="37"/>
-        <v>48974</v>
+        <v>48980</v>
       </c>
       <c r="AO45" s="14">
-        <v>259383</v>
+        <v>259389</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="38"/>
-        <v>0.98243693659571241</v>
+        <v>0.98245966214680702</v>
       </c>
       <c r="AQ45" s="8">
         <v>317407</v>
@@ -8629,14 +8629,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="39"/>
-        <v>63286</v>
+        <v>63296</v>
       </c>
       <c r="AT45" s="14">
-        <v>311476</v>
+        <v>311486</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="40"/>
-        <v>0.98131421172185873</v>
+        <v>0.98134571701317241</v>
       </c>
       <c r="AV45" s="8">
         <v>263886</v>
@@ -8646,14 +8646,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="41"/>
-        <v>51105</v>
+        <v>51113</v>
       </c>
       <c r="AY45" s="14">
-        <v>259531</v>
+        <v>259539</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="42"/>
-        <v>0.98349666143713577</v>
+        <v>0.98352697755849117</v>
       </c>
       <c r="BA45" s="8">
         <v>265781</v>
@@ -8663,14 +8663,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="43"/>
-        <v>49556</v>
+        <v>49565</v>
       </c>
       <c r="BD45" s="14">
-        <v>261244</v>
+        <v>261253</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="44"/>
-        <v>0.98292955478382582</v>
+        <v>0.98296341724954006</v>
       </c>
       <c r="BF45" s="8">
         <v>319799</v>
@@ -8680,14 +8680,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="45"/>
-        <v>79735</v>
+        <v>79750</v>
       </c>
       <c r="BI45" s="14">
-        <v>314544</v>
+        <v>314559</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="46"/>
-        <v>0.98356780352659012</v>
+        <v>0.98361470798845529</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8705,14 +8705,14 @@
       </c>
       <c r="E46" s="4">
         <f t="shared" si="0"/>
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F46" s="14">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="24"/>
-        <v>1.0718157181571815</v>
+        <v>1.0722673893405601</v>
       </c>
       <c r="H46" s="8">
         <v>2377</v>
@@ -8722,14 +8722,14 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" si="25"/>
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="K46" s="14">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="26"/>
-        <v>1.0588977702986959</v>
+        <v>1.0593184686579722</v>
       </c>
       <c r="M46" s="8">
         <v>6689</v>
@@ -8739,14 +8739,14 @@
       </c>
       <c r="O46" s="4">
         <f t="shared" si="27"/>
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="P46" s="14">
-        <v>6869</v>
+        <v>6870</v>
       </c>
       <c r="Q46" s="5">
         <f t="shared" si="28"/>
-        <v>1.026909851995814</v>
+        <v>1.0270593511735686</v>
       </c>
       <c r="R46" s="8">
         <v>2186</v>
@@ -8756,14 +8756,14 @@
       </c>
       <c r="T46" s="4">
         <f t="shared" si="29"/>
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="U46" s="14">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="V46" s="5">
         <f t="shared" si="30"/>
-        <v>1.0718206770356815</v>
+        <v>1.0722781335773102</v>
       </c>
       <c r="W46" s="8">
         <v>2396</v>
@@ -8773,14 +8773,14 @@
       </c>
       <c r="Y46" s="4">
         <f t="shared" si="31"/>
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="Z46" s="14">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="32"/>
-        <v>1.025041736227045</v>
+        <v>1.0254590984974958</v>
       </c>
       <c r="AB46" s="8">
         <v>6920</v>
@@ -8790,14 +8790,14 @@
       </c>
       <c r="AD46" s="4">
         <f t="shared" si="33"/>
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="AE46" s="14">
-        <v>7156</v>
+        <v>7158</v>
       </c>
       <c r="AF46" s="5">
         <f t="shared" si="34"/>
-        <v>1.0341040462427746</v>
+        <v>1.034393063583815</v>
       </c>
       <c r="AG46" s="8">
         <v>2260</v>
@@ -8807,14 +8807,14 @@
       </c>
       <c r="AI46" s="4">
         <f t="shared" si="35"/>
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AJ46" s="14">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="AK46" s="5">
         <f t="shared" si="36"/>
-        <v>1.0486725663716814</v>
+        <v>1.0491150442477877</v>
       </c>
       <c r="AL46" s="8">
         <v>2436</v>
@@ -8824,14 +8824,14 @@
       </c>
       <c r="AN46" s="4">
         <f t="shared" si="37"/>
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AO46" s="14">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="AP46" s="5">
         <f t="shared" si="38"/>
-        <v>1.0102627257799672</v>
+        <v>1.0106732348111658</v>
       </c>
       <c r="AQ46" s="8">
         <v>7143</v>
@@ -8841,14 +8841,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="39"/>
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="AT46" s="14">
-        <v>7358</v>
+        <v>7359</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="40"/>
-        <v>1.0300993980120399</v>
+        <v>1.0302393952120958</v>
       </c>
       <c r="AV46" s="8">
         <v>2225</v>
@@ -8858,14 +8858,14 @@
       </c>
       <c r="AX46" s="4">
         <f t="shared" si="41"/>
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AY46" s="14">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="AZ46" s="5">
         <f t="shared" si="42"/>
-        <v>1.0629213483146067</v>
+        <v>1.063370786516854</v>
       </c>
       <c r="BA46" s="8">
         <v>2388</v>
@@ -8875,14 +8875,14 @@
       </c>
       <c r="BC46" s="4">
         <f t="shared" si="43"/>
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="BD46" s="14">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="BE46" s="5">
         <f t="shared" si="44"/>
-        <v>1.0175879396984924</v>
+        <v>1.018425460636516</v>
       </c>
       <c r="BF46" s="8">
         <v>7407</v>
@@ -8892,14 +8892,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="45"/>
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="BI46" s="14">
-        <v>7550</v>
+        <v>7551</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="46"/>
-        <v>1.0193060618334009</v>
+        <v>1.0194410692588092</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9115,10 +9115,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A48" s="22" t="s">
+      <c r="A48" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="22"/>
+      <c r="B48" s="27"/>
       <c r="C48" s="10">
         <f>SUM(C10:C47)</f>
         <v>7712416</v>
@@ -9129,15 +9129,15 @@
       </c>
       <c r="E48" s="12">
         <f t="shared" ref="E48" si="47">F48-D48</f>
-        <v>1449776</v>
+        <v>1449869</v>
       </c>
       <c r="F48" s="11">
         <f>SUM(F10:F47)</f>
-        <v>7677471</v>
+        <v>7677564</v>
       </c>
       <c r="G48" s="13">
         <f t="shared" ref="G48" si="48">F48/C48</f>
-        <v>0.99546899441108982</v>
+        <v>0.99548105288926325</v>
       </c>
       <c r="H48" s="10">
         <f>SUM(H10:H47)</f>
@@ -9149,15 +9149,15 @@
       </c>
       <c r="J48" s="12">
         <f t="shared" si="25"/>
-        <v>1416144</v>
+        <v>1416245</v>
       </c>
       <c r="K48" s="11">
         <f>SUM(K10:K47)</f>
-        <v>7772779</v>
+        <v>7772880</v>
       </c>
       <c r="L48" s="13">
         <f t="shared" si="26"/>
-        <v>0.98798006036090447</v>
+        <v>0.98799289823859238</v>
       </c>
       <c r="M48" s="10">
         <f>SUM(M10:M47)</f>
@@ -9169,15 +9169,15 @@
       </c>
       <c r="O48" s="12">
         <f t="shared" si="27"/>
-        <v>2192810</v>
+        <v>2193012</v>
       </c>
       <c r="P48" s="11">
         <f>SUM(P10:P47)</f>
-        <v>12049867</v>
+        <v>12050069</v>
       </c>
       <c r="Q48" s="13">
         <f t="shared" si="28"/>
-        <v>0.99157481263555103</v>
+        <v>0.99159143506898972</v>
       </c>
       <c r="R48" s="10">
         <f>SUM(R10:R47)</f>
@@ -9189,15 +9189,15 @@
       </c>
       <c r="T48" s="12">
         <f t="shared" ref="T48" si="49">U48-S48</f>
-        <v>1489053</v>
+        <v>1489195</v>
       </c>
       <c r="U48" s="11">
         <f>SUM(U10:U47)</f>
-        <v>7743505</v>
+        <v>7743647</v>
       </c>
       <c r="V48" s="13">
         <f t="shared" si="30"/>
-        <v>0.99200757683970298</v>
+        <v>0.99202576822408406</v>
       </c>
       <c r="W48" s="10">
         <f>SUM(W10:W47)</f>
@@ -9209,15 +9209,15 @@
       </c>
       <c r="Y48" s="12">
         <f t="shared" si="31"/>
-        <v>1484581</v>
+        <v>1484743</v>
       </c>
       <c r="Z48" s="11">
         <f>SUM(Z10:Z47)</f>
-        <v>7828025</v>
+        <v>7828187</v>
       </c>
       <c r="AA48" s="13">
         <f t="shared" si="32"/>
-        <v>0.98492595023724083</v>
+        <v>0.98494633315680713</v>
       </c>
       <c r="AB48" s="10">
         <f>SUM(AB10:AB47)</f>
@@ -9229,15 +9229,15 @@
       </c>
       <c r="AD48" s="12">
         <f t="shared" si="33"/>
-        <v>2328872</v>
+        <v>2329156</v>
       </c>
       <c r="AE48" s="11">
         <f>SUM(AE10:AE47)</f>
-        <v>12195719</v>
+        <v>12196003</v>
       </c>
       <c r="AF48" s="13">
         <f t="shared" si="34"/>
-        <v>0.9927988675515067</v>
+        <v>0.99282198671966604</v>
       </c>
       <c r="AG48" s="10">
         <f>SUM(AG10:AG47)</f>
@@ -9249,15 +9249,15 @@
       </c>
       <c r="AI48" s="12">
         <f t="shared" si="35"/>
-        <v>1608662</v>
+        <v>1608878</v>
       </c>
       <c r="AJ48" s="11">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7874840</v>
+        <v>7875056</v>
       </c>
       <c r="AK48" s="13">
         <f t="shared" si="36"/>
-        <v>0.9924951974859807</v>
+        <v>0.99252242076450525</v>
       </c>
       <c r="AL48" s="10">
         <f>SUM(AL10:AL47)</f>
@@ -9269,15 +9269,15 @@
       </c>
       <c r="AN48" s="12">
         <f t="shared" si="37"/>
-        <v>1382649</v>
+        <v>1382888</v>
       </c>
       <c r="AO48" s="11">
         <f>SUM(AO10:AO47)</f>
-        <v>7957028</v>
+        <v>7957267</v>
       </c>
       <c r="AP48" s="13">
         <f t="shared" si="38"/>
-        <v>0.98496634947404071</v>
+        <v>0.98499593425840049</v>
       </c>
       <c r="AQ48" s="10">
         <f>SUM(AQ10:AQ47)</f>
@@ -9289,15 +9289,15 @@
       </c>
       <c r="AS48" s="12">
         <f t="shared" si="39"/>
-        <v>2139071</v>
+        <v>2139476</v>
       </c>
       <c r="AT48" s="11">
         <f>SUM(AT10:AT47)</f>
-        <v>12387788</v>
+        <v>12388193</v>
       </c>
       <c r="AU48" s="13">
         <f t="shared" si="40"/>
-        <v>0.99538313666117972</v>
+        <v>0.99541567920794816</v>
       </c>
       <c r="AV48" s="10">
         <f>SUM(AV10:AV47)</f>
@@ -9309,15 +9309,15 @@
       </c>
       <c r="AX48" s="12">
         <f t="shared" si="41"/>
-        <v>1372653</v>
+        <v>1372940</v>
       </c>
       <c r="AY48" s="11">
         <f>SUM(AY10:AY47)</f>
-        <v>8013868</v>
+        <v>8014155</v>
       </c>
       <c r="AZ48" s="13">
         <f t="shared" si="42"/>
-        <v>0.99411164601004098</v>
+        <v>0.99414724804920673</v>
       </c>
       <c r="BA48" s="10">
         <f>SUM(BA10:BA47)</f>
@@ -9329,15 +9329,15 @@
       </c>
       <c r="BC48" s="12">
         <f t="shared" si="43"/>
-        <v>1320879</v>
+        <v>1321183</v>
       </c>
       <c r="BD48" s="11">
         <f>SUM(BD10:BD47)</f>
-        <v>8098057</v>
+        <v>8098361</v>
       </c>
       <c r="BE48" s="13">
         <f t="shared" si="44"/>
-        <v>0.98727234712046574</v>
+        <v>0.98730940919517385</v>
       </c>
       <c r="BF48" s="10">
         <f>SUM(BF10:BF47)</f>
@@ -9349,15 +9349,15 @@
       </c>
       <c r="BH48" s="12">
         <f t="shared" si="45"/>
-        <v>2709422</v>
+        <v>2709991</v>
       </c>
       <c r="BI48" s="11">
         <f>SUM(BI10:BI47)</f>
-        <v>12555903</v>
+        <v>12556472</v>
       </c>
       <c r="BJ48" s="13">
         <f t="shared" si="46"/>
-        <v>0.99208624168975179</v>
+        <v>0.99213120038937863</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
@@ -9580,18 +9580,23 @@
       <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A55" s="21" t="s">
+      <c r="A55" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
       <c r="F55" s="6"/>
       <c r="G55" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="AV8:AZ8"/>
@@ -9605,11 +9610,6 @@
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2023-2024.xlsx
+++ b/gstdatabase/GSTR-3B-2023-2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC45CEA-3FAA-4FC4-966E-C5E70D1F95F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976BE507-149D-4303-AF47-0A39A49B64BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2023-2024</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -415,21 +415,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -441,6 +426,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -733,7 +733,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BJ55"/>
+  <dimension ref="A1:BJ53"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.21875" bestFit="1" customWidth="1"/>
@@ -741,12 +741,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -758,10 +758,10 @@
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="21"/>
+      <c r="B3" s="28"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -807,100 +807,100 @@
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:62" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="25">
         <v>45017</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="23">
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="25">
         <v>45047</v>
       </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="23">
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="25">
         <v>45078</v>
       </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="23">
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="25">
         <v>45108</v>
       </c>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="23">
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="26"/>
+      <c r="V8" s="27"/>
+      <c r="W8" s="25">
         <v>45139</v>
       </c>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="23">
+      <c r="X8" s="26"/>
+      <c r="Y8" s="26"/>
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="27"/>
+      <c r="AB8" s="25">
         <v>45170</v>
       </c>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="25"/>
-      <c r="AG8" s="23">
+      <c r="AC8" s="26"/>
+      <c r="AD8" s="26"/>
+      <c r="AE8" s="26"/>
+      <c r="AF8" s="27"/>
+      <c r="AG8" s="25">
         <v>45200</v>
       </c>
-      <c r="AH8" s="24"/>
-      <c r="AI8" s="24"/>
-      <c r="AJ8" s="24"/>
-      <c r="AK8" s="25"/>
-      <c r="AL8" s="23">
+      <c r="AH8" s="26"/>
+      <c r="AI8" s="26"/>
+      <c r="AJ8" s="26"/>
+      <c r="AK8" s="27"/>
+      <c r="AL8" s="25">
         <v>45231</v>
       </c>
-      <c r="AM8" s="24"/>
-      <c r="AN8" s="24"/>
-      <c r="AO8" s="24"/>
-      <c r="AP8" s="25"/>
-      <c r="AQ8" s="23">
+      <c r="AM8" s="26"/>
+      <c r="AN8" s="26"/>
+      <c r="AO8" s="26"/>
+      <c r="AP8" s="27"/>
+      <c r="AQ8" s="25">
         <v>45261</v>
       </c>
-      <c r="AR8" s="24"/>
-      <c r="AS8" s="24"/>
-      <c r="AT8" s="24"/>
-      <c r="AU8" s="25"/>
-      <c r="AV8" s="23">
+      <c r="AR8" s="26"/>
+      <c r="AS8" s="26"/>
+      <c r="AT8" s="26"/>
+      <c r="AU8" s="27"/>
+      <c r="AV8" s="25">
         <v>45292</v>
       </c>
-      <c r="AW8" s="24"/>
-      <c r="AX8" s="24"/>
-      <c r="AY8" s="24"/>
-      <c r="AZ8" s="25"/>
-      <c r="BA8" s="23">
+      <c r="AW8" s="26"/>
+      <c r="AX8" s="26"/>
+      <c r="AY8" s="26"/>
+      <c r="AZ8" s="27"/>
+      <c r="BA8" s="25">
         <v>45323</v>
       </c>
-      <c r="BB8" s="24"/>
-      <c r="BC8" s="24"/>
-      <c r="BD8" s="24"/>
-      <c r="BE8" s="25"/>
-      <c r="BF8" s="23">
+      <c r="BB8" s="26"/>
+      <c r="BC8" s="26"/>
+      <c r="BD8" s="26"/>
+      <c r="BE8" s="27"/>
+      <c r="BF8" s="25">
         <v>45352</v>
       </c>
-      <c r="BG8" s="24"/>
-      <c r="BH8" s="24"/>
-      <c r="BI8" s="24"/>
-      <c r="BJ8" s="25"/>
+      <c r="BG8" s="26"/>
+      <c r="BH8" s="26"/>
+      <c r="BI8" s="26"/>
+      <c r="BJ8" s="27"/>
     </row>
     <row r="9" spans="1:62" s="16" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="17" t="s">
         <v>2</v>
       </c>
@@ -1131,14 +1131,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>23852</v>
+        <v>23854</v>
       </c>
       <c r="P10" s="14">
-        <v>120205</v>
+        <v>120207</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.99783341357727495</v>
+        <v>0.9978500157720851</v>
       </c>
       <c r="R10" s="8">
         <v>70979</v>
@@ -1199,14 +1199,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>15069</v>
+        <v>15070</v>
       </c>
       <c r="AJ10" s="14">
-        <v>72017</v>
+        <v>72018</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>1.0009312022237664</v>
+        <v>1.0009451007644197</v>
       </c>
       <c r="AL10" s="8">
         <v>73532</v>
@@ -1216,14 +1216,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>14451</v>
+        <v>14453</v>
       </c>
       <c r="AO10" s="14">
-        <v>72986</v>
+        <v>72988</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>0.99257466137191974</v>
+        <v>0.99260186041451337</v>
       </c>
       <c r="AQ10" s="8">
         <v>125499</v>
@@ -1233,14 +1233,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>22106</v>
+        <v>22109</v>
       </c>
       <c r="AT10" s="14">
-        <v>125745</v>
+        <v>125748</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>1.0019601749814739</v>
+        <v>1.0019840795544188</v>
       </c>
       <c r="AV10" s="8">
         <v>72481</v>
@@ -1250,14 +1250,14 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>14007</v>
+        <v>14009</v>
       </c>
       <c r="AY10" s="14">
-        <v>72379</v>
+        <v>72381</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>0.99859273464770082</v>
+        <v>0.99862032808598111</v>
       </c>
       <c r="BA10" s="8">
         <v>73790</v>
@@ -1267,14 +1267,14 @@
       </c>
       <c r="BC10" s="4">
         <f>BD10-BB10</f>
-        <v>13149</v>
+        <v>13151</v>
       </c>
       <c r="BD10" s="14">
-        <v>73303</v>
+        <v>73305</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10/BA10</f>
-        <v>0.99340018972760535</v>
+        <v>0.99342729367122917</v>
       </c>
       <c r="BF10" s="8">
         <v>128129</v>
@@ -1284,14 +1284,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>30704</v>
+        <v>30707</v>
       </c>
       <c r="BI10" s="14">
-        <v>127904</v>
+        <v>127907</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.99824395726182202</v>
+        <v>0.99826737116499775</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1309,14 +1309,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E47" si="0">F11-D11</f>
-        <v>8352</v>
+        <v>8354</v>
       </c>
       <c r="F11" s="14">
-        <v>45070</v>
+        <v>45072</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>1.0124904524419285</v>
+        <v>1.0125353821269714</v>
       </c>
       <c r="H11" s="8">
         <v>46110</v>
@@ -1326,14 +1326,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>8438</v>
+        <v>8440</v>
       </c>
       <c r="K11" s="14">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>1.0002168726957277</v>
+        <v>1.0002602472348732</v>
       </c>
       <c r="M11" s="8">
         <v>102242</v>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>17897</v>
+        <v>17901</v>
       </c>
       <c r="P11" s="14">
-        <v>102363</v>
+        <v>102367</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>1.0011834666770993</v>
+        <v>1.001222589542458</v>
       </c>
       <c r="R11" s="8">
         <v>44890</v>
@@ -1360,14 +1360,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>8658</v>
+        <v>8660</v>
       </c>
       <c r="U11" s="14">
-        <v>45095</v>
+        <v>45097</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>1.004566718645578</v>
+        <v>1.0046112719982179</v>
       </c>
       <c r="W11" s="8">
         <v>46425</v>
@@ -1377,14 +1377,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8817</v>
+        <v>8819</v>
       </c>
       <c r="Z11" s="14">
-        <v>46021</v>
+        <v>46023</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.99129779213785674</v>
+        <v>0.99134087237479807</v>
       </c>
       <c r="AB11" s="8">
         <v>103964</v>
@@ -1394,14 +1394,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>17249</v>
+        <v>17253</v>
       </c>
       <c r="AE11" s="14">
-        <v>104134</v>
+        <v>104138</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>1.0016351814089492</v>
+        <v>1.0016736562656303</v>
       </c>
       <c r="AG11" s="8">
         <v>45569</v>
@@ -1411,14 +1411,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>8684</v>
+        <v>8689</v>
       </c>
       <c r="AJ11" s="14">
-        <v>45673</v>
+        <v>45678</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>1.0022822532862252</v>
+        <v>1.0023919770019092</v>
       </c>
       <c r="AL11" s="8">
         <v>46951</v>
@@ -1428,14 +1428,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>7784</v>
+        <v>7787</v>
       </c>
       <c r="AO11" s="14">
-        <v>46369</v>
+        <v>46372</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.98760409788928882</v>
+        <v>0.98766799429192131</v>
       </c>
       <c r="AQ11" s="8">
         <v>105644</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>15137</v>
+        <v>15143</v>
       </c>
       <c r="AT11" s="14">
-        <v>105851</v>
+        <v>105857</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>1.0019594108515391</v>
+        <v>1.002016205368975</v>
       </c>
       <c r="AV11" s="8">
         <v>46072</v>
@@ -1462,14 +1462,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>7553</v>
+        <v>7556</v>
       </c>
       <c r="AY11" s="14">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>1.0028433755860393</v>
+        <v>1.0029084910574753</v>
       </c>
       <c r="BA11" s="8">
         <v>47252</v>
@@ -1479,14 +1479,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>7187</v>
+        <v>7191</v>
       </c>
       <c r="BD11" s="14">
-        <v>47002</v>
+        <v>47006</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.99470921865741135</v>
+        <v>0.99479387115889273</v>
       </c>
       <c r="BF11" s="8">
         <v>107665</v>
@@ -1496,14 +1496,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>19643</v>
+        <v>19654</v>
       </c>
       <c r="BI11" s="14">
-        <v>107533</v>
+        <v>107544</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.99877397482933172</v>
+        <v>0.99887614359355403</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1589,14 +1589,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>27609</v>
+        <v>27610</v>
       </c>
       <c r="Z12" s="14">
-        <v>170067</v>
+        <v>170068</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.98954405809244517</v>
+        <v>0.98954987664665084</v>
       </c>
       <c r="AB12" s="8">
         <v>349048</v>
@@ -1606,14 +1606,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>58558</v>
+        <v>58561</v>
       </c>
       <c r="AE12" s="14">
-        <v>348027</v>
+        <v>348030</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.99707490087323236</v>
+        <v>0.99708349567967725</v>
       </c>
       <c r="AG12" s="8">
         <v>170526</v>
@@ -1623,14 +1623,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>27744</v>
+        <v>27747</v>
       </c>
       <c r="AJ12" s="14">
-        <v>170188</v>
+        <v>170191</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.99801789756400783</v>
+        <v>0.99803549018917936</v>
       </c>
       <c r="AL12" s="8">
         <v>174892</v>
@@ -1640,14 +1640,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>25078</v>
+        <v>25080</v>
       </c>
       <c r="AO12" s="14">
-        <v>172404</v>
+        <v>172406</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.98577407771653358</v>
+        <v>0.98578551334537889</v>
       </c>
       <c r="AQ12" s="8">
         <v>353589</v>
@@ -1657,14 +1657,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>50894</v>
+        <v>50897</v>
       </c>
       <c r="AT12" s="14">
-        <v>352804</v>
+        <v>352807</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.99777990831162733</v>
+        <v>0.99778839273846187</v>
       </c>
       <c r="AV12" s="8">
         <v>172980</v>
@@ -1674,14 +1674,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>24627</v>
+        <v>24629</v>
       </c>
       <c r="AY12" s="14">
-        <v>172344</v>
+        <v>172346</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.99632327436697887</v>
+        <v>0.99633483639727138</v>
       </c>
       <c r="BA12" s="8">
         <v>177212</v>
@@ -1691,14 +1691,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>24040</v>
+        <v>24044</v>
       </c>
       <c r="BD12" s="14">
-        <v>174791</v>
+        <v>174795</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.98633839694828795</v>
+        <v>0.98636096878315238</v>
       </c>
       <c r="BF12" s="8">
         <v>359260</v>
@@ -1708,14 +1708,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>65710</v>
+        <v>65717</v>
       </c>
       <c r="BI12" s="14">
-        <v>357416</v>
+        <v>357423</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.99486722707788233</v>
+        <v>0.99488671157379061</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1920,14 +1920,14 @@
       </c>
       <c r="BH13" s="4">
         <f t="shared" si="22"/>
-        <v>4904</v>
+        <v>4905</v>
       </c>
       <c r="BI13" s="14">
-        <v>28647</v>
+        <v>28648</v>
       </c>
       <c r="BJ13" s="5">
         <f t="shared" si="23"/>
-        <v>1.0025547700706936</v>
+        <v>1.0025897669209771</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -1945,14 +1945,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>18160</v>
+        <v>18162</v>
       </c>
       <c r="F14" s="14">
-        <v>85319</v>
+        <v>85321</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.99925043626951504</v>
+        <v>0.99927386013609265</v>
       </c>
       <c r="H14" s="8">
         <v>88261</v>
@@ -1962,14 +1962,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18273</v>
+        <v>18275</v>
       </c>
       <c r="K14" s="14">
-        <v>87142</v>
+        <v>87144</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.98732169361326072</v>
+        <v>0.98734435367829509</v>
       </c>
       <c r="M14" s="8">
         <v>157146</v>
@@ -1979,14 +1979,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>32108</v>
+        <v>32114</v>
       </c>
       <c r="P14" s="14">
-        <v>155509</v>
+        <v>155515</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.989582935614015</v>
+        <v>0.98962111666857577</v>
       </c>
       <c r="R14" s="8">
         <v>86469</v>
@@ -1996,14 +1996,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18345</v>
+        <v>18349</v>
       </c>
       <c r="U14" s="14">
-        <v>85410</v>
+        <v>85414</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.98775283627658472</v>
+        <v>0.98779909562964763</v>
       </c>
       <c r="W14" s="8">
         <v>88169</v>
@@ -2013,14 +2013,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>17862</v>
+        <v>17866</v>
       </c>
       <c r="Z14" s="14">
-        <v>86570</v>
+        <v>86574</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.98186437409974026</v>
+        <v>0.98190974151912802</v>
       </c>
       <c r="AB14" s="8">
         <v>157930</v>
@@ -2030,14 +2030,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>33751</v>
+        <v>33762</v>
       </c>
       <c r="AE14" s="14">
-        <v>157176</v>
+        <v>157187</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.995225732919648</v>
+        <v>0.99529538403089979</v>
       </c>
       <c r="AG14" s="8">
         <v>87312</v>
@@ -2047,14 +2047,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>19597</v>
+        <v>19601</v>
       </c>
       <c r="AJ14" s="14">
-        <v>86929</v>
+        <v>86933</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.99561343228880339</v>
+        <v>0.99565924500641378</v>
       </c>
       <c r="AL14" s="8">
         <v>89337</v>
@@ -2064,14 +2064,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>16995</v>
+        <v>17003</v>
       </c>
       <c r="AO14" s="14">
-        <v>87935</v>
+        <v>87943</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.98430661428075716</v>
+        <v>0.98439616284406239</v>
       </c>
       <c r="AQ14" s="8">
         <v>160173</v>
@@ -2081,14 +2081,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>29862</v>
+        <v>29870</v>
       </c>
       <c r="AT14" s="14">
-        <v>160303</v>
+        <v>160311</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>1.000811622433244</v>
+        <v>1.000861568429136</v>
       </c>
       <c r="AV14" s="8">
         <v>88523</v>
@@ -2098,14 +2098,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>17229</v>
+        <v>17233</v>
       </c>
       <c r="AY14" s="14">
-        <v>88589</v>
+        <v>88593</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>1.000745568948183</v>
+        <v>1.0007907549450425</v>
       </c>
       <c r="BA14" s="8">
         <v>90782</v>
@@ -2115,14 +2115,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>16194</v>
+        <v>16198</v>
       </c>
       <c r="BD14" s="14">
-        <v>89775</v>
+        <v>89779</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.9889074926747593</v>
+        <v>0.98895155427287351</v>
       </c>
       <c r="BF14" s="8">
         <v>163900</v>
@@ -2132,14 +2132,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>39490</v>
+        <v>39498</v>
       </c>
       <c r="BI14" s="14">
-        <v>162850</v>
+        <v>162858</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.99359365466748018</v>
+        <v>0.99364246491763275</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2157,14 +2157,14 @@
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
-        <v>48200</v>
+        <v>48201</v>
       </c>
       <c r="F15" s="14">
-        <v>282995</v>
+        <v>282996</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.99554284427746231</v>
+        <v>0.9955463621588535</v>
       </c>
       <c r="H15" s="8">
         <v>290906</v>
@@ -2174,14 +2174,14 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" si="2"/>
-        <v>47676</v>
+        <v>47677</v>
       </c>
       <c r="K15" s="14">
-        <v>287272</v>
+        <v>287273</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
-        <v>0.98750799227241792</v>
+        <v>0.98751142980894169</v>
       </c>
       <c r="M15" s="8">
         <v>490131</v>
@@ -2191,14 +2191,14 @@
       </c>
       <c r="O15" s="4">
         <f t="shared" si="4"/>
-        <v>81158</v>
+        <v>81161</v>
       </c>
       <c r="P15" s="14">
-        <v>485412</v>
+        <v>485415</v>
       </c>
       <c r="Q15" s="5">
         <f t="shared" si="5"/>
-        <v>0.9903719617816461</v>
+        <v>0.9903780825942452</v>
       </c>
       <c r="R15" s="8">
         <v>287010</v>
@@ -2208,14 +2208,14 @@
       </c>
       <c r="T15" s="4">
         <f t="shared" si="6"/>
-        <v>51980</v>
+        <v>51981</v>
       </c>
       <c r="U15" s="14">
-        <v>284137</v>
+        <v>284138</v>
       </c>
       <c r="V15" s="5">
         <f t="shared" si="7"/>
-        <v>0.98998989582244523</v>
+        <v>0.98999338002160209</v>
       </c>
       <c r="W15" s="8">
         <v>292338</v>
@@ -2225,14 +2225,14 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="8"/>
-        <v>49401</v>
+        <v>49402</v>
       </c>
       <c r="Z15" s="14">
-        <v>287671</v>
+        <v>287672</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="9"/>
-        <v>0.98403560262435952</v>
+        <v>0.98403902332231874</v>
       </c>
       <c r="AB15" s="8">
         <v>495688</v>
@@ -2242,14 +2242,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>86719</v>
+        <v>86723</v>
       </c>
       <c r="AE15" s="14">
-        <v>491011</v>
+        <v>491015</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.99056462936363199</v>
+        <v>0.99057269895579481</v>
       </c>
       <c r="AG15" s="8">
         <v>292071</v>
@@ -2259,14 +2259,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>54940</v>
+        <v>54942</v>
       </c>
       <c r="AJ15" s="14">
-        <v>289858</v>
+        <v>289860</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.99242307521116446</v>
+        <v>0.99242992286122211</v>
       </c>
       <c r="AL15" s="8">
         <v>298411</v>
@@ -2276,14 +2276,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>47362</v>
+        <v>47365</v>
       </c>
       <c r="AO15" s="14">
-        <v>293456</v>
+        <v>293459</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>0.98339538421841022</v>
+        <v>0.9834054374671175</v>
       </c>
       <c r="AQ15" s="8">
         <v>502913</v>
@@ -2293,14 +2293,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>75296</v>
+        <v>75301</v>
       </c>
       <c r="AT15" s="14">
-        <v>498855</v>
+        <v>498860</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.99193100993611216</v>
+        <v>0.99194095201356891</v>
       </c>
       <c r="AV15" s="8">
         <v>298012</v>
@@ -2310,14 +2310,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>47949</v>
+        <v>47952</v>
       </c>
       <c r="AY15" s="14">
-        <v>295216</v>
+        <v>295219</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>0.9906178274700348</v>
+        <v>0.99062789417875785</v>
       </c>
       <c r="BA15" s="8">
         <v>303376</v>
@@ -2327,14 +2327,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>45513</v>
+        <v>45519</v>
       </c>
       <c r="BD15" s="14">
-        <v>299091</v>
+        <v>299097</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.98587561310057481</v>
+        <v>0.98589539053847375</v>
       </c>
       <c r="BF15" s="8">
         <v>511329</v>
@@ -2344,14 +2344,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>92296</v>
+        <v>92303</v>
       </c>
       <c r="BI15" s="14">
-        <v>506562</v>
+        <v>506569</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.99067723520473117</v>
+        <v>0.99069092502087697</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2369,14 +2369,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>73108</v>
+        <v>73115</v>
       </c>
       <c r="F16" s="14">
-        <v>427875</v>
+        <v>427882</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.99359086000905639</v>
+        <v>0.99360711507425081</v>
       </c>
       <c r="H16" s="8">
         <v>441093</v>
@@ -2386,14 +2386,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>74308</v>
+        <v>74315</v>
       </c>
       <c r="K16" s="14">
-        <v>432693</v>
+        <v>432700</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.98095639695030301</v>
+        <v>0.98097226661951109</v>
       </c>
       <c r="M16" s="8">
         <v>754668</v>
@@ -2403,14 +2403,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>125384</v>
+        <v>125402</v>
       </c>
       <c r="P16" s="14">
-        <v>749354</v>
+        <v>749372</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.9929584930061961</v>
+        <v>0.99298234455416157</v>
       </c>
       <c r="R16" s="8">
         <v>429537</v>
@@ -2420,14 +2420,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>78671</v>
+        <v>78681</v>
       </c>
       <c r="U16" s="14">
-        <v>424921</v>
+        <v>424931</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.98925354509623153</v>
+        <v>0.98927682597773881</v>
       </c>
       <c r="W16" s="8">
         <v>433887</v>
@@ -2437,14 +2437,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>76011</v>
+        <v>76023</v>
       </c>
       <c r="Z16" s="14">
-        <v>427137</v>
+        <v>427149</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.98444295404102911</v>
+        <v>0.98447061101162281</v>
       </c>
       <c r="AB16" s="8">
         <v>753330</v>
@@ -2454,14 +2454,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>135891</v>
+        <v>135918</v>
       </c>
       <c r="AE16" s="14">
-        <v>750096</v>
+        <v>750123</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.9957070606507108</v>
+        <v>0.9957429015172633</v>
       </c>
       <c r="AG16" s="8">
         <v>431686</v>
@@ -2471,14 +2471,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>82772</v>
+        <v>82789</v>
       </c>
       <c r="AJ16" s="14">
-        <v>426950</v>
+        <v>426967</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.98902906279101011</v>
+        <v>0.98906844326663357</v>
       </c>
       <c r="AL16" s="8">
         <v>438911</v>
@@ -2488,14 +2488,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>74016</v>
+        <v>74035</v>
       </c>
       <c r="AO16" s="14">
-        <v>430597</v>
+        <v>430616</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.98105766317089338</v>
+        <v>0.98110095212924719</v>
       </c>
       <c r="AQ16" s="8">
         <v>759875</v>
@@ -2505,14 +2505,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>119995</v>
+        <v>120029</v>
       </c>
       <c r="AT16" s="14">
-        <v>756890</v>
+        <v>756924</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.99607172232275043</v>
+        <v>0.99611646652409935</v>
       </c>
       <c r="AV16" s="8">
         <v>437477</v>
@@ -2522,14 +2522,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>69872</v>
+        <v>69897</v>
       </c>
       <c r="AY16" s="14">
-        <v>432349</v>
+        <v>432374</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.98827824091323657</v>
+        <v>0.98833538677461896</v>
       </c>
       <c r="BA16" s="8">
         <v>445887</v>
@@ -2539,14 +2539,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>70511</v>
+        <v>70535</v>
       </c>
       <c r="BD16" s="14">
-        <v>437176</v>
+        <v>437200</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98046366007531061</v>
+        <v>0.98051748537185435</v>
       </c>
       <c r="BF16" s="8">
         <v>770088</v>
@@ -2556,14 +2556,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>139390</v>
+        <v>139436</v>
       </c>
       <c r="BI16" s="14">
-        <v>762945</v>
+        <v>762991</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.99072443668775512</v>
+        <v>0.99078417012081732</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2581,14 +2581,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>52702</v>
+        <v>52710</v>
       </c>
       <c r="F17" s="14">
-        <v>303720</v>
+        <v>303728</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>1.0037875032223522</v>
+        <v>1.0038139430354227</v>
       </c>
       <c r="H17" s="8">
         <v>314962</v>
@@ -2598,14 +2598,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>52687</v>
+        <v>52694</v>
       </c>
       <c r="K17" s="14">
-        <v>311314</v>
+        <v>311321</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98841765038322082</v>
+        <v>0.98843987528654254</v>
       </c>
       <c r="M17" s="8">
         <v>695415</v>
@@ -2615,14 +2615,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>119307</v>
+        <v>119323</v>
       </c>
       <c r="P17" s="14">
-        <v>689968</v>
+        <v>689984</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.99216726702760227</v>
+        <v>0.99219027487183908</v>
       </c>
       <c r="R17" s="8">
         <v>305324</v>
@@ -2632,14 +2632,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>55821</v>
+        <v>55830</v>
       </c>
       <c r="U17" s="14">
-        <v>304489</v>
+        <v>304498</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>0.99726520024629572</v>
+        <v>0.99729467712986863</v>
       </c>
       <c r="W17" s="8">
         <v>316716</v>
@@ -2649,14 +2649,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>55809</v>
+        <v>55820</v>
       </c>
       <c r="Z17" s="14">
-        <v>310521</v>
+        <v>310532</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.98043988936460424</v>
+        <v>0.98047462079591807</v>
       </c>
       <c r="AB17" s="8">
         <v>703511</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>130800</v>
+        <v>130826</v>
       </c>
       <c r="AE17" s="14">
-        <v>698084</v>
+        <v>698110</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.99228583490521116</v>
+        <v>0.99232279239414878</v>
       </c>
       <c r="AG17" s="8">
         <v>311084</v>
@@ -2683,14 +2683,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>63034</v>
+        <v>63047</v>
       </c>
       <c r="AJ17" s="14">
-        <v>310713</v>
+        <v>310726</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.99880739607308633</v>
+        <v>0.99884918542901591</v>
       </c>
       <c r="AL17" s="8">
         <v>323550</v>
@@ -2700,14 +2700,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>52100</v>
+        <v>52114</v>
       </c>
       <c r="AO17" s="14">
-        <v>317171</v>
+        <v>317185</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.98028434554164734</v>
+        <v>0.98032761551537628</v>
       </c>
       <c r="AQ17" s="8">
         <v>714257</v>
@@ -2717,14 +2717,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>112870</v>
+        <v>112895</v>
       </c>
       <c r="AT17" s="14">
-        <v>712818</v>
+        <v>712843</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.99798531900982423</v>
+        <v>0.99802032041688071</v>
       </c>
       <c r="AV17" s="8">
         <v>316308</v>
@@ -2734,14 +2734,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>51105</v>
+        <v>51116</v>
       </c>
       <c r="AY17" s="14">
-        <v>316437</v>
+        <v>316448</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>1.0004078303425774</v>
+        <v>1.0004426065733398</v>
       </c>
       <c r="BA17" s="8">
         <v>328067</v>
@@ -2751,14 +2751,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>47157</v>
+        <v>47175</v>
       </c>
       <c r="BD17" s="14">
-        <v>322711</v>
+        <v>322729</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.98367406657786371</v>
+        <v>0.98372893341908818</v>
       </c>
       <c r="BF17" s="8">
         <v>726752</v>
@@ -2768,14 +2768,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>143860</v>
+        <v>143889</v>
       </c>
       <c r="BI17" s="14">
-        <v>723912</v>
+        <v>723941</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.99609220201664395</v>
+        <v>0.99613210558760068</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2793,14 +2793,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>166635</v>
+        <v>166644</v>
       </c>
       <c r="F18" s="14">
-        <v>919266</v>
+        <v>919275</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99786156858828789</v>
+        <v>0.99787133807189476</v>
       </c>
       <c r="H18" s="8">
         <v>943261</v>
@@ -2810,14 +2810,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>163842</v>
+        <v>163851</v>
       </c>
       <c r="K18" s="14">
-        <v>933270</v>
+        <v>933279</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.98940802174583709</v>
+        <v>0.98941756311349671</v>
       </c>
       <c r="M18" s="8">
         <v>1440086</v>
@@ -2827,14 +2827,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>251750</v>
+        <v>251765</v>
       </c>
       <c r="P18" s="14">
-        <v>1426808</v>
+        <v>1426823</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.99077971732243764</v>
+        <v>0.99079013336703503</v>
       </c>
       <c r="R18" s="8">
         <v>938677</v>
@@ -2844,14 +2844,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>170672</v>
+        <v>170686</v>
       </c>
       <c r="U18" s="14">
-        <v>929340</v>
+        <v>929354</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.99005302143335783</v>
+        <v>0.99006793604189725</v>
       </c>
       <c r="W18" s="8">
         <v>958009</v>
@@ -2861,14 +2861,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>169075</v>
+        <v>169090</v>
       </c>
       <c r="Z18" s="14">
-        <v>943646</v>
+        <v>943661</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.98500744773796489</v>
+        <v>0.98502310521091141</v>
       </c>
       <c r="AB18" s="8">
         <v>1463397</v>
@@ -2878,14 +2878,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>274193</v>
+        <v>274221</v>
       </c>
       <c r="AE18" s="14">
-        <v>1451185</v>
+        <v>1451213</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.99165503277647826</v>
+        <v>0.99167416634037109</v>
       </c>
       <c r="AG18" s="8">
         <v>959088</v>
@@ -2895,14 +2895,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>195115</v>
+        <v>195140</v>
       </c>
       <c r="AJ18" s="14">
-        <v>951968</v>
+        <v>951993</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.99257628080009341</v>
+        <v>0.9926023472298684</v>
       </c>
       <c r="AL18" s="8">
         <v>980581</v>
@@ -2912,14 +2912,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>166809</v>
+        <v>166835</v>
       </c>
       <c r="AO18" s="14">
-        <v>964351</v>
+        <v>964377</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.98344858813295388</v>
+        <v>0.98347510302565522</v>
       </c>
       <c r="AQ18" s="8">
         <v>1490329</v>
@@ -2929,14 +2929,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>246097</v>
+        <v>246133</v>
       </c>
       <c r="AT18" s="14">
-        <v>1482573</v>
+        <v>1482609</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.99479577999220303</v>
+        <v>0.99481993573231142</v>
       </c>
       <c r="AV18" s="8">
         <v>983291</v>
@@ -2946,14 +2946,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>170134</v>
+        <v>170161</v>
       </c>
       <c r="AY18" s="14">
-        <v>975890</v>
+        <v>975917</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.99247323528843445</v>
+        <v>0.99250069409767805</v>
       </c>
       <c r="BA18" s="8">
         <v>1002255</v>
@@ -2963,14 +2963,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>160648</v>
+        <v>160679</v>
       </c>
       <c r="BD18" s="14">
-        <v>988249</v>
+        <v>988280</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.98602551246938153</v>
+        <v>0.9860564427216626</v>
       </c>
       <c r="BF18" s="8">
         <v>1522890</v>
@@ -2980,14 +2980,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>329290</v>
+        <v>329348</v>
       </c>
       <c r="BI18" s="14">
-        <v>1509031</v>
+        <v>1509089</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.99089953969098232</v>
+        <v>0.9909376251731904</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3039,14 +3039,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>93783</v>
+        <v>93787</v>
       </c>
       <c r="P19" s="14">
-        <v>468688</v>
+        <v>468692</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.97828392041612044</v>
+        <v>0.97829226954321924</v>
       </c>
       <c r="R19" s="8">
         <v>279649</v>
@@ -3056,14 +3056,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>57749</v>
+        <v>57751</v>
       </c>
       <c r="U19" s="14">
-        <v>272793</v>
+        <v>272795</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.97548355259629038</v>
+        <v>0.97549070441875352</v>
       </c>
       <c r="W19" s="8">
         <v>287758</v>
@@ -3073,14 +3073,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>59222</v>
+        <v>59227</v>
       </c>
       <c r="Z19" s="14">
-        <v>276642</v>
+        <v>276647</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.96137031811452678</v>
+        <v>0.96138769382606215</v>
       </c>
       <c r="AB19" s="8">
         <v>485015</v>
@@ -3090,14 +3090,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>101779</v>
+        <v>101792</v>
       </c>
       <c r="AE19" s="14">
-        <v>474965</v>
+        <v>474978</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.97927899137140084</v>
+        <v>0.97930579466614431</v>
       </c>
       <c r="AG19" s="8">
         <v>283525</v>
@@ -3107,14 +3107,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>74607</v>
+        <v>74615</v>
       </c>
       <c r="AJ19" s="14">
-        <v>276710</v>
+        <v>276718</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.97596331893131116</v>
+        <v>0.97599153513799486</v>
       </c>
       <c r="AL19" s="8">
         <v>295027</v>
@@ -3124,14 +3124,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>58079</v>
+        <v>58086</v>
       </c>
       <c r="AO19" s="14">
-        <v>282157</v>
+        <v>282164</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.95637687398102544</v>
+        <v>0.95640060062299381</v>
       </c>
       <c r="AQ19" s="8">
         <v>494059</v>
@@ -3141,14 +3141,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>91580</v>
+        <v>91602</v>
       </c>
       <c r="AT19" s="14">
-        <v>486368</v>
+        <v>486390</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.98443303330169074</v>
+        <v>0.98447756239639395</v>
       </c>
       <c r="AV19" s="8">
         <v>287237</v>
@@ -3158,14 +3158,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>56638</v>
+        <v>56651</v>
       </c>
       <c r="AY19" s="14">
-        <v>283388</v>
+        <v>283401</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.98659991574901562</v>
+        <v>0.98664517454227696</v>
       </c>
       <c r="BA19" s="8">
         <v>298081</v>
@@ -3175,14 +3175,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>54995</v>
+        <v>55006</v>
       </c>
       <c r="BD19" s="14">
-        <v>287506</v>
+        <v>287517</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.96452306587806669</v>
+        <v>0.96455996859913917</v>
       </c>
       <c r="BF19" s="8">
         <v>503654</v>
@@ -3192,14 +3192,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>132311</v>
+        <v>132341</v>
       </c>
       <c r="BI19" s="14">
-        <v>492707</v>
+        <v>492737</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.97826484054529494</v>
+        <v>0.97832440524645892</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3353,14 +3353,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="AT20" s="14">
-        <v>9730</v>
+        <v>9731</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>1.0101744186046511</v>
+        <v>1.0102782392026579</v>
       </c>
       <c r="AV20" s="8">
         <v>6297</v>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>3246</v>
+        <v>3247</v>
       </c>
       <c r="BI20" s="14">
-        <v>9881</v>
+        <v>9882</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>1.0028417740789608</v>
+        <v>1.0029432660103521</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3429,14 +3429,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>3695</v>
+        <v>3697</v>
       </c>
       <c r="F21" s="14">
-        <v>9829</v>
+        <v>9831</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>1.026956430884965</v>
+        <v>1.0271653954654687</v>
       </c>
       <c r="H21" s="8">
         <v>10057</v>
@@ -3446,14 +3446,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3493</v>
+        <v>3495</v>
       </c>
       <c r="K21" s="14">
-        <v>9972</v>
+        <v>9974</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.99154817540021878</v>
+        <v>0.99174704186139007</v>
       </c>
       <c r="M21" s="8">
         <v>12982</v>
@@ -3463,14 +3463,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>4298</v>
+        <v>4300</v>
       </c>
       <c r="P21" s="14">
-        <v>13239</v>
+        <v>13241</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>1.0197966415036204</v>
+        <v>1.0199507009705746</v>
       </c>
       <c r="R21" s="8">
         <v>9811</v>
@@ -3480,14 +3480,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3473</v>
+        <v>3475</v>
       </c>
       <c r="U21" s="14">
-        <v>10034</v>
+        <v>10036</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>1.0227295892365711</v>
+        <v>1.0229334420548364</v>
       </c>
       <c r="W21" s="8">
         <v>10152</v>
@@ -3497,14 +3497,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3292</v>
+        <v>3294</v>
       </c>
       <c r="Z21" s="14">
-        <v>10178</v>
+        <v>10180</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>1.002561071710008</v>
+        <v>1.0027580772261624</v>
       </c>
       <c r="AB21" s="8">
         <v>13231</v>
@@ -3514,14 +3514,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="AE21" s="14">
-        <v>13565</v>
+        <v>13568</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>1.0252437457486208</v>
+        <v>1.0254704859798958</v>
       </c>
       <c r="AG21" s="8">
         <v>10040</v>
@@ -3531,14 +3531,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3821</v>
+        <v>3823</v>
       </c>
       <c r="AJ21" s="14">
-        <v>10249</v>
+        <v>10251</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>1.0208167330677291</v>
+        <v>1.02101593625498</v>
       </c>
       <c r="AL21" s="8">
         <v>10211</v>
@@ -3548,14 +3548,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3453</v>
+        <v>3455</v>
       </c>
       <c r="AO21" s="14">
-        <v>10400</v>
+        <v>10402</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>1.0185094505924983</v>
+        <v>1.0187053177945353</v>
       </c>
       <c r="AQ21" s="8">
         <v>13473</v>
@@ -3565,14 +3565,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4289</v>
+        <v>4292</v>
       </c>
       <c r="AT21" s="14">
-        <v>13892</v>
+        <v>13895</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>1.031099235508053</v>
+        <v>1.03132190306539</v>
       </c>
       <c r="AV21" s="8">
         <v>10213</v>
@@ -3582,14 +3582,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3528</v>
+        <v>3531</v>
       </c>
       <c r="AY21" s="14">
-        <v>10511</v>
+        <v>10514</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>1.0291784979927543</v>
+        <v>1.0294722412611377</v>
       </c>
       <c r="BA21" s="8">
         <v>10449</v>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3338</v>
+        <v>3341</v>
       </c>
       <c r="BD21" s="14">
-        <v>10636</v>
+        <v>10639</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>1.0178964494209972</v>
+        <v>1.0181835582352379</v>
       </c>
       <c r="BF21" s="8">
         <v>13925</v>
@@ -3616,14 +3616,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>6496</v>
+        <v>6501</v>
       </c>
       <c r="BI21" s="14">
-        <v>14323</v>
+        <v>14328</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>1.0285816876122083</v>
+        <v>1.0289407540394973</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3641,14 +3641,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="F22" s="14">
-        <v>6227</v>
+        <v>6228</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>1.0110407533690535</v>
+        <v>1.0112031173891864</v>
       </c>
       <c r="H22" s="8">
         <v>6265</v>
@@ -3658,14 +3658,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="K22" s="14">
-        <v>6309</v>
+        <v>6310</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>1.007023144453312</v>
+        <v>1.0071827613727056</v>
       </c>
       <c r="M22" s="8">
         <v>7537</v>
@@ -3675,14 +3675,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="P22" s="14">
-        <v>7597</v>
+        <v>7600</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>1.0079607270797399</v>
+        <v>1.008358763433727</v>
       </c>
       <c r="R22" s="8">
         <v>6306</v>
@@ -3692,14 +3692,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="U22" s="14">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>1.009197589597209</v>
+        <v>1.0093561687281953</v>
       </c>
       <c r="W22" s="8">
         <v>6435</v>
@@ -3709,14 +3709,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="Z22" s="14">
-        <v>6437</v>
+        <v>6438</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>1.0003108003108003</v>
+        <v>1.0004662004662004</v>
       </c>
       <c r="AB22" s="8">
         <v>7668</v>
@@ -3726,14 +3726,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="AE22" s="14">
-        <v>7712</v>
+        <v>7715</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>1.0057381324986958</v>
+        <v>1.0061293688054251</v>
       </c>
       <c r="AG22" s="8">
         <v>6422</v>
@@ -3743,14 +3743,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="AJ22" s="14">
-        <v>6455</v>
+        <v>6457</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>1.005138586110246</v>
+        <v>1.005450015571473</v>
       </c>
       <c r="AL22" s="8">
         <v>6508</v>
@@ -3760,14 +3760,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="AO22" s="14">
-        <v>6502</v>
+        <v>6504</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.9990780577750461</v>
+        <v>0.99938537185003073</v>
       </c>
       <c r="AQ22" s="8">
         <v>7781</v>
@@ -3777,14 +3777,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2097</v>
+        <v>2101</v>
       </c>
       <c r="AT22" s="14">
-        <v>7809</v>
+        <v>7813</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>1.0035985091890502</v>
+        <v>1.0041125819303431</v>
       </c>
       <c r="AV22" s="8">
         <v>6603</v>
@@ -3794,14 +3794,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="AY22" s="14">
-        <v>6518</v>
+        <v>6520</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.98712706345600487</v>
+        <v>0.98742995608056949</v>
       </c>
       <c r="BA22" s="8">
         <v>6608</v>
@@ -3811,14 +3811,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="BD22" s="14">
-        <v>6559</v>
+        <v>6561</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>0.99258474576271183</v>
+        <v>0.99288740920096852</v>
       </c>
       <c r="BF22" s="8">
         <v>7906</v>
@@ -3828,14 +3828,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2452</v>
+        <v>2457</v>
       </c>
       <c r="BI22" s="14">
-        <v>7950</v>
+        <v>7955</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>1.0055653933721225</v>
+        <v>1.0061978244371363</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3853,14 +3853,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>5984</v>
+        <v>5986</v>
       </c>
       <c r="F23" s="14">
-        <v>8471</v>
+        <v>8473</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.96261363636363639</v>
+        <v>0.96284090909090914</v>
       </c>
       <c r="H23" s="8">
         <v>8763</v>
@@ -3870,14 +3870,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>5148</v>
+        <v>5150</v>
       </c>
       <c r="K23" s="14">
-        <v>8500</v>
+        <v>8502</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.96998744722127128</v>
+        <v>0.97021567956179389</v>
       </c>
       <c r="M23" s="8">
         <v>10654</v>
@@ -3887,14 +3887,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>5545</v>
+        <v>5547</v>
       </c>
       <c r="P23" s="14">
-        <v>10477</v>
+        <v>10479</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.98338652149427441</v>
+        <v>0.9835742444152431</v>
       </c>
       <c r="R23" s="8">
         <v>8621</v>
@@ -3904,14 +3904,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>3750</v>
+        <v>3752</v>
       </c>
       <c r="U23" s="14">
-        <v>8394</v>
+        <v>8396</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.97366894791787495</v>
+        <v>0.97390093956617563</v>
       </c>
       <c r="W23" s="8">
         <v>8774</v>
@@ -3921,14 +3921,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>3699</v>
+        <v>3701</v>
       </c>
       <c r="Z23" s="14">
-        <v>8430</v>
+        <v>8432</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.96079325279234096</v>
+        <v>0.96102119899703675</v>
       </c>
       <c r="AB23" s="8">
         <v>10734</v>
@@ -3938,14 +3938,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3664</v>
+        <v>3666</v>
       </c>
       <c r="AE23" s="14">
-        <v>10552</v>
+        <v>10554</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.98304453139556547</v>
+        <v>0.98323085522638343</v>
       </c>
       <c r="AG23" s="8">
         <v>8589</v>
@@ -3955,14 +3955,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>3099</v>
+        <v>3101</v>
       </c>
       <c r="AJ23" s="14">
-        <v>8441</v>
+        <v>8443</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.98276865758528353</v>
+        <v>0.98300151356386078</v>
       </c>
       <c r="AL23" s="8">
         <v>8660</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2900</v>
+        <v>2904</v>
       </c>
       <c r="AO23" s="14">
-        <v>8502</v>
+        <v>8506</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.98175519630484986</v>
+        <v>0.98221709006928404</v>
       </c>
       <c r="AQ23" s="8">
         <v>10698</v>
@@ -3989,14 +3989,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3515</v>
+        <v>3519</v>
       </c>
       <c r="AT23" s="14">
-        <v>10734</v>
+        <v>10738</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>1.0033651149747616</v>
+        <v>1.003739016638624</v>
       </c>
       <c r="AV23" s="8">
         <v>8445</v>
@@ -4006,14 +4006,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="AY23" s="14">
-        <v>8495</v>
+        <v>8498</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>1.0059206631142688</v>
+        <v>1.006275902901125</v>
       </c>
       <c r="BA23" s="8">
         <v>8623</v>
@@ -4023,14 +4023,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2719</v>
+        <v>2722</v>
       </c>
       <c r="BD23" s="14">
-        <v>8542</v>
+        <v>8545</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.99060651745332251</v>
+        <v>0.99095442421431057</v>
       </c>
       <c r="BF23" s="8">
         <v>11023</v>
@@ -4040,14 +4040,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4232</v>
+        <v>4237</v>
       </c>
       <c r="BI23" s="14">
-        <v>10903</v>
+        <v>10908</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.9891136714143155</v>
+        <v>0.98956726843871901</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4133,14 +4133,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="Z24" s="14">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.98025316455696199</v>
+        <v>0.98042194092827006</v>
       </c>
       <c r="AB24" s="8">
         <v>6940</v>
@@ -4150,14 +4150,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="AE24" s="14">
-        <v>6802</v>
+        <v>6804</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.98011527377521612</v>
+        <v>0.98040345821325647</v>
       </c>
       <c r="AG24" s="8">
         <v>6076</v>
@@ -4167,14 +4167,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="AJ24" s="14">
-        <v>5951</v>
+        <v>5952</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.97942725477287684</v>
+        <v>0.97959183673469385</v>
       </c>
       <c r="AL24" s="8">
         <v>6181</v>
@@ -4184,14 +4184,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="AO24" s="14">
-        <v>6010</v>
+        <v>6012</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.97233457369357712</v>
+        <v>0.97265814593107913</v>
       </c>
       <c r="AQ24" s="8">
         <v>6974</v>
@@ -4201,14 +4201,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="AT24" s="14">
-        <v>6898</v>
+        <v>6901</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.98910238026957265</v>
+        <v>0.98953254946945801</v>
       </c>
       <c r="AV24" s="8">
         <v>6124</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="AX24" s="4">
         <f t="shared" si="18"/>
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="AY24" s="14">
-        <v>6043</v>
+        <v>6045</v>
       </c>
       <c r="AZ24" s="5">
         <f t="shared" si="19"/>
-        <v>0.98677335075114303</v>
+        <v>0.98709993468321355</v>
       </c>
       <c r="BA24" s="8">
         <v>6202</v>
@@ -4235,14 +4235,14 @@
       </c>
       <c r="BC24" s="4">
         <f t="shared" si="20"/>
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="BD24" s="14">
-        <v>6134</v>
+        <v>6136</v>
       </c>
       <c r="BE24" s="5">
         <f t="shared" si="21"/>
-        <v>0.98903579490486937</v>
+        <v>0.98935827152531441</v>
       </c>
       <c r="BF24" s="8">
         <v>7084</v>
@@ -4252,14 +4252,14 @@
       </c>
       <c r="BH24" s="4">
         <f t="shared" si="22"/>
-        <v>1751</v>
+        <v>1754</v>
       </c>
       <c r="BI24" s="14">
-        <v>7027</v>
+        <v>7030</v>
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="23"/>
-        <v>0.99195369847543757</v>
+        <v>0.99237718802936192</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4277,14 +4277,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="F25" s="14">
-        <v>18488</v>
+        <v>18489</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>1.0111572959964996</v>
+        <v>1.0112119886239335</v>
       </c>
       <c r="H25" s="8">
         <v>18682</v>
@@ -4294,14 +4294,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>3639</v>
+        <v>3640</v>
       </c>
       <c r="K25" s="14">
-        <v>18849</v>
+        <v>18850</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>1.0089390857509903</v>
+        <v>1.0089926132105771</v>
       </c>
       <c r="M25" s="8">
         <v>25970</v>
@@ -4311,14 +4311,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>4732</v>
+        <v>4733</v>
       </c>
       <c r="P25" s="14">
-        <v>26233</v>
+        <v>26234</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>1.0101270696958029</v>
+        <v>1.010165575664228</v>
       </c>
       <c r="R25" s="8">
         <v>18895</v>
@@ -4328,14 +4328,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>3737</v>
+        <v>3739</v>
       </c>
       <c r="U25" s="14">
-        <v>19060</v>
+        <v>19062</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>1.0087324689071182</v>
+        <v>1.0088383170150834</v>
       </c>
       <c r="W25" s="8">
         <v>19436</v>
@@ -4345,14 +4345,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>3767</v>
+        <v>3769</v>
       </c>
       <c r="Z25" s="14">
-        <v>19320</v>
+        <v>19322</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.99403169376414902</v>
+        <v>0.99413459559580164</v>
       </c>
       <c r="AB25" s="8">
         <v>26661</v>
@@ -4362,14 +4362,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>5247</v>
+        <v>5250</v>
       </c>
       <c r="AE25" s="14">
-        <v>26844</v>
+        <v>26847</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>1.0068639585912007</v>
+        <v>1.0069764825025318</v>
       </c>
       <c r="AG25" s="8">
         <v>19440</v>
@@ -4379,14 +4379,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>4237</v>
+        <v>4240</v>
       </c>
       <c r="AJ25" s="14">
-        <v>19515</v>
+        <v>19518</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>1.003858024691358</v>
+        <v>1.0040123456790124</v>
       </c>
       <c r="AL25" s="8">
         <v>19709</v>
@@ -4396,14 +4396,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>3697</v>
+        <v>3701</v>
       </c>
       <c r="AO25" s="14">
-        <v>19677</v>
+        <v>19681</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.99837637627479836</v>
+        <v>0.99857932924044857</v>
       </c>
       <c r="AQ25" s="8">
         <v>27081</v>
@@ -4413,14 +4413,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>5081</v>
+        <v>5086</v>
       </c>
       <c r="AT25" s="14">
-        <v>27275</v>
+        <v>27280</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>1.0071636941028765</v>
+        <v>1.0073483253941877</v>
       </c>
       <c r="AV25" s="8">
         <v>19795</v>
@@ -4430,14 +4430,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>3983</v>
+        <v>3987</v>
       </c>
       <c r="AY25" s="14">
-        <v>19926</v>
+        <v>19930</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>1.0066178327860571</v>
+        <v>1.0068199040161656</v>
       </c>
       <c r="BA25" s="8">
         <v>20139</v>
@@ -4447,14 +4447,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>3851</v>
+        <v>3855</v>
       </c>
       <c r="BD25" s="14">
-        <v>20125</v>
+        <v>20129</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>0.99930483142161974</v>
+        <v>0.99950345101544269</v>
       </c>
       <c r="BF25" s="8">
         <v>27639</v>
@@ -4464,14 +4464,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>7525</v>
+        <v>7530</v>
       </c>
       <c r="BI25" s="14">
-        <v>27763</v>
+        <v>27768</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>1.0044864141249683</v>
+        <v>1.00466731792033</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3464</v>
+        <v>3466</v>
       </c>
       <c r="F26" s="14">
-        <v>13364</v>
+        <v>13366</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.98736608792020686</v>
+        <v>0.9875138529737717</v>
       </c>
       <c r="H26" s="8">
         <v>13884</v>
@@ -4506,14 +4506,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3309</v>
+        <v>3311</v>
       </c>
       <c r="K26" s="14">
-        <v>13937</v>
+        <v>13939</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>1.0038173437049842</v>
+        <v>1.0039613944108325</v>
       </c>
       <c r="M26" s="8">
         <v>25920</v>
@@ -4523,14 +4523,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5143</v>
+        <v>5145</v>
       </c>
       <c r="P26" s="14">
-        <v>26304</v>
+        <v>26306</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>1.0148148148148148</v>
+        <v>1.0148919753086421</v>
       </c>
       <c r="R26" s="8">
         <v>13869</v>
@@ -4540,14 +4540,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3710</v>
+        <v>3714</v>
       </c>
       <c r="U26" s="14">
-        <v>14171</v>
+        <v>14175</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>1.0217751820607108</v>
+        <v>1.0220635950681376</v>
       </c>
       <c r="W26" s="8">
         <v>14474</v>
@@ -4557,14 +4557,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3391</v>
+        <v>3397</v>
       </c>
       <c r="Z26" s="14">
-        <v>14436</v>
+        <v>14442</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.99737460273594025</v>
+        <v>0.99778913914605505</v>
       </c>
       <c r="AB26" s="8">
         <v>27035</v>
@@ -4574,14 +4574,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5642</v>
+        <v>5647</v>
       </c>
       <c r="AE26" s="14">
-        <v>26980</v>
+        <v>26985</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.99796560014795632</v>
+        <v>0.99815054558905125</v>
       </c>
       <c r="AG26" s="8">
         <v>14053</v>
@@ -4591,14 +4591,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3375</v>
+        <v>3380</v>
       </c>
       <c r="AJ26" s="14">
-        <v>14096</v>
+        <v>14101</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>1.0030598448729808</v>
+        <v>1.0034156407884438</v>
       </c>
       <c r="AL26" s="8">
         <v>14372</v>
@@ -4608,14 +4608,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>3140</v>
+        <v>3147</v>
       </c>
       <c r="AO26" s="14">
-        <v>14224</v>
+        <v>14231</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.98970219871973286</v>
+        <v>0.9901892568883941</v>
       </c>
       <c r="AQ26" s="8">
         <v>27267</v>
@@ -4625,14 +4625,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5388</v>
+        <v>5398</v>
       </c>
       <c r="AT26" s="14">
-        <v>27081</v>
+        <v>27091</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.99317856749917488</v>
+        <v>0.99354531118201495</v>
       </c>
       <c r="AV26" s="8">
         <v>14007</v>
@@ -4642,14 +4642,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3135</v>
+        <v>3142</v>
       </c>
       <c r="AY26" s="14">
-        <v>14019</v>
+        <v>14026</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>1.000856714499893</v>
+        <v>1.0013564646248305</v>
       </c>
       <c r="BA26" s="8">
         <v>14398</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3046</v>
+        <v>3058</v>
       </c>
       <c r="BD26" s="14">
-        <v>14098</v>
+        <v>14110</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.9791637727462148</v>
+        <v>0.97999722183636617</v>
       </c>
       <c r="BF26" s="8">
         <v>27339</v>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6623</v>
+        <v>6638</v>
       </c>
       <c r="BI26" s="14">
-        <v>27099</v>
+        <v>27114</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.99122133216284425</v>
+        <v>0.99176999890266648</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4701,14 +4701,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>34627</v>
+        <v>34632</v>
       </c>
       <c r="F27" s="14">
-        <v>120704</v>
+        <v>120709</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>1.0018425988944406</v>
+        <v>1.0018840988695408</v>
       </c>
       <c r="H27" s="8">
         <v>123649</v>
@@ -4718,14 +4718,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>32451</v>
+        <v>32456</v>
       </c>
       <c r="K27" s="14">
-        <v>122553</v>
+        <v>122558</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.99113620005014191</v>
+        <v>0.99117663709370885</v>
       </c>
       <c r="M27" s="8">
         <v>182121</v>
@@ -4735,14 +4735,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>47472</v>
+        <v>47481</v>
       </c>
       <c r="P27" s="14">
-        <v>180963</v>
+        <v>180972</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99364158993196827</v>
+        <v>0.99369100762679752</v>
       </c>
       <c r="R27" s="8">
         <v>122848</v>
@@ -4752,14 +4752,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>33827</v>
+        <v>33835</v>
       </c>
       <c r="U27" s="14">
-        <v>122056</v>
+        <v>122064</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.9935530085959885</v>
+        <v>0.99361812972128161</v>
       </c>
       <c r="W27" s="8">
         <v>125846</v>
@@ -4769,14 +4769,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>34894</v>
+        <v>34904</v>
       </c>
       <c r="Z27" s="14">
-        <v>123342</v>
+        <v>123352</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.98010266516218236</v>
+        <v>0.98018212736201393</v>
       </c>
       <c r="AB27" s="8">
         <v>184102</v>
@@ -4786,14 +4786,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>50104</v>
+        <v>50121</v>
       </c>
       <c r="AE27" s="14">
-        <v>182686</v>
+        <v>182703</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.9923086115305646</v>
+        <v>0.99240095164636999</v>
       </c>
       <c r="AG27" s="8">
         <v>124176</v>
@@ -4803,14 +4803,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>34586</v>
+        <v>34597</v>
       </c>
       <c r="AJ27" s="14">
-        <v>123203</v>
+        <v>123214</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.99216434737791526</v>
+        <v>0.99225293132328307</v>
       </c>
       <c r="AL27" s="8">
         <v>126536</v>
@@ -4820,14 +4820,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>31854</v>
+        <v>31867</v>
       </c>
       <c r="AO27" s="14">
-        <v>124048</v>
+        <v>124061</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.98033761143073905</v>
+        <v>0.98044034899159127</v>
       </c>
       <c r="AQ27" s="8">
         <v>184835</v>
@@ -4837,14 +4837,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>47452</v>
+        <v>47474</v>
       </c>
       <c r="AT27" s="14">
-        <v>184291</v>
+        <v>184313</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.99705683447399029</v>
+        <v>0.99717585955040977</v>
       </c>
       <c r="AV27" s="8">
         <v>124975</v>
@@ -4854,14 +4854,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>31808</v>
+        <v>31827</v>
       </c>
       <c r="AY27" s="14">
-        <v>124348</v>
+        <v>124367</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.99498299659931988</v>
+        <v>0.99513502700540113</v>
       </c>
       <c r="BA27" s="8">
         <v>127493</v>
@@ -4871,14 +4871,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>31121</v>
+        <v>31143</v>
       </c>
       <c r="BD27" s="14">
-        <v>125402</v>
+        <v>125424</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.98359909955840708</v>
+        <v>0.98377165805181466</v>
       </c>
       <c r="BF27" s="8">
         <v>187636</v>
@@ -4888,14 +4888,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>63136</v>
+        <v>63175</v>
       </c>
       <c r="BI27" s="14">
-        <v>185689</v>
+        <v>185728</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.98962352640218298</v>
+        <v>0.98983137564220081</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4913,14 +4913,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>64594</v>
+        <v>64596</v>
       </c>
       <c r="F28" s="14">
-        <v>380036</v>
+        <v>380038</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.99431723040857334</v>
+        <v>0.99432246316141992</v>
       </c>
       <c r="H28" s="8">
         <v>389922</v>
@@ -4930,14 +4930,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>63270</v>
+        <v>63272</v>
       </c>
       <c r="K28" s="14">
-        <v>385063</v>
+        <v>385065</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.98753853334769515</v>
+        <v>0.98754366257866955</v>
       </c>
       <c r="M28" s="8">
         <v>650891</v>
@@ -4947,14 +4947,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>104700</v>
+        <v>104706</v>
       </c>
       <c r="P28" s="14">
-        <v>645773</v>
+        <v>645779</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.99213693229741995</v>
+        <v>0.9921461504307173</v>
       </c>
       <c r="R28" s="8">
         <v>389073</v>
@@ -4964,14 +4964,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>67527</v>
+        <v>67532</v>
       </c>
       <c r="U28" s="14">
-        <v>386531</v>
+        <v>386536</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.99346652170672345</v>
+        <v>0.99347937276552212</v>
       </c>
       <c r="W28" s="8">
         <v>397763</v>
@@ -4981,14 +4981,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>67040</v>
+        <v>67046</v>
       </c>
       <c r="Z28" s="14">
-        <v>391725</v>
+        <v>391731</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.98482010644529527</v>
+        <v>0.9848351908045746</v>
       </c>
       <c r="AB28" s="8">
         <v>660941</v>
@@ -4998,14 +4998,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>103887</v>
+        <v>103898</v>
       </c>
       <c r="AE28" s="14">
-        <v>656452</v>
+        <v>656463</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.99320816835390757</v>
+        <v>0.99322481129177942</v>
       </c>
       <c r="AG28" s="8">
         <v>397417</v>
@@ -5015,14 +5015,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>68391</v>
+        <v>68399</v>
       </c>
       <c r="AJ28" s="14">
-        <v>394595</v>
+        <v>394603</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.99289914623682429</v>
+        <v>0.99291927622623088</v>
       </c>
       <c r="AL28" s="8">
         <v>405895</v>
@@ -5032,14 +5032,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>61114</v>
+        <v>61123</v>
       </c>
       <c r="AO28" s="14">
-        <v>398909</v>
+        <v>398918</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.98278865223764766</v>
+        <v>0.98281082545978637</v>
       </c>
       <c r="AQ28" s="8">
         <v>670091</v>
@@ -5049,14 +5049,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>96078</v>
+        <v>96092</v>
       </c>
       <c r="AT28" s="14">
-        <v>666150</v>
+        <v>666164</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.99411870924993773</v>
+        <v>0.99413960193466255</v>
       </c>
       <c r="AV28" s="8">
         <v>405395</v>
@@ -5066,14 +5066,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>60991</v>
+        <v>61000</v>
       </c>
       <c r="AY28" s="14">
-        <v>402791</v>
+        <v>402800</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.99357663513363514</v>
+        <v>0.99359883570344976</v>
       </c>
       <c r="BA28" s="8">
         <v>412255</v>
@@ -5083,14 +5083,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>59410</v>
+        <v>59420</v>
       </c>
       <c r="BD28" s="14">
-        <v>406895</v>
+        <v>406905</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98699833840705387</v>
+        <v>0.98702259523838398</v>
       </c>
       <c r="BF28" s="8">
         <v>680839</v>
@@ -5100,14 +5100,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>127410</v>
+        <v>127439</v>
       </c>
       <c r="BI28" s="14">
-        <v>676319</v>
+        <v>676348</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.99336113236756418</v>
+        <v>0.99340372687228551</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5125,14 +5125,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>24824</v>
+        <v>24828</v>
       </c>
       <c r="F29" s="14">
-        <v>126964</v>
+        <v>126968</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.99535109794052856</v>
+        <v>0.99538245647044066</v>
       </c>
       <c r="H29" s="8">
         <v>129829</v>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>23855</v>
+        <v>23859</v>
       </c>
       <c r="K29" s="14">
-        <v>128366</v>
+        <v>128370</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.98873133121259504</v>
+        <v>0.98876214097004522</v>
       </c>
       <c r="M29" s="8">
         <v>176637</v>
@@ -5159,14 +5159,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>30949</v>
+        <v>30954</v>
       </c>
       <c r="P29" s="14">
-        <v>174214</v>
+        <v>174219</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98628260217281771</v>
+        <v>0.98631090881298933</v>
       </c>
       <c r="R29" s="8">
         <v>129740</v>
@@ -5176,14 +5176,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>24242</v>
+        <v>24247</v>
       </c>
       <c r="U29" s="14">
-        <v>128537</v>
+        <v>128542</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.99072760906428237</v>
+        <v>0.99076614767997528</v>
       </c>
       <c r="W29" s="8">
         <v>131766</v>
@@ -5193,14 +5193,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>23812</v>
+        <v>23817</v>
       </c>
       <c r="Z29" s="14">
-        <v>129574</v>
+        <v>129579</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.98336444909916065</v>
+        <v>0.98340239515504757</v>
       </c>
       <c r="AB29" s="8">
         <v>178083</v>
@@ -5210,14 +5210,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>32802</v>
+        <v>32807</v>
       </c>
       <c r="AE29" s="14">
-        <v>176356</v>
+        <v>176361</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.99030227478198363</v>
+        <v>0.99033035157763516</v>
       </c>
       <c r="AG29" s="8">
         <v>131984</v>
@@ -5227,14 +5227,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>28864</v>
+        <v>28870</v>
       </c>
       <c r="AJ29" s="14">
-        <v>130683</v>
+        <v>130689</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.99014274457509999</v>
+        <v>0.99018820463086432</v>
       </c>
       <c r="AL29" s="8">
         <v>133676</v>
@@ -5244,14 +5244,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>23040</v>
+        <v>23045</v>
       </c>
       <c r="AO29" s="14">
-        <v>131832</v>
+        <v>131837</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.98620545198838983</v>
+        <v>0.98624285586043869</v>
       </c>
       <c r="AQ29" s="8">
         <v>179800</v>
@@ -5261,14 +5261,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>29843</v>
+        <v>29851</v>
       </c>
       <c r="AT29" s="14">
-        <v>178973</v>
+        <v>178981</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.99540044493882096</v>
+        <v>0.99544493882091212</v>
       </c>
       <c r="AV29" s="8">
         <v>134089</v>
@@ -5278,14 +5278,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>22667</v>
+        <v>22672</v>
       </c>
       <c r="AY29" s="14">
-        <v>133159</v>
+        <v>133164</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.99306430803421608</v>
+        <v>0.99310159670069875</v>
       </c>
       <c r="BA29" s="8">
         <v>136058</v>
@@ -5295,14 +5295,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>23009</v>
+        <v>23015</v>
       </c>
       <c r="BD29" s="14">
-        <v>134472</v>
+        <v>134478</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.98834320657366714</v>
+        <v>0.98838730541386766</v>
       </c>
       <c r="BF29" s="8">
         <v>182623</v>
@@ -5312,14 +5312,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>41939</v>
+        <v>41948</v>
       </c>
       <c r="BI29" s="14">
-        <v>181416</v>
+        <v>181425</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.99339075581936553</v>
+        <v>0.99344003767323941</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>39283</v>
+        <v>39284</v>
       </c>
       <c r="F30" s="14">
-        <v>166410</v>
+        <v>166411</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.99709995566047915</v>
+        <v>0.99710594748762693</v>
       </c>
       <c r="H30" s="8">
         <v>172134</v>
@@ -5354,14 +5354,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>41656</v>
+        <v>41657</v>
       </c>
       <c r="K30" s="14">
-        <v>169537</v>
+        <v>169538</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.98491291668119019</v>
+        <v>0.98491872610872921</v>
       </c>
       <c r="M30" s="8">
         <v>289249</v>
@@ -5371,14 +5371,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>59680</v>
+        <v>59684</v>
       </c>
       <c r="P30" s="14">
-        <v>286053</v>
+        <v>286057</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.98895069645876044</v>
+        <v>0.98896452537433144</v>
       </c>
       <c r="R30" s="8">
         <v>169142</v>
@@ -5388,14 +5388,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>37562</v>
+        <v>37564</v>
       </c>
       <c r="U30" s="14">
-        <v>167859</v>
+        <v>167861</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.99241465750671032</v>
+        <v>0.9924264818909555</v>
       </c>
       <c r="W30" s="8">
         <v>174259</v>
@@ -5405,14 +5405,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>41375</v>
+        <v>41378</v>
       </c>
       <c r="Z30" s="14">
-        <v>170999</v>
+        <v>171002</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.98129221446238069</v>
+        <v>0.98130943021594297</v>
       </c>
       <c r="AB30" s="8">
         <v>293307</v>
@@ -5422,14 +5422,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>62868</v>
+        <v>62877</v>
       </c>
       <c r="AE30" s="14">
-        <v>290506</v>
+        <v>290515</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.99045027905914285</v>
+        <v>0.99048096363196236</v>
       </c>
       <c r="AG30" s="8">
         <v>172053</v>
@@ -5439,14 +5439,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>37797</v>
+        <v>37802</v>
       </c>
       <c r="AJ30" s="14">
-        <v>170982</v>
+        <v>170987</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.99377517392896375</v>
+        <v>0.99380423474162027</v>
       </c>
       <c r="AL30" s="8">
         <v>176835</v>
@@ -5456,14 +5456,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>36119</v>
+        <v>36124</v>
       </c>
       <c r="AO30" s="14">
-        <v>173663</v>
+        <v>173668</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.98206237452992906</v>
+        <v>0.98209064947549973</v>
       </c>
       <c r="AQ30" s="8">
         <v>297651</v>
@@ -5473,14 +5473,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>57664</v>
+        <v>57676</v>
       </c>
       <c r="AT30" s="14">
-        <v>296255</v>
+        <v>296267</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.99530994352446323</v>
+        <v>0.9953502591961727</v>
       </c>
       <c r="AV30" s="8">
         <v>175428</v>
@@ -5490,14 +5490,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>36229</v>
+        <v>36238</v>
       </c>
       <c r="AY30" s="14">
-        <v>174375</v>
+        <v>174384</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.99399753745126207</v>
+        <v>0.99404884054996923</v>
       </c>
       <c r="BA30" s="8">
         <v>179593</v>
@@ -5507,14 +5507,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>36013</v>
+        <v>36023</v>
       </c>
       <c r="BD30" s="14">
-        <v>176241</v>
+        <v>176251</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.9813355754400227</v>
+        <v>0.98139125689754059</v>
       </c>
       <c r="BF30" s="8">
         <v>302258</v>
@@ -5524,14 +5524,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>72838</v>
+        <v>72858</v>
       </c>
       <c r="BI30" s="14">
-        <v>299457</v>
+        <v>299477</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.99073308233363555</v>
+        <v>0.99079925097102473</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>35674</v>
+        <v>35676</v>
       </c>
       <c r="P31" s="14">
-        <v>133541</v>
+        <v>133543</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>0.99847470933492843</v>
+        <v>0.99848966316497811</v>
       </c>
       <c r="R31" s="8">
         <v>74974</v>
@@ -5651,14 +5651,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>22398</v>
+        <v>22399</v>
       </c>
       <c r="AJ31" s="14">
-        <v>75997</v>
+        <v>75998</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>0.99694346057982419</v>
+        <v>0.99695657877476063</v>
       </c>
       <c r="AL31" s="8">
         <v>77611</v>
@@ -5685,14 +5685,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>34722</v>
+        <v>34724</v>
       </c>
       <c r="AT31" s="14">
-        <v>137474</v>
+        <v>137476</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>1.0043469049306322</v>
+        <v>1.0043615163757771</v>
       </c>
       <c r="AV31" s="8">
         <v>76719</v>
@@ -5702,14 +5702,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>18046</v>
+        <v>18047</v>
       </c>
       <c r="AY31" s="14">
-        <v>76907</v>
+        <v>76908</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>1.0024505011796296</v>
+        <v>1.0024635357603722</v>
       </c>
       <c r="BA31" s="8">
         <v>78720</v>
@@ -5719,14 +5719,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>18509</v>
+        <v>18510</v>
       </c>
       <c r="BD31" s="14">
-        <v>78333</v>
+        <v>78334</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.99508384146341466</v>
+        <v>0.99509654471544717</v>
       </c>
       <c r="BF31" s="8">
         <v>140181</v>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>48216</v>
+        <v>48223</v>
       </c>
       <c r="BI31" s="14">
-        <v>140205</v>
+        <v>140212</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>1.0001712072249449</v>
+        <v>1.0002211426655538</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5761,14 +5761,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>45720</v>
+        <v>45723</v>
       </c>
       <c r="F32" s="14">
-        <v>203713</v>
+        <v>203716</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.99997545626797824</v>
+        <v>0.99999018250719129</v>
       </c>
       <c r="H32" s="8">
         <v>210874</v>
@@ -5778,14 +5778,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>42717</v>
+        <v>42720</v>
       </c>
       <c r="K32" s="14">
-        <v>208089</v>
+        <v>208092</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.9867930612593302</v>
+        <v>0.9868072877642573</v>
       </c>
       <c r="M32" s="8">
         <v>441035</v>
@@ -5795,14 +5795,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>93397</v>
+        <v>93404</v>
       </c>
       <c r="P32" s="14">
-        <v>438315</v>
+        <v>438322</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.99383268901561106</v>
+        <v>0.99384856077182082</v>
       </c>
       <c r="R32" s="8">
         <v>206418</v>
@@ -5812,14 +5812,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>44058</v>
+        <v>44062</v>
       </c>
       <c r="U32" s="14">
-        <v>205099</v>
+        <v>205103</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99361005338681707</v>
+        <v>0.99362943154182293</v>
       </c>
       <c r="W32" s="8">
         <v>212709</v>
@@ -5829,14 +5829,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>45956</v>
+        <v>45960</v>
       </c>
       <c r="Z32" s="14">
-        <v>209143</v>
+        <v>209147</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.98323531209304726</v>
+        <v>0.98325411712715494</v>
       </c>
       <c r="AB32" s="8">
         <v>446806</v>
@@ -5846,14 +5846,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>97533</v>
+        <v>97540</v>
       </c>
       <c r="AE32" s="14">
-        <v>444957</v>
+        <v>444964</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.99586173865167438</v>
+        <v>0.99587740540637326</v>
       </c>
       <c r="AG32" s="8">
         <v>210129</v>
@@ -5863,14 +5863,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>49144</v>
+        <v>49148</v>
       </c>
       <c r="AJ32" s="14">
-        <v>209498</v>
+        <v>209502</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.99699708274440935</v>
+        <v>0.99701611866995987</v>
       </c>
       <c r="AL32" s="8">
         <v>217332</v>
@@ -5880,14 +5880,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>40351</v>
+        <v>40356</v>
       </c>
       <c r="AO32" s="14">
-        <v>212883</v>
+        <v>212888</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.97952901551543259</v>
+        <v>0.97955202179154477</v>
       </c>
       <c r="AQ32" s="8">
         <v>453805</v>
@@ -5897,14 +5897,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>93295</v>
+        <v>93305</v>
       </c>
       <c r="AT32" s="14">
-        <v>452814</v>
+        <v>452824</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.99781624265929203</v>
+        <v>0.99783827855576734</v>
       </c>
       <c r="AV32" s="8">
         <v>213428</v>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>40176</v>
+        <v>40182</v>
       </c>
       <c r="AY32" s="14">
-        <v>213401</v>
+        <v>213407</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.99987349363719846</v>
+        <v>0.99990160616226553</v>
       </c>
       <c r="BA32" s="8">
         <v>220509</v>
@@ -5931,14 +5931,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>39357</v>
+        <v>39361</v>
       </c>
       <c r="BD32" s="14">
-        <v>217599</v>
+        <v>217603</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98680325973089533</v>
+        <v>0.98682139958006254</v>
       </c>
       <c r="BF32" s="8">
         <v>463937</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>127812</v>
+        <v>127821</v>
       </c>
       <c r="BI32" s="14">
-        <v>461014</v>
+        <v>461023</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99369957558892696</v>
+        <v>0.99371897477459226</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5973,14 +5973,14 @@
       </c>
       <c r="E33" s="4">
         <f t="shared" si="0"/>
-        <v>74090</v>
+        <v>74092</v>
       </c>
       <c r="F33" s="14">
-        <v>623262</v>
+        <v>623264</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>1.0036505929999437</v>
+        <v>1.003653813637791</v>
       </c>
       <c r="H33" s="8">
         <v>630476</v>
@@ -5990,14 +5990,14 @@
       </c>
       <c r="J33" s="4">
         <f t="shared" si="2"/>
-        <v>78136</v>
+        <v>78137</v>
       </c>
       <c r="K33" s="14">
-        <v>630448</v>
+        <v>630449</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="3"/>
-        <v>0.99995558911044991</v>
+        <v>0.99995717521364813</v>
       </c>
       <c r="M33" s="8">
         <v>1032030</v>
@@ -6007,14 +6007,14 @@
       </c>
       <c r="O33" s="4">
         <f t="shared" si="4"/>
-        <v>130781</v>
+        <v>130784</v>
       </c>
       <c r="P33" s="14">
-        <v>1032142</v>
+        <v>1032145</v>
       </c>
       <c r="Q33" s="5">
         <f t="shared" si="5"/>
-        <v>1.0001085239770162</v>
+        <v>1.0001114308692576</v>
       </c>
       <c r="R33" s="8">
         <v>629419</v>
@@ -6024,14 +6024,14 @@
       </c>
       <c r="T33" s="4">
         <f t="shared" si="6"/>
-        <v>79468</v>
+        <v>79470</v>
       </c>
       <c r="U33" s="14">
-        <v>629962</v>
+        <v>629964</v>
       </c>
       <c r="V33" s="5">
         <f t="shared" si="7"/>
-        <v>1.000862700363351</v>
+        <v>1.0008658778969177</v>
       </c>
       <c r="W33" s="8">
         <v>637378</v>
@@ -6041,14 +6041,14 @@
       </c>
       <c r="Y33" s="4">
         <f t="shared" si="8"/>
-        <v>80054</v>
+        <v>80055</v>
       </c>
       <c r="Z33" s="14">
-        <v>635163</v>
+        <v>635164</v>
       </c>
       <c r="AA33" s="5">
         <f t="shared" si="9"/>
-        <v>0.99652482514300778</v>
+        <v>0.99652639407070842</v>
       </c>
       <c r="AB33" s="8">
         <v>1041984</v>
@@ -6058,14 +6058,14 @@
       </c>
       <c r="AD33" s="4">
         <f t="shared" si="10"/>
-        <v>142388</v>
+        <v>142394</v>
       </c>
       <c r="AE33" s="14">
-        <v>1042243</v>
+        <v>1042249</v>
       </c>
       <c r="AF33" s="5">
         <f t="shared" si="11"/>
-        <v>1.0002485642773786</v>
+        <v>1.0002543225231866</v>
       </c>
       <c r="AG33" s="8">
         <v>638215</v>
@@ -6075,14 +6075,14 @@
       </c>
       <c r="AI33" s="4">
         <f t="shared" si="12"/>
-        <v>115968</v>
+        <v>115969</v>
       </c>
       <c r="AJ33" s="14">
-        <v>638850</v>
+        <v>638851</v>
       </c>
       <c r="AK33" s="5">
         <f t="shared" si="13"/>
-        <v>1.0009949625126329</v>
+        <v>1.0009965293827314</v>
       </c>
       <c r="AL33" s="8">
         <v>645318</v>
@@ -6092,14 +6092,14 @@
       </c>
       <c r="AN33" s="4">
         <f t="shared" si="14"/>
-        <v>75266</v>
+        <v>75268</v>
       </c>
       <c r="AO33" s="14">
-        <v>642419</v>
+        <v>642421</v>
       </c>
       <c r="AP33" s="5">
         <f t="shared" si="15"/>
-        <v>0.99550764119395396</v>
+        <v>0.99551074044114685</v>
       </c>
       <c r="AQ33" s="8">
         <v>1053133</v>
@@ -6109,14 +6109,14 @@
       </c>
       <c r="AS33" s="4">
         <f t="shared" si="16"/>
-        <v>135437</v>
+        <v>135442</v>
       </c>
       <c r="AT33" s="14">
-        <v>1054023</v>
+        <v>1054028</v>
       </c>
       <c r="AU33" s="5">
         <f t="shared" si="17"/>
-        <v>1.0008450974378356</v>
+        <v>1.0008498451762502</v>
       </c>
       <c r="AV33" s="8">
         <v>647979</v>
@@ -6126,14 +6126,14 @@
       </c>
       <c r="AX33" s="4">
         <f t="shared" si="18"/>
-        <v>69701</v>
+        <v>69703</v>
       </c>
       <c r="AY33" s="14">
-        <v>649948</v>
+        <v>649950</v>
       </c>
       <c r="AZ33" s="5">
         <f t="shared" si="19"/>
-        <v>1.0030386787226129</v>
+        <v>1.0030417652423922</v>
       </c>
       <c r="BA33" s="8">
         <v>657743</v>
@@ -6143,14 +6143,14 @@
       </c>
       <c r="BC33" s="4">
         <f t="shared" si="20"/>
-        <v>65956</v>
+        <v>65962</v>
       </c>
       <c r="BD33" s="14">
-        <v>658023</v>
+        <v>658029</v>
       </c>
       <c r="BE33" s="5">
         <f t="shared" si="21"/>
-        <v>1.0004256981830288</v>
+        <v>1.0004348202869511</v>
       </c>
       <c r="BF33" s="8">
         <v>1071541</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="BH33" s="4">
         <f t="shared" si="22"/>
-        <v>153839</v>
+        <v>153845</v>
       </c>
       <c r="BI33" s="14">
-        <v>1071083</v>
+        <v>1071089</v>
       </c>
       <c r="BJ33" s="5">
         <f t="shared" si="23"/>
-        <v>0.99957257818412926</v>
+        <v>0.9995781775965642</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6492,14 +6492,14 @@
       </c>
       <c r="AN35" s="4">
         <f t="shared" ref="AN35:AN48" si="37">AO35-AM35</f>
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="AO35" s="14">
-        <v>11758</v>
+        <v>11759</v>
       </c>
       <c r="AP35" s="5">
         <f t="shared" ref="AP35:AP48" si="38">AO35/AL35</f>
-        <v>0.99315820592955484</v>
+        <v>0.99324267252301712</v>
       </c>
       <c r="AQ35" s="8">
         <v>14639</v>
@@ -6509,14 +6509,14 @@
       </c>
       <c r="AS35" s="4">
         <f t="shared" ref="AS35:AS48" si="39">AT35-AR35</f>
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="AT35" s="14">
-        <v>14594</v>
+        <v>14595</v>
       </c>
       <c r="AU35" s="5">
         <f t="shared" ref="AU35:AU48" si="40">AT35/AQ35</f>
-        <v>0.99692601953685356</v>
+        <v>0.99699433021381245</v>
       </c>
       <c r="AV35" s="8">
         <v>11843</v>
@@ -6526,14 +6526,14 @@
       </c>
       <c r="AX35" s="4">
         <f t="shared" ref="AX35:AX48" si="41">AY35-AW35</f>
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="AY35" s="14">
-        <v>11830</v>
+        <v>11831</v>
       </c>
       <c r="AZ35" s="5">
         <f t="shared" ref="AZ35:AZ48" si="42">AY35/AV35</f>
-        <v>0.99890230515916578</v>
+        <v>0.99898674322384529</v>
       </c>
       <c r="BA35" s="8">
         <v>11921</v>
@@ -6543,14 +6543,14 @@
       </c>
       <c r="BC35" s="4">
         <f t="shared" ref="BC35:BC48" si="43">BD35-BB35</f>
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="BD35" s="14">
-        <v>11855</v>
+        <v>11856</v>
       </c>
       <c r="BE35" s="5">
         <f t="shared" ref="BE35:BE48" si="44">BD35/BA35</f>
-        <v>0.99446355171546008</v>
+        <v>0.99454743729552886</v>
       </c>
       <c r="BF35" s="8">
         <v>14735</v>
@@ -6560,14 +6560,14 @@
       </c>
       <c r="BH35" s="4">
         <f t="shared" ref="BH35:BH48" si="45">BI35-BG35</f>
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="BI35" s="14">
-        <v>14696</v>
+        <v>14697</v>
       </c>
       <c r="BJ35" s="5">
         <f t="shared" ref="BJ35:BJ48" si="46">BI35/BF35</f>
-        <v>0.99735324058364438</v>
+        <v>0.99742110620970481</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="0"/>
-        <v>175060</v>
+        <v>175070</v>
       </c>
       <c r="F36" s="14">
-        <v>834238</v>
+        <v>834248</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="24"/>
-        <v>0.99784818136039433</v>
+        <v>0.99786014255349942</v>
       </c>
       <c r="H36" s="8">
         <v>854298</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="25"/>
-        <v>170047</v>
+        <v>170055</v>
       </c>
       <c r="K36" s="14">
-        <v>844052</v>
+        <v>844060</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="26"/>
-        <v>0.98800652699643454</v>
+        <v>0.98801589141025736</v>
       </c>
       <c r="M36" s="8">
         <v>1510524</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="27"/>
-        <v>313986</v>
+        <v>313998</v>
       </c>
       <c r="P36" s="14">
-        <v>1500984</v>
+        <v>1500996</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="28"/>
-        <v>0.99368431087490172</v>
+        <v>0.99369225513795212</v>
       </c>
       <c r="R36" s="8">
         <v>845008</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="29"/>
-        <v>178616</v>
+        <v>178624</v>
       </c>
       <c r="U36" s="14">
-        <v>840681</v>
+        <v>840689</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="30"/>
-        <v>0.99487933842046461</v>
+        <v>0.99488880578645411</v>
       </c>
       <c r="W36" s="8">
         <v>865288</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="31"/>
-        <v>186864</v>
+        <v>186873</v>
       </c>
       <c r="Z36" s="14">
-        <v>849774</v>
+        <v>849783</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="32"/>
-        <v>0.9820707094054234</v>
+        <v>0.98208111056665526</v>
       </c>
       <c r="AB36" s="8">
         <v>1522408</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="33"/>
-        <v>327740</v>
+        <v>327760</v>
       </c>
       <c r="AE36" s="14">
-        <v>1515086</v>
+        <v>1515106</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="34"/>
-        <v>0.99519051397522873</v>
+        <v>0.99520365105806063</v>
       </c>
       <c r="AG36" s="8">
         <v>860909</v>
@@ -6687,14 +6687,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="35"/>
-        <v>196479</v>
+        <v>196494</v>
       </c>
       <c r="AJ36" s="14">
-        <v>856914</v>
+        <v>856929</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="36"/>
-        <v>0.99535955600417703</v>
+        <v>0.9953769794484667</v>
       </c>
       <c r="AL36" s="8">
         <v>879793</v>
@@ -6704,14 +6704,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="37"/>
-        <v>162051</v>
+        <v>162061</v>
       </c>
       <c r="AO36" s="14">
-        <v>866646</v>
+        <v>866656</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="38"/>
-        <v>0.98505671220389346</v>
+        <v>0.9850680785139232</v>
       </c>
       <c r="AQ36" s="8">
         <v>1539776</v>
@@ -6721,14 +6721,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="39"/>
-        <v>300071</v>
+        <v>300093</v>
       </c>
       <c r="AT36" s="14">
-        <v>1536682</v>
+        <v>1536704</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="40"/>
-        <v>0.99799061681699153</v>
+        <v>0.99800490460950164</v>
       </c>
       <c r="AV36" s="8">
         <v>875330</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="41"/>
-        <v>161002</v>
+        <v>161014</v>
       </c>
       <c r="AY36" s="14">
-        <v>873839</v>
+        <v>873851</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="42"/>
-        <v>0.9982966424091485</v>
+        <v>0.99831035152456793</v>
       </c>
       <c r="BA36" s="8">
         <v>893595</v>
@@ -6755,14 +6755,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="43"/>
-        <v>151810</v>
+        <v>151822</v>
       </c>
       <c r="BD36" s="14">
-        <v>884077</v>
+        <v>884089</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="44"/>
-        <v>0.98934864228201813</v>
+        <v>0.98936207118437325</v>
       </c>
       <c r="BF36" s="8">
         <v>1566403</v>
@@ -6772,14 +6772,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="45"/>
-        <v>365321</v>
+        <v>365351</v>
       </c>
       <c r="BI36" s="14">
-        <v>1557118</v>
+        <v>1557148</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="46"/>
-        <v>0.9940724066539709</v>
+        <v>0.99409155881340883</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6797,14 +6797,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="0"/>
-        <v>131197</v>
+        <v>131201</v>
       </c>
       <c r="F37" s="14">
-        <v>667636</v>
+        <v>667640</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="24"/>
-        <v>0.98828656396501213</v>
+        <v>0.98829248507510192</v>
       </c>
       <c r="H37" s="8">
         <v>681828</v>
@@ -6814,14 +6814,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="25"/>
-        <v>121654</v>
+        <v>121659</v>
       </c>
       <c r="K37" s="14">
-        <v>670319</v>
+        <v>670324</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="26"/>
-        <v>0.98312037639991312</v>
+        <v>0.98312770962764806</v>
       </c>
       <c r="M37" s="8">
         <v>856106</v>
@@ -6831,14 +6831,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="27"/>
-        <v>152385</v>
+        <v>152394</v>
       </c>
       <c r="P37" s="14">
-        <v>844591</v>
+        <v>844600</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="28"/>
-        <v>0.98654956278778561</v>
+        <v>0.98656007550466884</v>
       </c>
       <c r="R37" s="8">
         <v>679636</v>
@@ -6848,14 +6848,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="29"/>
-        <v>129369</v>
+        <v>129381</v>
       </c>
       <c r="U37" s="14">
-        <v>671332</v>
+        <v>671344</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="30"/>
-        <v>0.98778169490727386</v>
+        <v>0.98779935141752351</v>
       </c>
       <c r="W37" s="8">
         <v>687189</v>
@@ -6865,14 +6865,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="31"/>
-        <v>130992</v>
+        <v>131004</v>
       </c>
       <c r="Z37" s="14">
-        <v>676126</v>
+        <v>676138</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="32"/>
-        <v>0.98390108107085528</v>
+        <v>0.98391854351568486</v>
       </c>
       <c r="AB37" s="8">
         <v>863912</v>
@@ -6882,14 +6882,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="33"/>
-        <v>163647</v>
+        <v>163661</v>
       </c>
       <c r="AE37" s="14">
-        <v>853770</v>
+        <v>853784</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="34"/>
-        <v>0.9882603783718712</v>
+        <v>0.98827658372612026</v>
       </c>
       <c r="AG37" s="8">
         <v>690763</v>
@@ -6899,14 +6899,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="35"/>
-        <v>132013</v>
+        <v>132026</v>
       </c>
       <c r="AJ37" s="14">
-        <v>682580</v>
+        <v>682593</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="36"/>
-        <v>0.98815367933719667</v>
+        <v>0.98817249910606098</v>
       </c>
       <c r="AL37" s="8">
         <v>697437</v>
@@ -6916,14 +6916,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="37"/>
-        <v>116215</v>
+        <v>116230</v>
       </c>
       <c r="AO37" s="14">
-        <v>688186</v>
+        <v>688201</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="38"/>
-        <v>0.98673571949867878</v>
+        <v>0.98675722681761935</v>
       </c>
       <c r="AQ37" s="8">
         <v>873380</v>
@@ -6933,14 +6933,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="39"/>
-        <v>150058</v>
+        <v>150077</v>
       </c>
       <c r="AT37" s="14">
-        <v>867347</v>
+        <v>867366</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="40"/>
-        <v>0.99309235384368777</v>
+        <v>0.993114108406421</v>
       </c>
       <c r="AV37" s="8">
         <v>700086</v>
@@ -6950,14 +6950,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="41"/>
-        <v>117130</v>
+        <v>117149</v>
       </c>
       <c r="AY37" s="14">
-        <v>694542</v>
+        <v>694561</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="42"/>
-        <v>0.99208097290904262</v>
+        <v>0.99210811243190122</v>
       </c>
       <c r="BA37" s="8">
         <v>708485</v>
@@ -6967,14 +6967,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="43"/>
-        <v>113183</v>
+        <v>113202</v>
       </c>
       <c r="BD37" s="14">
-        <v>699055</v>
+        <v>699074</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="44"/>
-        <v>0.98668990874895024</v>
+        <v>0.98671672653620046</v>
       </c>
       <c r="BF37" s="8">
         <v>887779</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="45"/>
-        <v>186668</v>
+        <v>186699</v>
       </c>
       <c r="BI37" s="14">
-        <v>876503</v>
+        <v>876534</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="46"/>
-        <v>0.98729864076532559</v>
+        <v>0.98733355936556277</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7060,14 +7060,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="29"/>
-        <v>6110</v>
+        <v>6111</v>
       </c>
       <c r="U38" s="14">
-        <v>23140</v>
+        <v>23141</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="30"/>
-        <v>1.0099951988127973</v>
+        <v>1.0100388459691851</v>
       </c>
       <c r="W38" s="8">
         <v>23450</v>
@@ -7162,14 +7162,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="41"/>
-        <v>5578</v>
+        <v>5579</v>
       </c>
       <c r="AY38" s="14">
-        <v>24171</v>
+        <v>24172</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="42"/>
-        <v>1.0141820165316997</v>
+        <v>1.0142239751604918</v>
       </c>
       <c r="BA38" s="8">
         <v>24292</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="BC38" s="4">
         <f t="shared" si="43"/>
-        <v>5304</v>
+        <v>5307</v>
       </c>
       <c r="BD38" s="14">
-        <v>24410</v>
+        <v>24413</v>
       </c>
       <c r="BE38" s="5">
         <f t="shared" si="44"/>
-        <v>1.0048575662769637</v>
+        <v>1.004981063724683</v>
       </c>
       <c r="BF38" s="8">
         <v>37393</v>
@@ -7196,14 +7196,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="45"/>
-        <v>10300</v>
+        <v>10303</v>
       </c>
       <c r="BI38" s="14">
-        <v>37536</v>
+        <v>37539</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="46"/>
-        <v>1.0038242451795791</v>
+        <v>1.0039044740994303</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="0"/>
-        <v>58586</v>
+        <v>58593</v>
       </c>
       <c r="F40" s="14">
-        <v>275703</v>
+        <v>275710</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="24"/>
-        <v>0.99273014021215455</v>
+        <v>0.99275534527333087</v>
       </c>
       <c r="H40" s="8">
         <v>279588</v>
@@ -7450,14 +7450,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="25"/>
-        <v>56618</v>
+        <v>56625</v>
       </c>
       <c r="K40" s="14">
-        <v>277365</v>
+        <v>277372</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="26"/>
-        <v>0.99204901497918363</v>
+        <v>0.99207405181910524</v>
       </c>
       <c r="M40" s="8">
         <v>339205</v>
@@ -7467,14 +7467,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="27"/>
-        <v>71969</v>
+        <v>71976</v>
       </c>
       <c r="P40" s="14">
-        <v>336828</v>
+        <v>336835</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="28"/>
-        <v>0.99299243820108785</v>
+        <v>0.99301307468934719</v>
       </c>
       <c r="R40" s="8">
         <v>280405</v>
@@ -7484,14 +7484,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="29"/>
-        <v>61852</v>
+        <v>61857</v>
       </c>
       <c r="U40" s="14">
-        <v>278725</v>
+        <v>278730</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="30"/>
-        <v>0.99400866603662563</v>
+        <v>0.9940264973877071</v>
       </c>
       <c r="W40" s="8">
         <v>283529</v>
@@ -7501,14 +7501,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="31"/>
-        <v>57461</v>
+        <v>57467</v>
       </c>
       <c r="Z40" s="14">
-        <v>280619</v>
+        <v>280625</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="32"/>
-        <v>0.98973649961732313</v>
+        <v>0.98975766147378219</v>
       </c>
       <c r="AB40" s="8">
         <v>342699</v>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="33"/>
-        <v>73646</v>
+        <v>73660</v>
       </c>
       <c r="AE40" s="14">
-        <v>341085</v>
+        <v>341099</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="34"/>
-        <v>0.9952903276636349</v>
+        <v>0.9953311798400345</v>
       </c>
       <c r="AG40" s="8">
         <v>284836</v>
@@ -7535,14 +7535,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="35"/>
-        <v>61244</v>
+        <v>61254</v>
       </c>
       <c r="AJ40" s="14">
-        <v>283336</v>
+        <v>283346</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="36"/>
-        <v>0.99473381173728037</v>
+        <v>0.99476891965903191</v>
       </c>
       <c r="AL40" s="8">
         <v>287465</v>
@@ -7552,14 +7552,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="37"/>
-        <v>57558</v>
+        <v>57570</v>
       </c>
       <c r="AO40" s="14">
-        <v>285425</v>
+        <v>285437</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="38"/>
-        <v>0.99290348390238814</v>
+        <v>0.99294522811472696</v>
       </c>
       <c r="AQ40" s="8">
         <v>346543</v>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="39"/>
-        <v>69344</v>
+        <v>69364</v>
       </c>
       <c r="AT40" s="14">
-        <v>345834</v>
+        <v>345854</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="40"/>
-        <v>0.99795407784892498</v>
+        <v>0.99801179074458291</v>
       </c>
       <c r="AV40" s="8">
         <v>288959</v>
@@ -7586,14 +7586,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="41"/>
-        <v>60351</v>
+        <v>60366</v>
       </c>
       <c r="AY40" s="14">
-        <v>287657</v>
+        <v>287672</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="42"/>
-        <v>0.99549417045324773</v>
+        <v>0.99554608093189689</v>
       </c>
       <c r="BA40" s="8">
         <v>291465</v>
@@ -7603,14 +7603,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="43"/>
-        <v>55959</v>
+        <v>55979</v>
       </c>
       <c r="BD40" s="14">
-        <v>288806</v>
+        <v>288826</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="44"/>
-        <v>0.9908771207520628</v>
+        <v>0.990945739625684</v>
       </c>
       <c r="BF40" s="8">
         <v>351557</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="45"/>
-        <v>85138</v>
+        <v>85164</v>
       </c>
       <c r="BI40" s="14">
-        <v>348730</v>
+        <v>348756</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="46"/>
-        <v>0.99195862975278548</v>
+        <v>0.99203258646535275</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="0"/>
-        <v>143395</v>
+        <v>143406</v>
       </c>
       <c r="F41" s="14">
-        <v>904682</v>
+        <v>904693</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="24"/>
-        <v>0.99185189570601917</v>
+        <v>0.99186395560204099</v>
       </c>
       <c r="H41" s="8">
         <v>920596</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="25"/>
-        <v>139017</v>
+        <v>139029</v>
       </c>
       <c r="K41" s="14">
-        <v>909711</v>
+        <v>909723</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="26"/>
-        <v>0.98817613806707827</v>
+        <v>0.98818917310090415</v>
       </c>
       <c r="M41" s="8">
         <v>1028922</v>
@@ -7679,14 +7679,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="27"/>
-        <v>156584</v>
+        <v>156600</v>
       </c>
       <c r="P41" s="14">
-        <v>1016721</v>
+        <v>1016737</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="28"/>
-        <v>0.98814195828255202</v>
+        <v>0.98815750853806217</v>
       </c>
       <c r="R41" s="8">
         <v>924082</v>
@@ -7696,14 +7696,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="29"/>
-        <v>157513</v>
+        <v>157530</v>
       </c>
       <c r="U41" s="14">
-        <v>914382</v>
+        <v>914399</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="30"/>
-        <v>0.98950309604558906</v>
+        <v>0.98952149268138545</v>
       </c>
       <c r="W41" s="8">
         <v>929406</v>
@@ -7713,14 +7713,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="31"/>
-        <v>146255</v>
+        <v>146273</v>
       </c>
       <c r="Z41" s="14">
-        <v>918158</v>
+        <v>918176</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="32"/>
-        <v>0.98789764645375644</v>
+        <v>0.98791701366248985</v>
       </c>
       <c r="AB41" s="8">
         <v>1036539</v>
@@ -7730,14 +7730,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="33"/>
-        <v>166510</v>
+        <v>166537</v>
       </c>
       <c r="AE41" s="14">
-        <v>1025868</v>
+        <v>1025895</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="34"/>
-        <v>0.98970516304741063</v>
+        <v>0.98973121127135588</v>
       </c>
       <c r="AG41" s="8">
         <v>935526</v>
@@ -7747,14 +7747,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="35"/>
-        <v>150502</v>
+        <v>150524</v>
       </c>
       <c r="AJ41" s="14">
-        <v>924965</v>
+        <v>924987</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="36"/>
-        <v>0.98871116355932387</v>
+        <v>0.98873467974166407</v>
       </c>
       <c r="AL41" s="8">
         <v>940174</v>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="37"/>
-        <v>143230</v>
+        <v>143255</v>
       </c>
       <c r="AO41" s="14">
-        <v>929436</v>
+        <v>929461</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="38"/>
-        <v>0.98857870989838048</v>
+        <v>0.98860530072093034</v>
       </c>
       <c r="AQ41" s="8">
         <v>1046219</v>
@@ -7781,14 +7781,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="39"/>
-        <v>165626</v>
+        <v>165660</v>
       </c>
       <c r="AT41" s="14">
-        <v>1037513</v>
+        <v>1037547</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="40"/>
-        <v>0.99167860648678718</v>
+        <v>0.99171110446283239</v>
       </c>
       <c r="AV41" s="8">
         <v>945246</v>
@@ -7798,14 +7798,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="41"/>
-        <v>138763</v>
+        <v>138790</v>
       </c>
       <c r="AY41" s="14">
-        <v>936473</v>
+        <v>936500</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="42"/>
-        <v>0.99071881817008478</v>
+        <v>0.99074738216295022</v>
       </c>
       <c r="BA41" s="8">
         <v>950318</v>
@@ -7815,14 +7815,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="43"/>
-        <v>134265</v>
+        <v>134292</v>
       </c>
       <c r="BD41" s="14">
-        <v>940070</v>
+        <v>940097</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="44"/>
-        <v>0.98921624130028052</v>
+        <v>0.98924465284252217</v>
       </c>
       <c r="BF41" s="8">
         <v>1056723</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="45"/>
-        <v>199485</v>
+        <v>199533</v>
       </c>
       <c r="BI41" s="14">
-        <v>1047461</v>
+        <v>1047509</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="46"/>
-        <v>0.99123516758885721</v>
+        <v>0.99128059103473665</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7857,14 +7857,14 @@
       </c>
       <c r="E42" s="4">
         <f t="shared" si="0"/>
-        <v>3673</v>
+        <v>3674</v>
       </c>
       <c r="F42" s="14">
-        <v>18228</v>
+        <v>18229</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="24"/>
-        <v>0.9882352941176471</v>
+        <v>0.98828950935212789</v>
       </c>
       <c r="H42" s="8">
         <v>18615</v>
@@ -7874,14 +7874,14 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" si="25"/>
-        <v>3660</v>
+        <v>3661</v>
       </c>
       <c r="K42" s="14">
-        <v>18335</v>
+        <v>18336</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="26"/>
-        <v>0.98495836690840721</v>
+        <v>0.98501208702659149</v>
       </c>
       <c r="M42" s="8">
         <v>20702</v>
@@ -7891,14 +7891,14 @@
       </c>
       <c r="O42" s="4">
         <f t="shared" si="27"/>
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="P42" s="14">
-        <v>20360</v>
+        <v>20361</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" si="28"/>
-        <v>0.98347985701864549</v>
+        <v>0.98352816153028688</v>
       </c>
       <c r="R42" s="8">
         <v>18543</v>
@@ -7908,14 +7908,14 @@
       </c>
       <c r="T42" s="4">
         <f t="shared" si="29"/>
-        <v>4115</v>
+        <v>4116</v>
       </c>
       <c r="U42" s="14">
-        <v>18332</v>
+        <v>18333</v>
       </c>
       <c r="V42" s="5">
         <f t="shared" si="30"/>
-        <v>0.98862104298117892</v>
+        <v>0.98867497168742924</v>
       </c>
       <c r="W42" s="8">
         <v>18720</v>
@@ -8239,14 +8239,14 @@
       </c>
       <c r="BC43" s="4">
         <f t="shared" si="43"/>
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="BD43" s="14">
-        <v>3650</v>
+        <v>3651</v>
       </c>
       <c r="BE43" s="5">
         <f t="shared" si="44"/>
-        <v>0.99863201094391241</v>
+        <v>0.99890560875513001</v>
       </c>
       <c r="BF43" s="8">
         <v>4544</v>
@@ -8281,14 +8281,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="0"/>
-        <v>76621</v>
+        <v>76626</v>
       </c>
       <c r="F44" s="14">
-        <v>333322</v>
+        <v>333327</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="24"/>
-        <v>0.9913570553315012</v>
+        <v>0.99137192619294046</v>
       </c>
       <c r="H44" s="8">
         <v>340996</v>
@@ -8298,14 +8298,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="25"/>
-        <v>75672</v>
+        <v>75677</v>
       </c>
       <c r="K44" s="14">
-        <v>337285</v>
+        <v>337290</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="26"/>
-        <v>0.98911717439500757</v>
+        <v>0.98913183732360499</v>
       </c>
       <c r="M44" s="8">
         <v>408512</v>
@@ -8315,14 +8315,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="27"/>
-        <v>87285</v>
+        <v>87290</v>
       </c>
       <c r="P44" s="14">
-        <v>403996</v>
+        <v>404001</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="28"/>
-        <v>0.98894524518251603</v>
+        <v>0.98895748472505096</v>
       </c>
       <c r="R44" s="8">
         <v>342556</v>
@@ -8332,14 +8332,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="29"/>
-        <v>80308</v>
+        <v>80313</v>
       </c>
       <c r="U44" s="14">
-        <v>339396</v>
+        <v>339401</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="30"/>
-        <v>0.99077523091115027</v>
+        <v>0.99078982706477192</v>
       </c>
       <c r="W44" s="8">
         <v>347597</v>
@@ -8349,14 +8349,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="31"/>
-        <v>79021</v>
+        <v>79026</v>
       </c>
       <c r="Z44" s="14">
-        <v>343164</v>
+        <v>343169</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="32"/>
-        <v>0.98724672537449976</v>
+        <v>0.98726110984847393</v>
       </c>
       <c r="AB44" s="8">
         <v>416340</v>
@@ -8366,14 +8366,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="33"/>
-        <v>92061</v>
+        <v>92069</v>
       </c>
       <c r="AE44" s="14">
-        <v>412361</v>
+        <v>412369</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="34"/>
-        <v>0.99044290723927564</v>
+        <v>0.99046212230388619</v>
       </c>
       <c r="AG44" s="8">
         <v>350469</v>
@@ -8383,14 +8383,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="35"/>
-        <v>79576</v>
+        <v>79584</v>
       </c>
       <c r="AJ44" s="14">
-        <v>347348</v>
+        <v>347356</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="36"/>
-        <v>0.99109479012409085</v>
+        <v>0.99111761667936393</v>
       </c>
       <c r="AL44" s="8">
         <v>355186</v>
@@ -8400,14 +8400,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="37"/>
-        <v>72537</v>
+        <v>72544</v>
       </c>
       <c r="AO44" s="14">
-        <v>350818</v>
+        <v>350825</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="38"/>
-        <v>0.98770221799282631</v>
+        <v>0.98772192597681219</v>
       </c>
       <c r="AQ44" s="8">
         <v>424208</v>
@@ -8417,14 +8417,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="39"/>
-        <v>85721</v>
+        <v>85733</v>
       </c>
       <c r="AT44" s="14">
-        <v>420957</v>
+        <v>420969</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="40"/>
-        <v>0.99233630671745932</v>
+        <v>0.99236459472711502</v>
       </c>
       <c r="AV44" s="8">
         <v>358114</v>
@@ -8434,14 +8434,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="41"/>
-        <v>72317</v>
+        <v>72328</v>
       </c>
       <c r="AY44" s="14">
-        <v>354432</v>
+        <v>354443</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="42"/>
-        <v>0.98971835784135775</v>
+        <v>0.98974907431711689</v>
       </c>
       <c r="BA44" s="8">
         <v>361984</v>
@@ -8451,14 +8451,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="43"/>
-        <v>71204</v>
+        <v>71215</v>
       </c>
       <c r="BD44" s="14">
-        <v>357392</v>
+        <v>357403</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="44"/>
-        <v>0.98731435643564358</v>
+        <v>0.98734474451909482</v>
       </c>
       <c r="BF44" s="8">
         <v>432310</v>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="45"/>
-        <v>106866</v>
+        <v>106886</v>
       </c>
       <c r="BI44" s="14">
-        <v>427043</v>
+        <v>427063</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="46"/>
-        <v>0.98781661307857782</v>
+        <v>0.98786287617681756</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8527,14 +8527,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="27"/>
-        <v>59537</v>
+        <v>59540</v>
       </c>
       <c r="P45" s="14">
-        <v>304809</v>
+        <v>304812</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="28"/>
-        <v>0.98209533260730875</v>
+        <v>0.98210499861453893</v>
       </c>
       <c r="R45" s="8">
         <v>257356</v>
@@ -8544,14 +8544,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="29"/>
-        <v>53296</v>
+        <v>53300</v>
       </c>
       <c r="U45" s="14">
-        <v>253717</v>
+        <v>253721</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="30"/>
-        <v>0.98586005377764652</v>
+        <v>0.98587559645005363</v>
       </c>
       <c r="W45" s="8">
         <v>260553</v>
@@ -8561,14 +8561,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="31"/>
-        <v>55334</v>
+        <v>55338</v>
       </c>
       <c r="Z45" s="14">
-        <v>255678</v>
+        <v>255682</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="32"/>
-        <v>0.98128979516643444</v>
+        <v>0.98130514712937478</v>
       </c>
       <c r="AB45" s="8">
         <v>313911</v>
@@ -8578,14 +8578,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="33"/>
-        <v>65028</v>
+        <v>65035</v>
       </c>
       <c r="AE45" s="14">
-        <v>308435</v>
+        <v>308442</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="34"/>
-        <v>0.98255556511240449</v>
+        <v>0.98257786442654127</v>
       </c>
       <c r="AG45" s="8">
         <v>261210</v>
@@ -8595,14 +8595,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="35"/>
-        <v>53744</v>
+        <v>53752</v>
       </c>
       <c r="AJ45" s="14">
-        <v>257074</v>
+        <v>257082</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="36"/>
-        <v>0.98416599670762983</v>
+        <v>0.98419662340645453</v>
       </c>
       <c r="AL45" s="8">
         <v>264020</v>
@@ -8612,14 +8612,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="37"/>
-        <v>48980</v>
+        <v>48990</v>
       </c>
       <c r="AO45" s="14">
-        <v>259389</v>
+        <v>259399</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="38"/>
-        <v>0.98245966214680702</v>
+        <v>0.98249753806529805</v>
       </c>
       <c r="AQ45" s="8">
         <v>317407</v>
@@ -8629,14 +8629,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="39"/>
-        <v>63296</v>
+        <v>63306</v>
       </c>
       <c r="AT45" s="14">
-        <v>311486</v>
+        <v>311496</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="40"/>
-        <v>0.98134571701317241</v>
+        <v>0.98137722230448599</v>
       </c>
       <c r="AV45" s="8">
         <v>263886</v>
@@ -8646,14 +8646,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="41"/>
-        <v>51113</v>
+        <v>51122</v>
       </c>
       <c r="AY45" s="14">
-        <v>259539</v>
+        <v>259548</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="42"/>
-        <v>0.98352697755849117</v>
+        <v>0.98356108319501601</v>
       </c>
       <c r="BA45" s="8">
         <v>265781</v>
@@ -8663,14 +8663,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="43"/>
-        <v>49565</v>
+        <v>49575</v>
       </c>
       <c r="BD45" s="14">
-        <v>261253</v>
+        <v>261263</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="44"/>
-        <v>0.98296341724954006</v>
+        <v>0.9830010422114448</v>
       </c>
       <c r="BF45" s="8">
         <v>319799</v>
@@ -8680,14 +8680,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="45"/>
-        <v>79750</v>
+        <v>79760</v>
       </c>
       <c r="BI45" s="14">
-        <v>314559</v>
+        <v>314569</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="46"/>
-        <v>0.98361470798845529</v>
+        <v>0.98364597762969863</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8824,14 +8824,14 @@
       </c>
       <c r="AN46" s="4">
         <f t="shared" si="37"/>
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AO46" s="14">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="AP46" s="5">
         <f t="shared" si="38"/>
-        <v>1.0106732348111658</v>
+        <v>1.0110837438423645</v>
       </c>
       <c r="AQ46" s="8">
         <v>7143</v>
@@ -8841,14 +8841,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="39"/>
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="AT46" s="14">
-        <v>7359</v>
+        <v>7361</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="40"/>
-        <v>1.0302393952120958</v>
+        <v>1.0305193896122078</v>
       </c>
       <c r="AV46" s="8">
         <v>2225</v>
@@ -8858,14 +8858,14 @@
       </c>
       <c r="AX46" s="4">
         <f t="shared" si="41"/>
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AY46" s="14">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="AZ46" s="5">
         <f t="shared" si="42"/>
-        <v>1.063370786516854</v>
+        <v>1.0638202247191011</v>
       </c>
       <c r="BA46" s="8">
         <v>2388</v>
@@ -8875,14 +8875,14 @@
       </c>
       <c r="BC46" s="4">
         <f t="shared" si="43"/>
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="BD46" s="14">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="BE46" s="5">
         <f t="shared" si="44"/>
-        <v>1.018425460636516</v>
+        <v>1.0188442211055277</v>
       </c>
       <c r="BF46" s="8">
         <v>7407</v>
@@ -8892,14 +8892,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="45"/>
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="BI46" s="14">
-        <v>7551</v>
+        <v>7552</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="46"/>
-        <v>1.0194410692588092</v>
+        <v>1.0195760766842177</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9115,10 +9115,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="27"/>
+      <c r="B48" s="22"/>
       <c r="C48" s="10">
         <f>SUM(C10:C47)</f>
         <v>7712416</v>
@@ -9129,15 +9129,15 @@
       </c>
       <c r="E48" s="12">
         <f t="shared" ref="E48" si="47">F48-D48</f>
-        <v>1449869</v>
+        <v>1449961</v>
       </c>
       <c r="F48" s="11">
         <f>SUM(F10:F47)</f>
-        <v>7677564</v>
+        <v>7677656</v>
       </c>
       <c r="G48" s="13">
         <f t="shared" ref="G48" si="48">F48/C48</f>
-        <v>0.99548105288926325</v>
+        <v>0.99549298170638101</v>
       </c>
       <c r="H48" s="10">
         <f>SUM(H10:H47)</f>
@@ -9149,15 +9149,15 @@
       </c>
       <c r="J48" s="12">
         <f t="shared" si="25"/>
-        <v>1416245</v>
+        <v>1416335</v>
       </c>
       <c r="K48" s="11">
         <f>SUM(K10:K47)</f>
-        <v>7772880</v>
+        <v>7772970</v>
       </c>
       <c r="L48" s="13">
         <f t="shared" si="26"/>
-        <v>0.98799289823859238</v>
+        <v>0.98800433793158149</v>
       </c>
       <c r="M48" s="10">
         <f>SUM(M10:M47)</f>
@@ -9169,15 +9169,15 @@
       </c>
       <c r="O48" s="12">
         <f t="shared" si="27"/>
-        <v>2193012</v>
+        <v>2193179</v>
       </c>
       <c r="P48" s="11">
         <f>SUM(P10:P47)</f>
-        <v>12050069</v>
+        <v>12050236</v>
       </c>
       <c r="Q48" s="13">
         <f t="shared" si="28"/>
-        <v>0.99159143506898972</v>
+        <v>0.99160517737782261</v>
       </c>
       <c r="R48" s="10">
         <f>SUM(R10:R47)</f>
@@ -9189,15 +9189,15 @@
       </c>
       <c r="T48" s="12">
         <f t="shared" ref="T48" si="49">U48-S48</f>
-        <v>1489195</v>
+        <v>1489327</v>
       </c>
       <c r="U48" s="11">
         <f>SUM(U10:U47)</f>
-        <v>7743647</v>
+        <v>7743779</v>
       </c>
       <c r="V48" s="13">
         <f t="shared" si="30"/>
-        <v>0.99202576822408406</v>
+        <v>0.9920426785250579</v>
       </c>
       <c r="W48" s="10">
         <f>SUM(W10:W47)</f>
@@ -9209,15 +9209,15 @@
       </c>
       <c r="Y48" s="12">
         <f t="shared" si="31"/>
-        <v>1484743</v>
+        <v>1484891</v>
       </c>
       <c r="Z48" s="11">
         <f>SUM(Z10:Z47)</f>
-        <v>7828187</v>
+        <v>7828335</v>
       </c>
       <c r="AA48" s="13">
         <f t="shared" si="32"/>
-        <v>0.98494633315680713</v>
+        <v>0.9849649545894974</v>
       </c>
       <c r="AB48" s="10">
         <f>SUM(AB10:AB47)</f>
@@ -9229,15 +9229,15 @@
       </c>
       <c r="AD48" s="12">
         <f t="shared" si="33"/>
-        <v>2329156</v>
+        <v>2329435</v>
       </c>
       <c r="AE48" s="11">
         <f>SUM(AE10:AE47)</f>
-        <v>12196003</v>
+        <v>12196282</v>
       </c>
       <c r="AF48" s="13">
         <f t="shared" si="34"/>
-        <v>0.99282198671966604</v>
+        <v>0.99284469886021687</v>
       </c>
       <c r="AG48" s="10">
         <f>SUM(AG10:AG47)</f>
@@ -9249,15 +9249,15 @@
       </c>
       <c r="AI48" s="12">
         <f t="shared" si="35"/>
-        <v>1608878</v>
+        <v>1609083</v>
       </c>
       <c r="AJ48" s="11">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7875056</v>
+        <v>7875261</v>
       </c>
       <c r="AK48" s="13">
         <f t="shared" si="36"/>
-        <v>0.99252242076450525</v>
+        <v>0.99254825767236432</v>
       </c>
       <c r="AL48" s="10">
         <f>SUM(AL10:AL47)</f>
@@ -9269,15 +9269,15 @@
       </c>
       <c r="AN48" s="12">
         <f t="shared" si="37"/>
-        <v>1382888</v>
+        <v>1383113</v>
       </c>
       <c r="AO48" s="11">
         <f>SUM(AO10:AO47)</f>
-        <v>7957267</v>
+        <v>7957492</v>
       </c>
       <c r="AP48" s="13">
         <f t="shared" si="38"/>
-        <v>0.98499593425840049</v>
+        <v>0.98502378604283947</v>
       </c>
       <c r="AQ48" s="10">
         <f>SUM(AQ10:AQ47)</f>
@@ -9289,15 +9289,15 @@
       </c>
       <c r="AS48" s="12">
         <f t="shared" si="39"/>
-        <v>2139476</v>
+        <v>2139841</v>
       </c>
       <c r="AT48" s="11">
         <f>SUM(AT10:AT47)</f>
-        <v>12388193</v>
+        <v>12388558</v>
       </c>
       <c r="AU48" s="13">
         <f t="shared" si="40"/>
-        <v>0.99541567920794816</v>
+        <v>0.9954450076760234</v>
       </c>
       <c r="AV48" s="10">
         <f>SUM(AV10:AV47)</f>
@@ -9309,15 +9309,15 @@
       </c>
       <c r="AX48" s="12">
         <f t="shared" si="41"/>
-        <v>1372940</v>
+        <v>1373198</v>
       </c>
       <c r="AY48" s="11">
         <f>SUM(AY10:AY47)</f>
-        <v>8014155</v>
+        <v>8014413</v>
       </c>
       <c r="AZ48" s="13">
         <f t="shared" si="42"/>
-        <v>0.99414724804920673</v>
+        <v>0.9941792526697808</v>
       </c>
       <c r="BA48" s="10">
         <f>SUM(BA10:BA47)</f>
@@ -9329,15 +9329,15 @@
       </c>
       <c r="BC48" s="12">
         <f t="shared" si="43"/>
-        <v>1321183</v>
+        <v>1321477</v>
       </c>
       <c r="BD48" s="11">
         <f>SUM(BD10:BD47)</f>
-        <v>8098361</v>
+        <v>8098655</v>
       </c>
       <c r="BE48" s="13">
         <f t="shared" si="44"/>
-        <v>0.98730940919517385</v>
+        <v>0.98734525212268764</v>
       </c>
       <c r="BF48" s="10">
         <f>SUM(BF10:BF47)</f>
@@ -9349,15 +9349,15 @@
       </c>
       <c r="BH48" s="12">
         <f t="shared" si="45"/>
-        <v>2709991</v>
+        <v>2710519</v>
       </c>
       <c r="BI48" s="11">
         <f>SUM(BI10:BI47)</f>
-        <v>12556472</v>
+        <v>12557000</v>
       </c>
       <c r="BJ48" s="13">
         <f t="shared" si="46"/>
-        <v>0.99213120038937863</v>
+        <v>0.99217291953419939</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
@@ -9432,61 +9432,6 @@
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1"/>
-      <c r="V50" s="1"/>
-      <c r="W50" s="1"/>
-      <c r="X50" s="1"/>
-      <c r="Y50" s="1"/>
-      <c r="Z50" s="1"/>
-      <c r="AA50" s="1"/>
-      <c r="AB50" s="1"/>
-      <c r="AC50" s="1"/>
-      <c r="AD50" s="1"/>
-      <c r="AE50" s="1"/>
-      <c r="AF50" s="1"/>
-      <c r="AG50" s="1"/>
-      <c r="AH50" s="1"/>
-      <c r="AI50" s="1"/>
-      <c r="AJ50" s="1"/>
-      <c r="AK50" s="1"/>
-      <c r="AL50" s="1"/>
-      <c r="AM50" s="1"/>
-      <c r="AN50" s="1"/>
-      <c r="AO50" s="1"/>
-      <c r="AP50" s="1"/>
-      <c r="AQ50" s="1"/>
-      <c r="AR50" s="1"/>
-      <c r="AS50" s="1"/>
-      <c r="AT50" s="1"/>
-      <c r="AU50" s="1"/>
-      <c r="AV50" s="1"/>
-      <c r="AW50" s="1"/>
-      <c r="AX50" s="1"/>
-      <c r="AY50" s="1"/>
-      <c r="AZ50" s="1"/>
-      <c r="BA50" s="1"/>
-      <c r="BB50" s="1"/>
-      <c r="BC50" s="1"/>
-      <c r="BD50" s="1"/>
-      <c r="BE50" s="1"/>
-      <c r="BF50" s="1"/>
-      <c r="BG50" s="1"/>
-      <c r="BH50" s="1"/>
-      <c r="BI50" s="1"/>
-      <c r="BJ50" s="1"/>
     </row>
     <row r="51" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
@@ -9496,61 +9441,6 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1"/>
-      <c r="R51" s="1"/>
-      <c r="S51" s="1"/>
-      <c r="T51" s="1"/>
-      <c r="U51" s="1"/>
-      <c r="V51" s="1"/>
-      <c r="W51" s="1"/>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="1"/>
-      <c r="Z51" s="1"/>
-      <c r="AA51" s="1"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="1"/>
-      <c r="AD51" s="1"/>
-      <c r="AE51" s="1"/>
-      <c r="AF51" s="1"/>
-      <c r="AG51" s="1"/>
-      <c r="AH51" s="1"/>
-      <c r="AI51" s="1"/>
-      <c r="AJ51" s="1"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="1"/>
-      <c r="AM51" s="1"/>
-      <c r="AN51" s="1"/>
-      <c r="AO51" s="1"/>
-      <c r="AP51" s="1"/>
-      <c r="AQ51" s="1"/>
-      <c r="AR51" s="1"/>
-      <c r="AS51" s="1"/>
-      <c r="AT51" s="1"/>
-      <c r="AU51" s="1"/>
-      <c r="AV51" s="1"/>
-      <c r="AW51" s="1"/>
-      <c r="AX51" s="1"/>
-      <c r="AY51" s="1"/>
-      <c r="AZ51" s="1"/>
-      <c r="BA51" s="1"/>
-      <c r="BB51" s="1"/>
-      <c r="BC51" s="1"/>
-      <c r="BD51" s="1"/>
-      <c r="BE51" s="1"/>
-      <c r="BF51" s="1"/>
-      <c r="BG51" s="1"/>
-      <c r="BH51" s="1"/>
-      <c r="BI51" s="1"/>
-      <c r="BJ51" s="1"/>
     </row>
     <row r="52" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -9562,41 +9452,18 @@
       <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
+      <c r="A53" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="6"/>
       <c r="G53" s="1"/>
-    </row>
-    <row r="54" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-    </row>
-    <row r="55" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A55" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="AV8:AZ8"/>
@@ -9610,6 +9477,11 @@
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
